--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rd38f9e7e06ea46ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Ra7375a2e5dfc433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Ra4a3221c8ea9478b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rf51891fb9c854582"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -838,7 +838,7 @@
         <v>买入税率（Flap）</v>
       </c>
       <c r="J7" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,25,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,25,FALSE)</f>
         <v>0</v>
       </c>
       <c r="K7" s="49"/>
@@ -863,7 +863,7 @@
         <v>卖出税率（Flap）</v>
       </c>
       <c r="J8" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,26,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,26,FALSE)</f>
         <v>0</v>
       </c>
       <c r="K8" s="49"/>
@@ -886,7 +886,7 @@
         <v>Creator Tax（Pons）</v>
       </c>
       <c r="J9" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,27,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,27,FALSE)</f>
         <v>0</v>
       </c>
       <c r="K9" s="49"/>
@@ -927,7 +927,7 @@
         <v>单地址 Gas</v>
       </c>
       <c r="G11" s="54" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,33,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,33,FALSE)</f>
         <v>0.01</v>
       </c>
       <c r="H11" s="49"/>
@@ -956,7 +956,7 @@
         <v>洗筹基础费率</v>
       </c>
       <c r="J12" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
         <v>0.0025</v>
       </c>
       <c r="K12" s="49"/>
@@ -1032,10 +1032,10 @@
       </c>
       <c r="D18" s="53" t="n">
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>114.7454228329424</v>
+        <v>112.69004142754045</v>
       </c>
       <c r="E18" s="48" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="F18" s="3" t="str">
@@ -1046,7 +1046,7 @@
         <v>2.2</v>
       </c>
       <c r="H18" s="48" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,4,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="I18" s="3" t="str">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J18" s="62" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>87910.6729483702</v>
+        <v>86489.00582052911</v>
       </c>
       <c r="K18" s="48" t="str">
         <v>USDT</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D19" s="63" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>86256.88030047243</v>
+        <v>84832.84998281738</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G19" s="63" t="n">
         <f>IF(G18=0,0,IF(AND(ISNUMBER(J44),J44&gt;0),G18*J44,""))</f>
-        <v>1653.7926478977554</v>
+        <v>1656.155837711734</v>
       </c>
       <c r="H19" s="3" t="str">
         <v>USDT</v>
@@ -1125,7 +1125,7 @@
         <v>71.23230102652082</v>
       </c>
       <c r="E22" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="F22" s="3"/>
@@ -1147,7 +1147,7 @@
         <v>18.180001026520895</v>
       </c>
       <c r="E23" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="F23" s="3"/>
@@ -1172,7 +1172,7 @@
         <v>7.055999999999987</v>
       </c>
       <c r="E24" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="F24" s="3"/>
@@ -1197,7 +1197,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="F25" s="3"/>
@@ -1218,11 +1218,11 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",IF($G$40="pons",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(1+$G$42)),"")))</f>
-        <v>4.277120779900693</v>
+        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
+        <v>2.221739374498758</v>
       </c>
       <c r="E26" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="F26" s="3"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D27" s="59" t="n">
         <f>D8*J54</f>
-        <v>0.9353058750000001</v>
+        <v>0.93765</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>目标持仓全部洗一轮，以卖出所得买回。补回为小单固定价 + 现有外盘曲线差额的保守预留，损耗仍按目标加缓冲 FDV；非逐笔模拟。Pons 按原批准口径持仓不降、补回为 0。</v>
+        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -1395,11 +1395,11 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="65" t="n">
-        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,23,FALSE))</f>
+        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,23,FALSE))</f>
         <v>3.5279999996314997</v>
       </c>
       <c r="H37" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="I37" s="3"/>
@@ -1441,7 +1441,7 @@
         <v>模型类型</v>
       </c>
       <c r="G40" s="49" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,10,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,10,FALSE)</f>
         <v>generic</v>
       </c>
       <c r="H40" s="49"/>
@@ -1458,7 +1458,7 @@
         <v>内盘基础费</v>
       </c>
       <c r="G41" s="58" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,19,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,19,FALSE)</f>
         <v>0.01</v>
       </c>
       <c r="H41" s="49"/>
@@ -1480,7 +1480,7 @@
         <v>外盘基础费</v>
       </c>
       <c r="G42" s="58" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
         <v>0.0025</v>
       </c>
       <c r="H42" s="49"/>
@@ -1497,7 +1497,7 @@
         <v>毕业控筹率</v>
       </c>
       <c r="G43" s="58" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,15,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,15,FALSE)</f>
         <v>0.8</v>
       </c>
       <c r="H43" s="49"/>
@@ -1505,7 +1505,7 @@
         <v>模型键</v>
       </c>
       <c r="J43" s="49" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,2,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,2,FALSE)</f>
         <v>fourmeme-bnb</v>
       </c>
       <c r="K43" s="49"/>
@@ -1519,7 +1519,7 @@
         <v>内盘初始 TOKEN</v>
       </c>
       <c r="G44" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,12,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,12,FALSE)</f>
         <v>1073972562</v>
       </c>
       <c r="H44" s="49"/>
@@ -1527,8 +1527,8 @@
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J44" s="49" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,7,FALSE))</f>
-        <v>751.723930862616</v>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,7,FALSE))</f>
+        <v>752.7981080507881</v>
       </c>
       <c r="K44" s="49"/>
       <c r="L44" s="49"/>
@@ -1538,7 +1538,7 @@
         <v>总供应量</v>
       </c>
       <c r="D45" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,11,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,11,FALSE)</f>
         <v>1000000000</v>
       </c>
       <c r="E45" s="49"/>
@@ -1546,7 +1546,7 @@
         <v>内盘初始 Quote</v>
       </c>
       <c r="G45" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,13,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,13,FALSE)</f>
         <v>6.164383561643836</v>
       </c>
       <c r="H45" s="49"/>
@@ -1554,7 +1554,7 @@
         <v>税率上限</v>
       </c>
       <c r="J45" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,32,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,32,FALSE)</f>
         <v>0.1</v>
       </c>
       <c r="K45" s="49"/>
@@ -1568,7 +1568,7 @@
         <v>内盘 K</v>
       </c>
       <c r="G46" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,14,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,14,FALSE)</f>
         <v>6620378206</v>
       </c>
       <c r="H46" s="49"/>
@@ -1607,7 +1607,7 @@
         <v>外盘初始 TOKEN</v>
       </c>
       <c r="G48" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,16,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,16,FALSE)</f>
         <v>200000000</v>
       </c>
       <c r="H48" s="49"/>
@@ -1629,7 +1629,7 @@
         <v>外盘初始 Quote</v>
       </c>
       <c r="G49" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,17,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,17,FALSE)</f>
         <v>17.64</v>
       </c>
       <c r="H49" s="49"/>
@@ -1646,7 +1646,7 @@
         <v>外盘 K</v>
       </c>
       <c r="G50" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,18,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,18,FALSE)</f>
         <v>3528000000</v>
       </c>
       <c r="H50" s="49"/>
@@ -1673,7 +1673,7 @@
         <v>永久锁仓 TOKEN</v>
       </c>
       <c r="G51" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,22,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,22,FALSE)</f>
         <v>0</v>
       </c>
       <c r="H51" s="49"/>
@@ -1700,7 +1700,7 @@
         <v>一套内盘原值</v>
       </c>
       <c r="G52" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,21,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,21,FALSE)</f>
         <v>18.180001026520895</v>
       </c>
       <c r="H52" s="49"/>
@@ -1727,7 +1727,7 @@
         <v>内盘募集 Quote</v>
       </c>
       <c r="G53" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,24,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,24,FALSE)</f>
         <v>18.000000483500074</v>
       </c>
       <c r="H53" s="49"/>
@@ -1757,8 +1757,8 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="58" t="n">
-        <f>IF($G$40="pons",1,(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))^2)</f>
-        <v>0.9950062500000001</v>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
+        <v>0.9975</v>
       </c>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -1768,15 +1768,15 @@
         <v>有效价格 / USDT</v>
       </c>
       <c r="D55" s="60" t="n">
-        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,6,FALSE),""))</f>
-        <v>751.723930862616</v>
+        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE),""))</f>
+        <v>752.7981080507881</v>
       </c>
       <c r="E55" s="49"/>
       <c r="F55" s="49" t="str">
         <v>价格来源</v>
       </c>
       <c r="G55" s="49" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,9,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,9,FALSE)</f>
         <v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</v>
       </c>
       <c r="H55" s="49"/>
@@ -1784,7 +1784,7 @@
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="49" t="n">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
         <v>60000000.00000005</v>
       </c>
       <c r="K55" s="49"/>
@@ -1795,8 +1795,8 @@
         <v>价格时间 / UTC</v>
       </c>
       <c r="D56" s="61" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,8,FALSE)</f>
-        <v>46283.40053702546</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,8,FALSE)</f>
+        <v>46285.27349457176</v>
       </c>
       <c r="E56" s="49"/>
       <c r="F56" s="49" t="str">
@@ -1811,8 +1811,8 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="49" t="n">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
-        <v>64694124.99999993</v>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
+        <v>62350000.000000015</v>
       </c>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G59" s="78" t="n">
         <f>IF(AND(ISNUMBER(F59),ISNUMBER($D$55)),F59*$D$55,"")</f>
-        <v>0.000004314741722182927</v>
+        <v>0.000004320907279697511</v>
       </c>
       <c r="H59" s="81" t="n">
         <f>IF(ISNUMBER(F59),F59*$D$45,"")</f>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I59" s="75" t="n">
         <f>IF(AND(ISNUMBER(H59),ISNUMBER($D$55)),H59*$D$55,"")</f>
-        <v>4314.741722182926</v>
+        <v>4320.907279697511</v>
       </c>
       <c r="J59" s="81" t="n">
         <f>0</f>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G60" s="79" t="n">
         <f>IF(AND(ISNUMBER(F60),ISNUMBER($D$55)),F60*$D$55,"")</f>
-        <v>0.000005246234891623481</v>
+        <v>0.0000052537315078851285</v>
       </c>
       <c r="H60" s="82" t="n">
         <f>IF(ISNUMBER(F60),F60*$D$45,"")</f>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="I60" s="76" t="n">
         <f>IF(AND(ISNUMBER(H60),ISNUMBER($D$55)),H60*$D$55,"")</f>
-        <v>5246.234891623481</v>
+        <v>5253.731507885129</v>
       </c>
       <c r="J60" s="82" t="n">
         <f>E60-E59</f>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G61" s="79" t="n">
         <f>IF(AND(ISNUMBER(F61),ISNUMBER($D$55)),F61*$D$55,"")</f>
-        <v>0.000006515467453233982</v>
+        <v>0.000006524777741520947</v>
       </c>
       <c r="H61" s="82" t="n">
         <f>IF(ISNUMBER(F61),F61*$D$45,"")</f>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I61" s="76" t="n">
         <f>IF(AND(ISNUMBER(H61),ISNUMBER($D$55)),H61*$D$55,"")</f>
-        <v>6515.467453233982</v>
+        <v>6524.777741520947</v>
       </c>
       <c r="J61" s="82" t="n">
         <f>E61-E60</f>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G62" s="79" t="n">
         <f>IF(AND(ISNUMBER(F62),ISNUMBER($D$55)),F62*$D$55,"")</f>
-        <v>0.0000083078767827702</v>
+        <v>0.00000831974833741388</v>
       </c>
       <c r="H62" s="82" t="n">
         <f>IF(ISNUMBER(F62),F62*$D$45,"")</f>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I62" s="76" t="n">
         <f>IF(AND(ISNUMBER(H62),ISNUMBER($D$55)),H62*$D$55,"")</f>
-        <v>8307.876782770201</v>
+        <v>8319.74833741388</v>
       </c>
       <c r="J62" s="82" t="n">
         <f>E62-E61</f>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G63" s="79" t="n">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER($D$55)),F63*$D$55,"")</f>
-        <v>0.000010956119073489936</v>
+        <v>0.000010971774838454255</v>
       </c>
       <c r="H63" s="82" t="n">
         <f>IF(ISNUMBER(F63),F63*$D$45,"")</f>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="I63" s="76" t="n">
         <f>IF(AND(ISNUMBER(H63),ISNUMBER($D$55)),H63*$D$55,"")</f>
-        <v>10956.119073489936</v>
+        <v>10971.774838454254</v>
       </c>
       <c r="J63" s="82" t="n">
         <f>E63-E62</f>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G64" s="79" t="n">
         <f>IF(AND(ISNUMBER(F64),ISNUMBER($D$55)),F64*$D$55,"")</f>
-        <v>0.000015106328075514286</v>
+        <v>0.00001512791428868318</v>
       </c>
       <c r="H64" s="82" t="n">
         <f>IF(ISNUMBER(F64),F64*$D$45,"")</f>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I64" s="76" t="n">
         <f>IF(AND(ISNUMBER(H64),ISNUMBER($D$55)),H64*$D$55,"")</f>
-        <v>15106.328075514286</v>
+        <v>15127.914288683181</v>
       </c>
       <c r="J64" s="82" t="n">
         <f>E64-E63</f>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G65" s="79" t="n">
         <f>IF(AND(ISNUMBER(F65),ISNUMBER($D$55)),F65*$D$55,"")</f>
-        <v>0.000022153113557891053</v>
+        <v>0.000022184769287147357</v>
       </c>
       <c r="H65" s="82" t="n">
         <f>IF(ISNUMBER(F65),F65*$D$45,"")</f>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="I65" s="76" t="n">
         <f>IF(AND(ISNUMBER(H65),ISNUMBER($D$55)),H65*$D$55,"")</f>
-        <v>22153.113557891054</v>
+        <v>22184.76928714736</v>
       </c>
       <c r="J65" s="82" t="n">
         <f>E65-E64</f>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G66" s="79" t="n">
         <f>IF(AND(ISNUMBER(F66),ISNUMBER($D$55)),F66*$D$55,"")</f>
-        <v>0.000035584567948144505</v>
+        <v>0.00003563541657697157</v>
       </c>
       <c r="H66" s="82" t="n">
         <f>IF(ISNUMBER(F66),F66*$D$45,"")</f>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="I66" s="76" t="n">
         <f>IF(AND(ISNUMBER(H66),ISNUMBER($D$55)),H66*$D$55,"")</f>
-        <v>35584.567948144504</v>
+        <v>35635.41657697157</v>
       </c>
       <c r="J66" s="82" t="n">
         <f>E66-E65</f>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G67" s="80" t="n">
         <f>IF(AND(ISNUMBER(F67),ISNUMBER($D$55)),F67*$D$55,"")</f>
-        <v>0.00006630206188782314</v>
+        <v>0.00006639680433180379</v>
       </c>
       <c r="H67" s="83" t="n">
         <f>IF(ISNUMBER(F67),F67*$D$45,"")</f>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I67" s="77" t="n">
         <f>IF(AND(ISNUMBER(H67),ISNUMBER($D$55)),H67*$D$55,"")</f>
-        <v>66302.06188782313</v>
+        <v>66396.8043318038</v>
       </c>
       <c r="J67" s="83" t="n">
         <f>E67-E66</f>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G72" s="78" t="n">
         <f>IF(AND(ISNUMBER(F72),ISNUMBER($D$55)),F72*$D$55,"")</f>
-        <v>0.00006630205070208274</v>
+        <v>0.00006639679313007951</v>
       </c>
       <c r="H72" s="81" t="n">
         <f>IF(ISNUMBER(F72),F72*$D$45,"")</f>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I72" s="75" t="n">
         <f>IF(AND(ISNUMBER(H72),ISNUMBER($D$55)),H72*$D$55,"")</f>
-        <v>66302.05070208274</v>
+        <v>66396.79313007952</v>
       </c>
       <c r="J72" s="81" t="n">
         <f>IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),0,E72-$G$49)</f>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G73" s="79" t="n">
         <f>IF(AND(ISNUMBER(F73),ISNUMBER($D$55)),F73*$D$55,"")</f>
-        <v>0.00006974574695814099</v>
+        <v>0.00006984541026175364</v>
       </c>
       <c r="H73" s="82" t="n">
         <f>IF(ISNUMBER(F73),F73*$D$45,"")</f>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="I73" s="76" t="n">
         <f>IF(AND(ISNUMBER(H73),ISNUMBER($D$55)),H73*$D$55,"")</f>
-        <v>69745.746958141</v>
+        <v>69845.41026175364</v>
       </c>
       <c r="J73" s="82" t="n">
         <f>IF(D73="","",E73-E72)</f>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G74" s="79" t="n">
         <f>IF(AND(ISNUMBER(F74),ISNUMBER($D$55)),F74*$D$55,"")</f>
-        <v>0.00007346487612419145</v>
+        <v>0.00007356985388374466</v>
       </c>
       <c r="H74" s="82" t="n">
         <f>IF(ISNUMBER(F74),F74*$D$45,"")</f>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I74" s="76" t="n">
         <f>IF(AND(ISNUMBER(H74),ISNUMBER($D$55)),H74*$D$55,"")</f>
-        <v>73464.87612419145</v>
+        <v>73569.85388374467</v>
       </c>
       <c r="J74" s="82" t="n">
         <f>IF(D74="","",E74-E73)</f>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G75" s="79" t="n">
         <f>IF(AND(ISNUMBER(F75),ISNUMBER($D$55)),F75*$D$55,"")</f>
-        <v>0.00007748961367664897</v>
+        <v>0.00007760034259176574</v>
       </c>
       <c r="H75" s="82" t="n">
         <f>IF(ISNUMBER(F75),F75*$D$45,"")</f>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="I75" s="76" t="n">
         <f>IF(AND(ISNUMBER(H75),ISNUMBER($D$55)),H75*$D$55,"")</f>
-        <v>77489.61367664898</v>
+        <v>77600.34259176573</v>
       </c>
       <c r="J75" s="82" t="n">
         <f>IF(D75="","",E75-E74)</f>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="G76" s="79" t="n">
         <f>IF(AND(ISNUMBER(F76),ISNUMBER($D$55)),F76*$D$55,"")</f>
-        <v>0.00008185438358281824</v>
+        <v>0.00008197134954330808</v>
       </c>
       <c r="H76" s="82" t="n">
         <f>IF(ISNUMBER(F76),F76*$D$45,"")</f>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I76" s="76" t="n">
         <f>IF(AND(ISNUMBER(H76),ISNUMBER($D$55)),H76*$D$55,"")</f>
-        <v>81854.38358281825</v>
+        <v>81971.34954330808</v>
       </c>
       <c r="J76" s="82" t="n">
         <f>IF(D76="","",E76-E75)</f>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G77" s="79" t="n">
         <f>IF(AND(ISNUMBER(F77),ISNUMBER($D$55)),F77*$D$55,"")</f>
-        <v>0.00008659859683537343</v>
+        <v>0.00008672234204745084</v>
       </c>
       <c r="H77" s="82" t="n">
         <f>IF(ISNUMBER(F77),F77*$D$45,"")</f>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="I77" s="76" t="n">
         <f>IF(AND(ISNUMBER(H77),ISNUMBER($D$55)),H77*$D$55,"")</f>
-        <v>86598.59683537342</v>
+        <v>86722.34204745085</v>
       </c>
       <c r="J77" s="82" t="n">
         <f>IF(D77="","",E77-E76)</f>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="G78" s="79" t="n">
         <f>IF(AND(ISNUMBER(F78),ISNUMBER($D$55)),F78*$D$55,"")</f>
-        <v>0.00009176754422433602</v>
+        <v>0.00009189867561256686</v>
       </c>
       <c r="H78" s="82" t="n">
         <f>IF(ISNUMBER(F78),F78*$D$45,"")</f>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I78" s="76" t="n">
         <f>IF(AND(ISNUMBER(H78),ISNUMBER($D$55)),H78*$D$55,"")</f>
-        <v>91767.54422433602</v>
+        <v>91898.67561256685</v>
       </c>
       <c r="J78" s="82" t="n">
         <f>IF(D78="","",E78-E77)</f>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G79" s="79" t="n">
         <f>IF(AND(ISNUMBER(F79),ISNUMBER($D$55)),F79*$D$55,"")</f>
-        <v>0.00009741348128864324</v>
+        <v>0.00009755268044823446</v>
       </c>
       <c r="H79" s="82" t="n">
         <f>IF(ISNUMBER(F79),F79*$D$45,"")</f>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="I79" s="76" t="n">
         <f>IF(AND(ISNUMBER(H79),ISNUMBER($D$55)),H79*$D$55,"")</f>
-        <v>97413.48128864325</v>
+        <v>97552.68044823447</v>
       </c>
       <c r="J79" s="82" t="n">
         <f>IF(D79="","",E79-E78)</f>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G80" s="79" t="n">
         <f>IF(AND(ISNUMBER(F80),ISNUMBER($D$55)),F80*$D$55,"")</f>
-        <v>0.00010359695422200438</v>
+        <v>0.00010374498926574933</v>
       </c>
       <c r="H80" s="82" t="n">
         <f>IF(ISNUMBER(F80),F80*$D$45,"")</f>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="I80" s="76" t="n">
         <f>IF(AND(ISNUMBER(H80),ISNUMBER($D$55)),H80*$D$55,"")</f>
-        <v>103596.95422200438</v>
+        <v>103744.98926574933</v>
       </c>
       <c r="J80" s="82" t="n">
         <f>IF(D80="","",E80-E79)</f>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="G81" s="79" t="n">
         <f>IF(AND(ISNUMBER(F81),ISNUMBER($D$55)),F81*$D$55,"")</f>
-        <v>0.00011038842988900364</v>
+        <v>0.00011054616962344156</v>
       </c>
       <c r="H81" s="82" t="n">
         <f>IF(ISNUMBER(F81),F81*$D$45,"")</f>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="I81" s="76" t="n">
         <f>IF(AND(ISNUMBER(H81),ISNUMBER($D$55)),H81*$D$55,"")</f>
-        <v>110388.42988900364</v>
+        <v>110546.16962344156</v>
       </c>
       <c r="J81" s="82" t="n">
         <f>IF(D81="","",E81-E80)</f>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G82" s="79" t="n">
         <f>IF(AND(ISNUMBER(F82),ISNUMBER($D$55)),F82*$D$55,"")</f>
-        <v>0.00011787031235925834</v>
+        <v>0.00011803874334236371</v>
       </c>
       <c r="H82" s="82" t="n">
         <f>IF(ISNUMBER(F82),F82*$D$45,"")</f>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="I82" s="76" t="n">
         <f>IF(AND(ISNUMBER(H82),ISNUMBER($D$55)),H82*$D$55,"")</f>
-        <v>117870.31235925833</v>
+        <v>118038.74334236371</v>
       </c>
       <c r="J82" s="82" t="n">
         <f>IF(D82="","",E82-E81)</f>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G83" s="79" t="n">
         <f>IF(AND(ISNUMBER(F83),ISNUMBER($D$55)),F83*$D$55,"")</f>
-        <v>0.0001261394543678151</v>
+        <v>0.00012631970155544273</v>
       </c>
       <c r="H83" s="82" t="n">
         <f>IF(ISNUMBER(F83),F83*$D$45,"")</f>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I83" s="76" t="n">
         <f>IF(AND(ISNUMBER(H83),ISNUMBER($D$55)),H83*$D$55,"")</f>
-        <v>126139.4543678151</v>
+        <v>126319.70155544273</v>
       </c>
       <c r="J83" s="82" t="n">
         <f>IF(D83="","",E83-E82)</f>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="G84" s="79" t="n">
         <f>IF(AND(ISNUMBER(F84),ISNUMBER($D$55)),F84*$D$55,"")</f>
-        <v>0.00013531030755527108</v>
+        <v>0.00013550365944914203</v>
       </c>
       <c r="H84" s="82" t="n">
         <f>IF(ISNUMBER(F84),F84*$D$45,"")</f>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="I84" s="76" t="n">
         <f>IF(AND(ISNUMBER(H84),ISNUMBER($D$55)),H84*$D$55,"")</f>
-        <v>135310.30755527105</v>
+        <v>135503.65944914203</v>
       </c>
       <c r="J84" s="82" t="n">
         <f>IF(D84="","",E84-E83)</f>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G85" s="79" t="n">
         <f>IF(AND(ISNUMBER(F85),ISNUMBER($D$55)),F85*$D$55,"")</f>
-        <v>0.00014551890414723234</v>
+        <v>0.0001457268436325476</v>
       </c>
       <c r="H85" s="82" t="n">
         <f>IF(ISNUMBER(F85),F85*$D$45,"")</f>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I85" s="76" t="n">
         <f>IF(AND(ISNUMBER(H85),ISNUMBER($D$55)),H85*$D$55,"")</f>
-        <v>145518.90414723233</v>
+        <v>145726.8436325476</v>
       </c>
       <c r="J85" s="82" t="n">
         <f>IF(D85="","",E85-E84)</f>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="G86" s="79" t="n">
         <f>IF(AND(ISNUMBER(F86),ISNUMBER($D$55)),F86*$D$55,"")</f>
-        <v>0.00015692793065581737</v>
+        <v>0.00015715217308894582</v>
       </c>
       <c r="H86" s="82" t="n">
         <f>IF(ISNUMBER(F86),F86*$D$45,"")</f>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="I86" s="76" t="n">
         <f>IF(AND(ISNUMBER(H86),ISNUMBER($D$55)),H86*$D$55,"")</f>
-        <v>156927.93065581736</v>
+        <v>157152.17308894583</v>
       </c>
       <c r="J86" s="82" t="n">
         <f>IF(D86="","",E86-E85)</f>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G87" s="79" t="n">
         <f>IF(AND(ISNUMBER(F87),ISNUMBER($D$55)),F87*$D$55,"")</f>
-        <v>0.0001697332497973318</v>
+        <v>0.00016997579041300355</v>
       </c>
       <c r="H87" s="82" t="n">
         <f>IF(ISNUMBER(F87),F87*$D$45,"")</f>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="I87" s="76" t="n">
         <f>IF(AND(ISNUMBER(H87),ISNUMBER($D$55)),H87*$D$55,"")</f>
-        <v>169733.2497973318</v>
+        <v>169975.79041300353</v>
       </c>
       <c r="J87" s="82" t="n">
         <f>IF(D87="","",E87-E86)</f>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G88" s="79" t="n">
         <f>IF(AND(ISNUMBER(F88),ISNUMBER($D$55)),F88*$D$55,"")</f>
-        <v>0.00018417236306134092</v>
+        <v>0.00018443553647244307</v>
       </c>
       <c r="H88" s="82" t="n">
         <f>IF(ISNUMBER(F88),F88*$D$45,"")</f>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="I88" s="76" t="n">
         <f>IF(AND(ISNUMBER(H88),ISNUMBER($D$55)),H88*$D$55,"")</f>
-        <v>184172.3630613409</v>
+        <v>184435.53647244305</v>
       </c>
       <c r="J88" s="82" t="n">
         <f>IF(D88="","",E88-E87)</f>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="G89" s="79" t="n">
         <f>IF(AND(ISNUMBER(F89),ISNUMBER($D$55)),F89*$D$55,"")</f>
-        <v>0.00020053550306868128</v>
+        <v>0.0002008220586164976</v>
       </c>
       <c r="H89" s="82" t="n">
         <f>IF(ISNUMBER(F89),F89*$D$45,"")</f>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I89" s="76" t="n">
         <f>IF(AND(ISNUMBER(H89),ISNUMBER($D$55)),H89*$D$55,"")</f>
-        <v>200535.50306868128</v>
+        <v>200822.0586164976</v>
       </c>
       <c r="J89" s="82" t="n">
         <f>IF(D89="","",E89-E88)</f>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G90" s="79" t="n">
         <f>IF(AND(ISNUMBER(F90),ISNUMBER($D$55)),F90*$D$55,"")</f>
-        <v>0.00021918033289944713</v>
+        <v>0.00021949353100852737</v>
       </c>
       <c r="H90" s="82" t="n">
         <f>IF(ISNUMBER(F90),F90*$D$45,"")</f>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="I90" s="76" t="n">
         <f>IF(AND(ISNUMBER(H90),ISNUMBER($D$55)),H90*$D$55,"")</f>
-        <v>219180.33289944712</v>
+        <v>219493.53100852738</v>
       </c>
       <c r="J90" s="82" t="n">
         <f>IF(D90="","",E90-E89)</f>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="G91" s="79" t="n">
         <f>IF(AND(ISNUMBER(F91),ISNUMBER($D$55)),F91*$D$55,"")</f>
-        <v>0.00024055165787603718</v>
+        <v>0.00024089539457625224</v>
       </c>
       <c r="H91" s="82" t="n">
         <f>IF(ISNUMBER(F91),F91*$D$45,"")</f>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I91" s="76" t="n">
         <f>IF(AND(ISNUMBER(H91),ISNUMBER($D$55)),H91*$D$55,"")</f>
-        <v>240551.65787603718</v>
+        <v>240895.39457625223</v>
       </c>
       <c r="J91" s="82" t="n">
         <f>IF(D91="","",E91-E90)</f>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G92" s="79" t="n">
         <f>IF(AND(ISNUMBER(F92),ISNUMBER($D$55)),F92*$D$55,"")</f>
-        <v>0.00026520820280833107</v>
+        <v>0.00026558717252031814</v>
       </c>
       <c r="H92" s="82" t="n">
         <f>IF(ISNUMBER(F92),F92*$D$45,"")</f>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="I92" s="76" t="n">
         <f>IF(AND(ISNUMBER(H92),ISNUMBER($D$55)),H92*$D$55,"")</f>
-        <v>265208.20280833106</v>
+        <v>265587.1725203181</v>
       </c>
       <c r="J92" s="82" t="n">
         <f>IF(D92="","",E92-E91)</f>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="G93" s="79" t="n">
         <f>IF(AND(ISNUMBER(F93),ISNUMBER($D$55)),F93*$D$55,"")</f>
-        <v>0.0002938595044967658</v>
+        <v>0.00029427941553497865</v>
       </c>
       <c r="H93" s="82" t="n">
         <f>IF(ISNUMBER(F93),F93*$D$45,"")</f>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="I93" s="76" t="n">
         <f>IF(AND(ISNUMBER(H93),ISNUMBER($D$55)),H93*$D$55,"")</f>
-        <v>293859.5044967658</v>
+        <v>294279.4155349787</v>
       </c>
       <c r="J93" s="82" t="n">
         <f>IF(D93="","",E93-E92)</f>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G94" s="79" t="n">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER($D$55)),F94*$D$55,"")</f>
-        <v>0.00032741753433127295</v>
+        <v>0.0003278853981732323</v>
       </c>
       <c r="H94" s="82" t="n">
         <f>IF(ISNUMBER(F94),F94*$D$45,"")</f>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="I94" s="76" t="n">
         <f>IF(AND(ISNUMBER(H94),ISNUMBER($D$55)),H94*$D$55,"")</f>
-        <v>327417.534331273</v>
+        <v>327885.39817323233</v>
       </c>
       <c r="J94" s="82" t="n">
         <f>IF(D94="","",E94-E93)</f>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G95" s="79" t="n">
         <f>IF(AND(ISNUMBER(F95),ISNUMBER($D$55)),F95*$D$55,"")</f>
-        <v>0.0003670701768973441</v>
+        <v>0.00036759470245026745</v>
       </c>
       <c r="H95" s="82" t="n">
         <f>IF(ISNUMBER(F95),F95*$D$45,"")</f>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="I95" s="76" t="n">
         <f>IF(AND(ISNUMBER(H95),ISNUMBER($D$55)),H95*$D$55,"")</f>
-        <v>367070.17689734406</v>
+        <v>367594.7024502674</v>
       </c>
       <c r="J95" s="82" t="n">
         <f>IF(D95="","",E95-E94)</f>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="G96" s="79" t="n">
         <f>IF(AND(ISNUMBER(F96),ISNUMBER($D$55)),F96*$D$55,"")</f>
-        <v>0.0004143878168880175</v>
+        <v>0.0004149799570629973</v>
       </c>
       <c r="H96" s="82" t="n">
         <f>IF(ISNUMBER(F96),F96*$D$45,"")</f>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="I96" s="76" t="n">
         <f>IF(AND(ISNUMBER(H96),ISNUMBER($D$55)),H96*$D$55,"")</f>
-        <v>414387.8168880175</v>
+        <v>414979.95706299733</v>
       </c>
       <c r="J96" s="82" t="n">
         <f>IF(D96="","",E96-E95)</f>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="G97" s="79" t="n">
         <f>IF(AND(ISNUMBER(F97),ISNUMBER($D$55)),F97*$D$55,"")</f>
-        <v>0.00047148124943703336</v>
+        <v>0.00047215497336945483</v>
       </c>
       <c r="H97" s="82" t="n">
         <f>IF(ISNUMBER(F97),F97*$D$45,"")</f>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I97" s="76" t="n">
         <f>IF(AND(ISNUMBER(H97),ISNUMBER($D$55)),H97*$D$55,"")</f>
-        <v>471481.2494370333</v>
+        <v>472154.97336945485</v>
       </c>
       <c r="J97" s="82" t="n">
         <f>IF(D97="","",E97-E96)</f>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G98" s="79" t="n">
         <f>IF(AND(ISNUMBER(F98),ISNUMBER($D$55)),F98*$D$55,"")</f>
-        <v>0.0005412412302210843</v>
+        <v>0.0005420146377965681</v>
       </c>
       <c r="H98" s="82" t="n">
         <f>IF(ISNUMBER(F98),F98*$D$45,"")</f>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="I98" s="76" t="n">
         <f>IF(AND(ISNUMBER(H98),ISNUMBER($D$55)),H98*$D$55,"")</f>
-        <v>541241.2302210842</v>
+        <v>542014.6377965681</v>
       </c>
       <c r="J98" s="82" t="n">
         <f>IF(D98="","",E98-E97)</f>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="G99" s="79" t="n">
         <f>IF(AND(ISNUMBER(F99),ISNUMBER($D$55)),F99*$D$55,"")</f>
-        <v>0.0006277117226232695</v>
+        <v>0.0006286086923557833</v>
       </c>
       <c r="H99" s="82" t="n">
         <f>IF(ISNUMBER(F99),F99*$D$45,"")</f>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="I99" s="76" t="n">
         <f>IF(AND(ISNUMBER(H99),ISNUMBER($D$55)),H99*$D$55,"")</f>
-        <v>627711.7226232694</v>
+        <v>628608.6923557833</v>
       </c>
       <c r="J99" s="82" t="n">
         <f>IF(D99="","",E99-E98)</f>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G100" s="79" t="n">
         <f>IF(AND(ISNUMBER(F100),ISNUMBER($D$55)),F100*$D$55,"")</f>
-        <v>0.0007366894522453653</v>
+        <v>0.0007377421458897739</v>
       </c>
       <c r="H100" s="82" t="n">
         <f>IF(ISNUMBER(F100),F100*$D$45,"")</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I100" s="76" t="n">
         <f>IF(AND(ISNUMBER(H100),ISNUMBER($D$55)),H100*$D$55,"")</f>
-        <v>736689.4522453652</v>
+        <v>737742.1458897738</v>
       </c>
       <c r="J100" s="82" t="n">
         <f>IF(D100="","",E100-E99)</f>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="G101" s="79" t="n">
         <f>IF(AND(ISNUMBER(F101),ISNUMBER($D$55)),F101*$D$55,"")</f>
-        <v>0.00087672133159779</v>
+        <v>0.000877974124034111</v>
       </c>
       <c r="H101" s="82" t="n">
         <f>IF(ISNUMBER(F101),F101*$D$45,"")</f>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="I101" s="76" t="n">
         <f>IF(AND(ISNUMBER(H101),ISNUMBER($D$55)),H101*$D$55,"")</f>
-        <v>876721.33159779</v>
+        <v>877974.124034111</v>
       </c>
       <c r="J101" s="82" t="n">
         <f>IF(D101="","",E101-E100)</f>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="G102" s="79" t="n">
         <f>IF(AND(ISNUMBER(F102),ISNUMBER($D$55)),F102*$D$55,"")</f>
-        <v>0.0010608328112333267</v>
+        <v>0.001062348690081275</v>
       </c>
       <c r="H102" s="82" t="n">
         <f>IF(ISNUMBER(F102),F102*$D$45,"")</f>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I102" s="76" t="n">
         <f>IF(AND(ISNUMBER(H102),ISNUMBER($D$55)),H102*$D$55,"")</f>
-        <v>1060832.8112333266</v>
+        <v>1062348.6900812748</v>
       </c>
       <c r="J102" s="82" t="n">
         <f>IF(D102="","",E102-E101)</f>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="G103" s="79" t="n">
         <f>IF(AND(ISNUMBER(F103),ISNUMBER($D$55)),F103*$D$55,"")</f>
-        <v>0.0013096701373250955</v>
+        <v>0.001311541592692933</v>
       </c>
       <c r="H103" s="82" t="n">
         <f>IF(ISNUMBER(F103),F103*$D$45,"")</f>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I103" s="76" t="n">
         <f>IF(AND(ISNUMBER(H103),ISNUMBER($D$55)),H103*$D$55,"")</f>
-        <v>1309670.1373250955</v>
+        <v>1311541.592692933</v>
       </c>
       <c r="J103" s="82" t="n">
         <f>IF(D103="","",E103-E102)</f>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G104" s="79" t="n">
         <f>IF(AND(ISNUMBER(F104),ISNUMBER($D$55)),F104*$D$55,"")</f>
-        <v>0.0016575512675520744</v>
+        <v>0.0016599198282519938</v>
       </c>
       <c r="H104" s="82" t="n">
         <f>IF(ISNUMBER(F104),F104*$D$45,"")</f>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="I104" s="76" t="n">
         <f>IF(AND(ISNUMBER(H104),ISNUMBER($D$55)),H104*$D$55,"")</f>
-        <v>1657551.2675520745</v>
+        <v>1659919.8282519937</v>
       </c>
       <c r="J104" s="82" t="n">
         <f>IF(D104="","",E104-E103)</f>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G105" s="79" t="n">
         <f>IF(AND(ISNUMBER(F105),ISNUMBER($D$55)),F105*$D$55,"")</f>
-        <v>0.002164964920884344</v>
+        <v>0.00216805855118628</v>
       </c>
       <c r="H105" s="82" t="n">
         <f>IF(ISNUMBER(F105),F105*$D$45,"")</f>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="I105" s="76" t="n">
         <f>IF(AND(ISNUMBER(H105),ISNUMBER($D$55)),H105*$D$55,"")</f>
-        <v>2164964.9208843443</v>
+        <v>2168058.55118628</v>
       </c>
       <c r="J105" s="82" t="n">
         <f>IF(D105="","",E105-E104)</f>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="G106" s="79" t="n">
         <f>IF(AND(ISNUMBER(F106),ISNUMBER($D$55)),F106*$D$55,"")</f>
-        <v>0.002946757808981472</v>
+        <v>0.0029509685835591064</v>
       </c>
       <c r="H106" s="82" t="n">
         <f>IF(ISNUMBER(F106),F106*$D$45,"")</f>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="I106" s="76" t="n">
         <f>IF(AND(ISNUMBER(H106),ISNUMBER($D$55)),H106*$D$55,"")</f>
-        <v>2946757.808981472</v>
+        <v>2950968.5835591066</v>
       </c>
       <c r="J106" s="82" t="n">
         <f>IF(D106="","",E106-E105)</f>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G107" s="79" t="n">
         <f>IF(AND(ISNUMBER(F107),ISNUMBER($D$55)),F107*$D$55,"")</f>
-        <v>0.004243331244933326</v>
+        <v>0.00424939476032512</v>
       </c>
       <c r="H107" s="82" t="n">
         <f>IF(ISNUMBER(F107),F107*$D$45,"")</f>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I107" s="76" t="n">
         <f>IF(AND(ISNUMBER(H107),ISNUMBER($D$55)),H107*$D$55,"")</f>
-        <v>4243331.244933326</v>
+        <v>4249394.76032512</v>
       </c>
       <c r="J107" s="82" t="n">
         <f>IF(D107="","",E107-E106)</f>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G108" s="79" t="n">
         <f>IF(AND(ISNUMBER(F108),ISNUMBER($D$55)),F108*$D$55,"")</f>
-        <v>0.006630205070208336</v>
+        <v>0.0066396793130080135</v>
       </c>
       <c r="H108" s="82" t="n">
         <f>IF(ISNUMBER(F108),F108*$D$45,"")</f>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="I108" s="76" t="n">
         <f>IF(AND(ISNUMBER(H108),ISNUMBER($D$55)),H108*$D$55,"")</f>
-        <v>6630205.070208336</v>
+        <v>6639679.313008014</v>
       </c>
       <c r="J108" s="82" t="n">
         <f>IF(D108="","",E108-E107)</f>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G109" s="79" t="n">
         <f>IF(AND(ISNUMBER(F109),ISNUMBER($D$55)),F109*$D$55,"")</f>
-        <v>0.011787031235925971</v>
+        <v>0.011803874334236509</v>
       </c>
       <c r="H109" s="82" t="n">
         <f>IF(ISNUMBER(F109),F109*$D$45,"")</f>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="I109" s="76" t="n">
         <f>IF(AND(ISNUMBER(H109),ISNUMBER($D$55)),H109*$D$55,"")</f>
-        <v>11787031.23592597</v>
+        <v>11803874.334236508</v>
       </c>
       <c r="J109" s="82" t="n">
         <f>IF(D109="","",E109-E108)</f>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G110" s="79" t="n">
         <f>IF(AND(ISNUMBER(F110),ISNUMBER($D$55)),F110*$D$55,"")</f>
-        <v>0.026520820280833045</v>
+        <v>0.026558717252031752</v>
       </c>
       <c r="H110" s="82" t="n">
         <f>IF(ISNUMBER(F110),F110*$D$45,"")</f>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I110" s="76" t="n">
         <f>IF(AND(ISNUMBER(H110),ISNUMBER($D$55)),H110*$D$55,"")</f>
-        <v>26520820.280833043</v>
+        <v>26558717.252031755</v>
       </c>
       <c r="J110" s="82" t="n">
         <f>IF(D110="","",E110-E109)</f>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="G111" s="79" t="n">
         <f>IF(AND(ISNUMBER(F111),ISNUMBER($D$55)),F111*$D$55,"")</f>
-        <v>0.10608328112333688</v>
+        <v>0.10623486900813173</v>
       </c>
       <c r="H111" s="82" t="n">
         <f>IF(ISNUMBER(F111),F111*$D$45,"")</f>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I111" s="76" t="n">
         <f>IF(AND(ISNUMBER(H111),ISNUMBER($D$55)),H111*$D$55,"")</f>
-        <v>106083281.12333688</v>
+        <v>106234869.00813173</v>
       </c>
       <c r="J111" s="82" t="n">
         <f>IF(D111="","",E111-E110)</f>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G118" s="78" t="n">
         <f>IF(AND(ISNUMBER(F118),ISNUMBER($D$55)),F118*$D$55,"")</f>
-        <v>0.00006630205070208274</v>
+        <v>0.00006639679313007951</v>
       </c>
       <c r="H118" s="81" t="n">
         <f>IF(ISNUMBER(F118),F118*$D$45,"")</f>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I118" s="75" t="n">
         <f>IF(AND(ISNUMBER(H118),ISNUMBER($D$55)),H118*$D$55,"")</f>
-        <v>66302.05070208274</v>
+        <v>66396.79313007952</v>
       </c>
       <c r="J118" s="72" t="n">
         <f>IF(H$118&gt;0,1-H118/H$118,"")</f>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G119" s="79" t="n">
         <f>IF(AND(ISNUMBER(F119),ISNUMBER($D$55)),F119*$D$55,"")</f>
-        <v>0.000029467578089814538</v>
+        <v>0.000029509685835590883</v>
       </c>
       <c r="H119" s="82" t="n">
         <f>IF(ISNUMBER(F119),F119*$D$45,"")</f>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="I119" s="76" t="n">
         <f>IF(AND(ISNUMBER(H119),ISNUMBER($D$55)),H119*$D$55,"")</f>
-        <v>29467.578089814542</v>
+        <v>29509.685835590884</v>
       </c>
       <c r="J119" s="73" t="n">
         <f>IF(H$118&gt;0,1-H119/H$118,"")</f>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G120" s="79" t="n">
         <f>IF(AND(ISNUMBER(F120),ISNUMBER($D$55)),F120*$D$55,"")</f>
-        <v>0.000016575512675520685</v>
+        <v>0.000016599198282519877</v>
       </c>
       <c r="H120" s="82" t="n">
         <f>IF(ISNUMBER(F120),F120*$D$45,"")</f>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="I120" s="76" t="n">
         <f>IF(AND(ISNUMBER(H120),ISNUMBER($D$55)),H120*$D$55,"")</f>
-        <v>16575.512675520684</v>
+        <v>16599.19828251988</v>
       </c>
       <c r="J120" s="73" t="n">
         <f>IF(H$118&gt;0,1-H120/H$118,"")</f>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G121" s="79" t="n">
         <f>IF(AND(ISNUMBER(F121),ISNUMBER($D$55)),F121*$D$55,"")</f>
-        <v>0.000010608328112333238</v>
+        <v>0.000010623486900812722</v>
       </c>
       <c r="H121" s="82" t="n">
         <f>IF(ISNUMBER(F121),F121*$D$45,"")</f>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I121" s="76" t="n">
         <f>IF(AND(ISNUMBER(H121),ISNUMBER($D$55)),H121*$D$55,"")</f>
-        <v>10608.328112333238</v>
+        <v>10623.48690081272</v>
       </c>
       <c r="J121" s="73" t="n">
         <f>IF(H$118&gt;0,1-H121/H$118,"")</f>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G122" s="79" t="n">
         <f>IF(AND(ISNUMBER(F122),ISNUMBER($D$55)),F122*$D$55,"")</f>
-        <v>0.000007366894522453637</v>
+        <v>0.000007377421458897723</v>
       </c>
       <c r="H122" s="82" t="n">
         <f>IF(ISNUMBER(F122),F122*$D$45,"")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="I122" s="76" t="n">
         <f>IF(AND(ISNUMBER(H122),ISNUMBER($D$55)),H122*$D$55,"")</f>
-        <v>7366.894522453637</v>
+        <v>7377.421458897724</v>
       </c>
       <c r="J122" s="73" t="n">
         <f>IF(H$118&gt;0,1-H122/H$118,"")</f>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="G123" s="79" t="n">
         <f>IF(AND(ISNUMBER(F123),ISNUMBER($D$55)),F123*$D$55,"")</f>
-        <v>0.000005412412302210836</v>
+        <v>0.000005420146377965674</v>
       </c>
       <c r="H123" s="82" t="n">
         <f>IF(ISNUMBER(F123),F123*$D$45,"")</f>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="I123" s="76" t="n">
         <f>IF(AND(ISNUMBER(H123),ISNUMBER($D$55)),H123*$D$55,"")</f>
-        <v>5412.412302210836</v>
+        <v>5420.146377965674</v>
       </c>
       <c r="J123" s="73" t="n">
         <f>IF(H$118&gt;0,1-H123/H$118,"")</f>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G124" s="79" t="n">
         <f>IF(AND(ISNUMBER(F124),ISNUMBER($D$55)),F124*$D$55,"")</f>
-        <v>0.000004143878168880171</v>
+        <v>0.000004149799570629969</v>
       </c>
       <c r="H124" s="82" t="n">
         <f>IF(ISNUMBER(F124),F124*$D$45,"")</f>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I124" s="76" t="n">
         <f>IF(AND(ISNUMBER(H124),ISNUMBER($D$55)),H124*$D$55,"")</f>
-        <v>4143.878168880171</v>
+        <v>4149.79957062997</v>
       </c>
       <c r="J124" s="73" t="n">
         <f>IF(H$118&gt;0,1-H124/H$118,"")</f>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G125" s="79" t="n">
         <f>IF(AND(ISNUMBER(F125),ISNUMBER($D$55)),F125*$D$55,"")</f>
-        <v>0.0000032741753433127275</v>
+        <v>0.000003278853981732321</v>
       </c>
       <c r="H125" s="82" t="n">
         <f>IF(ISNUMBER(F125),F125*$D$45,"")</f>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I125" s="76" t="n">
         <f>IF(AND(ISNUMBER(H125),ISNUMBER($D$55)),H125*$D$55,"")</f>
-        <v>3274.1753433127274</v>
+        <v>3278.8539817323212</v>
       </c>
       <c r="J125" s="73" t="n">
         <f>IF(H$118&gt;0,1-H125/H$118,"")</f>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="G126" s="80" t="n">
         <f>IF(AND(ISNUMBER(F126),ISNUMBER($D$55)),F126*$D$55,"")</f>
-        <v>0.0000026520820280833095</v>
+        <v>0.0000026558717252031804</v>
       </c>
       <c r="H126" s="83" t="n">
         <f>IF(ISNUMBER(F126),F126*$D$45,"")</f>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="I126" s="77" t="n">
         <f>IF(AND(ISNUMBER(H126),ISNUMBER($D$55)),H126*$D$55,"")</f>
-        <v>2652.0820280833095</v>
+        <v>2655.87172520318</v>
       </c>
       <c r="J126" s="74" t="n">
         <f>IF(H$118&gt;0,1-H126/H$118,"")</f>
@@ -4966,6 +4966,9 @@
     <x:col min="33" max="33" width="44" hidden="0" customWidth="1"/>
     <x:col min="34" max="34" width="20" hidden="0" customWidth="1"/>
     <x:col min="35" max="35" width="20" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="20" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="44" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
@@ -5004,6 +5007,9 @@
       <x:c r="AG1" s="5"/>
       <x:c r="AH1" s="5"/>
       <x:c r="AI1" s="5"/>
+      <x:c r="AJ1" s="5"/>
+      <x:c r="AK1" s="5"/>
+      <x:c r="AL1" s="5"/>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="5"/>
@@ -5043,6 +5049,9 @@
       <x:c r="AG2" s="7"/>
       <x:c r="AH2" s="7"/>
       <x:c r="AI2" s="7"/>
+      <x:c r="AJ2" s="7"/>
+      <x:c r="AK2" s="7"/>
+      <x:c r="AL2" s="7"/>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -5082,6 +5091,9 @@
       <x:c r="AG3" s="5"/>
       <x:c r="AH3" s="5"/>
       <x:c r="AI3" s="5"/>
+      <x:c r="AJ3" s="5"/>
+      <x:c r="AK3" s="5"/>
+      <x:c r="AL3" s="5"/>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="5"/>
@@ -5119,6 +5131,9 @@
       <x:c r="AG4" s="5"/>
       <x:c r="AH4" s="5"/>
       <x:c r="AI4" s="5"/>
+      <x:c r="AJ4" s="5"/>
+      <x:c r="AK4" s="5"/>
+      <x:c r="AL4" s="5"/>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
       <x:c r="A5" s="5"/>
@@ -5156,6 +5171,9 @@
       <x:c r="AG5" s="5"/>
       <x:c r="AH5" s="5"/>
       <x:c r="AI5" s="5"/>
+      <x:c r="AJ5" s="5"/>
+      <x:c r="AK5" s="5"/>
+      <x:c r="AL5" s="5"/>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
       <x:c r="A6" s="5"/>
@@ -5164,7 +5182,7 @@
         <x:v>USDT / USD</x:v>
       </x:c>
       <x:c r="D6" s="5" t="n">
-        <x:v>0.99917</x:v>
+        <x:v>0.999604</x:v>
       </x:c>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5"/>
@@ -5197,6 +5215,9 @@
       <x:c r="AG6" s="5"/>
       <x:c r="AH6" s="5"/>
       <x:c r="AI6" s="5"/>
+      <x:c r="AJ6" s="5"/>
+      <x:c r="AK6" s="5"/>
+      <x:c r="AL6" s="5"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
       <x:c r="A7" s="5"/>
@@ -5205,7 +5226,7 @@
         <x:v>快照时间 / UTC</x:v>
       </x:c>
       <x:c r="D7" s="6" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
       <x:c r="F7" s="5"/>
@@ -5238,6 +5259,9 @@
       <x:c r="AG7" s="5"/>
       <x:c r="AH7" s="5"/>
       <x:c r="AI7" s="5"/>
+      <x:c r="AJ7" s="5"/>
+      <x:c r="AK7" s="5"/>
+      <x:c r="AL7" s="5"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
       <x:c r="A8" s="5"/>
@@ -5279,6 +5303,9 @@
       <x:c r="AG8" s="5"/>
       <x:c r="AH8" s="5"/>
       <x:c r="AI8" s="5"/>
+      <x:c r="AJ8" s="5"/>
+      <x:c r="AK8" s="5"/>
+      <x:c r="AL8" s="5"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
       <x:c r="A9" s="5"/>
@@ -5316,6 +5343,9 @@
       <x:c r="AG9" s="5"/>
       <x:c r="AH9" s="5"/>
       <x:c r="AI9" s="5"/>
+      <x:c r="AJ9" s="5"/>
+      <x:c r="AK9" s="5"/>
+      <x:c r="AL9" s="5"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
       <x:c r="A10" s="5"/>
@@ -5357,6 +5387,9 @@
       <x:c r="AG10" s="5"/>
       <x:c r="AH10" s="5"/>
       <x:c r="AI10" s="5"/>
+      <x:c r="AJ10" s="5"/>
+      <x:c r="AK10" s="5"/>
+      <x:c r="AL10" s="5"/>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="5"/>
@@ -5365,7 +5398,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>损耗按目标加缓冲的 FDV × 双边费率。非 Pons 的补回按目标持仓洗一轮、小单固定价及现有外盘曲线差额估算；Pons 按原批准的 Quote 预算承担手续费，补回为 0。非逐笔模拟。</x:v>
+        <x:v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
@@ -5398,6 +5431,9 @@
       <x:c r="AG11" s="5"/>
       <x:c r="AH11" s="5"/>
       <x:c r="AI11" s="5"/>
+      <x:c r="AJ11" s="5"/>
+      <x:c r="AK11" s="5"/>
+      <x:c r="AL11" s="5"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
       <x:c r="A12" s="5"/>
@@ -5435,6 +5471,9 @@
       <x:c r="AG12" s="5"/>
       <x:c r="AH12" s="5"/>
       <x:c r="AI12" s="5"/>
+      <x:c r="AJ12" s="5"/>
+      <x:c r="AK12" s="5"/>
+      <x:c r="AL12" s="5"/>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
       <x:c r="A13" s="5"/>
@@ -5538,6 +5577,15 @@
       <x:c r="AI13" s="16" t="str">
         <x:v>单地址 Gas</x:v>
       </x:c>
+      <x:c r="AJ13" s="16" t="str">
+        <x:v>外盘扣费资产</x:v>
+      </x:c>
+      <x:c r="AK13" s="16" t="str">
+        <x:v>外盘扣费机制</x:v>
+      </x:c>
+      <x:c r="AL13" s="16" t="str">
+        <x:v>扣费机制来源</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" s="5"/>
@@ -5556,13 +5604,13 @@
       </x:c>
       <x:c r="G14" s="35" t="str"/>
       <x:c r="H14" s="20" t="n">
-        <x:v>105.97796170821782</x:v>
+        <x:v>108.53297905970763</x:v>
       </x:c>
       <x:c r="I14" s="20" t="n">
-        <x:v>105.97796170821782</x:v>
+        <x:v>108.53297905970763</x:v>
       </x:c>
       <x:c r="J14" s="23" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K14" s="35" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -5636,6 +5684,15 @@
       </x:c>
       <x:c r="AI14" s="17" t="n">
         <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AJ14" s="26" t="str">
+        <x:v>quote</x:v>
+      </x:c>
+      <x:c r="AK14" s="35" t="str">
+        <x:v>买卖两侧均以 Quote 收取，不直接扣除 Meme TOKEN</x:v>
+      </x:c>
+      <x:c r="AL14" s="35" t="str">
+        <x:v>https://github.com/pump-fun/pump-public-docs/blob/main/docs/instructions/BUY.md</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
@@ -5655,13 +5712,13 @@
       </x:c>
       <x:c r="G15" s="36" t="str"/>
       <x:c r="H15" s="21" t="n">
-        <x:v>1.000830689472262</x:v>
+        <x:v>1.0003961568781237</x:v>
       </x:c>
       <x:c r="I15" s="21" t="n">
-        <x:v>105.97796170821782</x:v>
+        <x:v>108.53297905970763</x:v>
       </x:c>
       <x:c r="J15" s="24" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K15" s="36" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -5735,6 +5792,15 @@
       </x:c>
       <x:c r="AI15" s="18" t="n">
         <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AJ15" s="27" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK15" s="36" t="str">
+        <x:v>Raydium CPMM 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</x:v>
+      </x:c>
+      <x:c r="AL15" s="36" t="str">
+        <x:v>https://docs.raydium.io/raydium/build/developers-zh/cao-zuo-fang-fa/ru-he-she-zhi-cpmm-fei-yong</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -5754,13 +5820,13 @@
       </x:c>
       <x:c r="G16" s="36" t="str"/>
       <x:c r="H16" s="21" t="n">
-        <x:v>1.000830689472262</x:v>
+        <x:v>1.0003961568781237</x:v>
       </x:c>
       <x:c r="I16" s="21" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="J16" s="24" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K16" s="36" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -5834,6 +5900,15 @@
       </x:c>
       <x:c r="AI16" s="18" t="n">
         <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="AJ16" s="27" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK16" s="36" t="str">
+        <x:v>PancakeSwap 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</x:v>
+      </x:c>
+      <x:c r="AL16" s="36" t="str">
+        <x:v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
@@ -5853,13 +5928,13 @@
       </x:c>
       <x:c r="G17" s="36" t="str"/>
       <x:c r="H17" s="21" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="I17" s="21" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="J17" s="24" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K17" s="36" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -5933,6 +6008,15 @@
       </x:c>
       <x:c r="AI17" s="18" t="n">
         <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="AJ17" s="27" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK17" s="36" t="str">
+        <x:v>PancakeSwap 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</x:v>
+      </x:c>
+      <x:c r="AL17" s="36" t="str">
+        <x:v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
@@ -5952,13 +6036,13 @@
       </x:c>
       <x:c r="G18" s="36" t="str"/>
       <x:c r="H18" s="21" t="n">
-        <x:v>0.7527247615520882</x:v>
+        <x:v>0.7357363515952317</x:v>
       </x:c>
       <x:c r="I18" s="21" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="J18" s="24" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K18" s="36" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -6032,6 +6116,15 @@
       </x:c>
       <x:c r="AI18" s="18" t="n">
         <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="AJ18" s="27" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK18" s="36" t="str">
+        <x:v>PancakeSwap 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</x:v>
+      </x:c>
+      <x:c r="AL18" s="36" t="str">
+        <x:v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
@@ -6051,13 +6144,13 @@
       </x:c>
       <x:c r="G19" s="36" t="str"/>
       <x:c r="H19" s="21" t="n">
-        <x:v>88.8037070768738</x:v>
+        <x:v>91.08607008375316</x:v>
       </x:c>
       <x:c r="I19" s="21" t="n">
-        <x:v>88.8037070768738</x:v>
+        <x:v>91.08607008375316</x:v>
       </x:c>
       <x:c r="J19" s="24" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K19" s="36" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -6131,6 +6224,15 @@
       </x:c>
       <x:c r="AI19" s="18" t="n">
         <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AJ19" s="27" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK19" s="36" t="str">
+        <x:v>HyperSwap V2 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</x:v>
+      </x:c>
+      <x:c r="AL19" s="36" t="str">
+        <x:v>https://docs.hyperswap.pro/technical-protocol/protocol-overview/how</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
@@ -6150,13 +6252,13 @@
       </x:c>
       <x:c r="G20" s="36" t="str"/>
       <x:c r="H20" s="21" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="I20" s="21" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="J20" s="24" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K20" s="36" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -6230,6 +6332,15 @@
       </x:c>
       <x:c r="AI20" s="18" t="n">
         <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="AJ20" s="27" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK20" s="36" t="str">
+        <x:v>PancakeSwap LP 费从输入币扣取；外盘买税扣输出 TOKEN，卖税扣输入 TOKEN</x:v>
+      </x:c>
+      <x:c r="AL20" s="36" t="str">
+        <x:v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
@@ -6249,13 +6360,13 @@
       </x:c>
       <x:c r="G21" s="36" t="str"/>
       <x:c r="H21" s="21" t="n">
-        <x:v>1.000830689472262</x:v>
+        <x:v>1.0003961568781237</x:v>
       </x:c>
       <x:c r="I21" s="21" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="J21" s="24" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K21" s="36" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -6329,6 +6440,15 @@
       </x:c>
       <x:c r="AI21" s="18" t="n">
         <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="AJ21" s="27" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK21" s="36" t="str">
+        <x:v>PancakeSwap LP 费从输入币扣取；外盘买税扣输出 TOKEN，卖税扣输入 TOKEN</x:v>
+      </x:c>
+      <x:c r="AL21" s="36" t="str">
+        <x:v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
@@ -6348,13 +6468,13 @@
       </x:c>
       <x:c r="G22" s="37" t="str"/>
       <x:c r="H22" s="22" t="n">
-        <x:v>2505.389473262808</x:v>
+        <x:v>2580.0817123580937</x:v>
       </x:c>
       <x:c r="I22" s="22" t="n">
-        <x:v>2505.389473262808</x:v>
+        <x:v>2580.0817123580937</x:v>
       </x:c>
       <x:c r="J22" s="25" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K22" s="37" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
@@ -6428,6 +6548,15 @@
       </x:c>
       <x:c r="AI22" s="19" t="n">
         <x:v>0.005</x:v>
+      </x:c>
+      <x:c r="AJ22" s="28" t="str">
+        <x:v>output</x:v>
+      </x:c>
+      <x:c r="AK22" s="37" t="str">
+        <x:v>Pons V4 Hook 从输出币扣费；买入侧输出币为 Meme TOKEN，卖出侧输出币为 Quote</x:v>
+      </x:c>
+      <x:c r="AL22" s="37" t="str">
+        <x:v>https://docs.ponsfamily.com/v2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Ra4a3221c8ea9478b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rf51891fb9c854582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R1423d5dfc8cd496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Re3e8b4bf065b459b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6550,10 +6550,10 @@
         <x:v>0.005</x:v>
       </x:c>
       <x:c r="AJ22" s="28" t="str">
-        <x:v>output</x:v>
+        <x:v>quote</x:v>
       </x:c>
       <x:c r="AK22" s="37" t="str">
-        <x:v>Pons V4 Hook 从输出币扣费；买入侧输出币为 Meme TOKEN，卖出侧输出币为 Quote</x:v>
+        <x:v>Pons V2 手续费始终按 Quote leg 计收；Hook 暂存的 Meme 费用会在池内转换回 Quote</x:v>
       </x:c>
       <x:c r="AL22" s="37" t="str">
         <x:v>https://docs.ponsfamily.com/v2</x:v>

--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R1423d5dfc8cd496e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Re3e8b4bf065b459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R18477e5145584d7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R4910903c19954c88"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1121,7 +1121,7 @@
         <v>预算 95% 理论资金</v>
       </c>
       <c r="D22" s="65" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",$G$50/$J$51-$G$49,IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
+        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",($G$50/$J$51-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
         <v>71.23230102652082</v>
       </c>
       <c r="E22" s="3" t="str">
@@ -1681,8 +1681,8 @@
         <v>预算交换 TOKEN</v>
       </c>
       <c r="J51" s="49" t="n">
-        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$48)</f>
-        <v>49624060.15037605</v>
+        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)</f>
+        <v>50000000.00000009</v>
       </c>
       <c r="K51" s="49"/>
       <c r="L51" s="49"/>
@@ -1741,7 +1741,7 @@
         <v>当前控筹上限</v>
       </c>
       <c r="D54" s="58" t="n">
-        <f>IF($G$40="pons",MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$48)*$G$48/$D$45),IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
+        <f>IF($G$40="pons",1-$G$51/$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
         <v>1</v>
       </c>
       <c r="E54" s="49"/>
@@ -2317,7 +2317,7 @@
         <v>0.8</v>
       </c>
       <c r="D72" s="75" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
         <v>200000000</v>
       </c>
       <c r="E72" s="81" t="n">
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="87" t="n">
-        <f>IF(D72="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
+        <f>IF(D72="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C72-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
         <v>18.180001026520895</v>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>0.805</v>
       </c>
       <c r="D73" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
         <v>194999999.99999994</v>
       </c>
       <c r="E73" s="82" t="n">
@@ -2391,7 +2391,7 @@
         <v>0.45343846153846773</v>
       </c>
       <c r="L73" s="88" t="n">
-        <f>IF(D73="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
+        <f>IF(D73="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C73-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
         <v>18.633439488059363</v>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v>0.81</v>
       </c>
       <c r="D74" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
         <v>189999999.99999994</v>
       </c>
       <c r="E74" s="82" t="n">
@@ -2433,7 +2433,7 @@
         <v>0.47730364372469575</v>
       </c>
       <c r="L74" s="88" t="n">
-        <f>IF(D74="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
+        <f>IF(D74="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C74-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
         <v>19.11074313178406</v>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
         <v>0.8150000000000001</v>
       </c>
       <c r="D75" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
         <v>184999999.99999994</v>
       </c>
       <c r="E75" s="82" t="n">
@@ -2475,7 +2475,7 @@
         <v>0.5031038406827896</v>
       </c>
       <c r="L75" s="88" t="n">
-        <f>IF(D75="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
+        <f>IF(D75="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C75-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
         <v>19.61384697246685</v>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="D76" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
         <v>179999999.99999994</v>
       </c>
       <c r="E76" s="82" t="n">
@@ -2517,7 +2517,7 @@
         <v>0.5310540540540513</v>
       </c>
       <c r="L76" s="88" t="n">
-        <f>IF(D76="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
+        <f>IF(D76="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C76-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
         <v>20.1449010265209</v>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>0.8250000000000001</v>
       </c>
       <c r="D77" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
         <v>174999999.99999994</v>
       </c>
       <c r="E77" s="82" t="n">
@@ -2559,7 +2559,7 @@
         <v>0.5614000000000022</v>
       </c>
       <c r="L77" s="88" t="n">
-        <f>IF(D77="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
+        <f>IF(D77="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C77-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
         <v>20.7063010265209</v>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D78" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
         <v>169999999.99999994</v>
       </c>
       <c r="E78" s="82" t="n">
@@ -2601,7 +2601,7 @@
         <v>0.5944235294117655</v>
       </c>
       <c r="L78" s="88" t="n">
-        <f>IF(D78="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
+        <f>IF(D78="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C78-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
         <v>21.300724555932668</v>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
         <v>0.8350000000000001</v>
       </c>
       <c r="D79" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
         <v>164999999.9999999</v>
       </c>
       <c r="E79" s="82" t="n">
@@ -2643,7 +2643,7 @@
         <v>0.6304491978609661</v>
       </c>
       <c r="L79" s="88" t="n">
-        <f>IF(D79="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
+        <f>IF(D79="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C79-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
         <v>21.931173753793633</v>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>0.8400000000000001</v>
       </c>
       <c r="D80" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
         <v>159999999.9999999</v>
       </c>
       <c r="E80" s="82" t="n">
@@ -2685,7 +2685,7 @@
         <v>0.6698522727272725</v>
       </c>
       <c r="L80" s="88" t="n">
-        <f>IF(D80="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
+        <f>IF(D80="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C80-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
         <v>22.601026026520906</v>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
         <v>0.8450000000000001</v>
       </c>
       <c r="D81" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
         <v>154999999.9999999</v>
       </c>
       <c r="E81" s="82" t="n">
@@ -2727,7 +2727,7 @@
         <v>0.7130685483871</v>
       </c>
       <c r="L81" s="88" t="n">
-        <f>IF(D81="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
+        <f>IF(D81="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C81-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
         <v>23.314094574908005</v>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
         <v>0.8500000000000001</v>
       </c>
       <c r="D82" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
         <v>149999999.9999999</v>
       </c>
       <c r="E82" s="82" t="n">
@@ -2769,7 +2769,7 @@
         <v>0.7606064516129024</v>
       </c>
       <c r="L82" s="88" t="n">
-        <f>IF(D82="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
+        <f>IF(D82="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C82-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
         <v>24.074701026520906</v>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
         <v>0.8550000000000001</v>
       </c>
       <c r="D83" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
         <v>144999999.9999999</v>
       </c>
       <c r="E83" s="82" t="n">
@@ -2811,7 +2811,7 @@
         <v>0.8130620689655182</v>
       </c>
       <c r="L83" s="88" t="n">
-        <f>IF(D83="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
+        <f>IF(D83="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C83-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
         <v>24.887763095486427</v>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
         <v>0.8600000000000001</v>
       </c>
       <c r="D84" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
         <v>139999999.9999999</v>
       </c>
       <c r="E84" s="82" t="n">
@@ -2853,7 +2853,7 @@
         <v>0.8711379310344849</v>
       </c>
       <c r="L84" s="88" t="n">
-        <f>IF(D84="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
+        <f>IF(D84="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C84-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
         <v>25.75890102652091</v>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
         <v>0.865</v>
       </c>
       <c r="D85" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
         <v>135000000</v>
       </c>
       <c r="E85" s="82" t="n">
@@ -2895,7 +2895,7 @@
         <v>0.935666666666649</v>
       </c>
       <c r="L85" s="88" t="n">
-        <f>IF(D85="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
+        <f>IF(D85="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C85-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
         <v>26.694567693187558</v>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
         <v>0.8700000000000001</v>
       </c>
       <c r="D86" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
         <v>129999999.9999999</v>
       </c>
       <c r="E86" s="82" t="n">
@@ -2937,7 +2937,7 @@
         <v>1.0076410256410469</v>
       </c>
       <c r="L86" s="88" t="n">
-        <f>IF(D86="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
+        <f>IF(D86="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C86-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
         <v>27.702208718828608</v>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
         <v>0.875</v>
       </c>
       <c r="D87" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
         <v>125000000</v>
       </c>
       <c r="E87" s="82" t="n">
@@ -2979,7 +2979,7 @@
         <v>1.088252307692287</v>
       </c>
       <c r="L87" s="88" t="n">
-        <f>IF(D87="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
+        <f>IF(D87="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C87-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
         <v>28.790461026520894</v>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
         <v>0.88</v>
       </c>
       <c r="D88" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
         <v>120000000</v>
       </c>
       <c r="E88" s="82" t="n">
@@ -3021,7 +3021,7 @@
         <v>1.1789399999999983</v>
       </c>
       <c r="L88" s="88" t="n">
-        <f>IF(D88="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
+        <f>IF(D88="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C88-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
         <v>29.96940102652089</v>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
         <v>0.885</v>
       </c>
       <c r="D89" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
         <v>114999999.99999999</v>
       </c>
       <c r="E89" s="82" t="n">
@@ -3063,7 +3063,7 @@
         <v>1.2814565217391358</v>
       </c>
       <c r="L89" s="88" t="n">
-        <f>IF(D89="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
+        <f>IF(D89="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C89-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
         <v>31.25085754826003</v>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
         <v>0.89</v>
       </c>
       <c r="D90" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
         <v>109999999.99999999</v>
       </c>
       <c r="E90" s="82" t="n">
@@ -3105,7 +3105,7 @@
         <v>1.3979525691699612</v>
       </c>
       <c r="L90" s="88" t="n">
-        <f>IF(D90="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
+        <f>IF(D90="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C90-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
         <v>32.64881011742999</v>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
         <v>0.895</v>
       </c>
       <c r="D91" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
         <v>104999999.99999999</v>
       </c>
       <c r="E91" s="82" t="n">
@@ -3147,7 +3147,7 @@
         <v>1.5310909090909055</v>
       </c>
       <c r="L91" s="88" t="n">
-        <f>IF(D91="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
+        <f>IF(D91="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C91-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
         <v>34.179901026520895</v>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
         <v>0.9</v>
       </c>
       <c r="D92" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
         <v>99999999.99999999</v>
       </c>
       <c r="E92" s="82" t="n">
@@ -3189,7 +3189,7 @@
         <v>1.6842000000000068</v>
       </c>
       <c r="L92" s="88" t="n">
-        <f>IF(D92="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
+        <f>IF(D92="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C92-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
         <v>35.8641010265209</v>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
         <v>0.905</v>
       </c>
       <c r="D93" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
         <v>94999999.99999997</v>
       </c>
       <c r="E93" s="82" t="n">
@@ -3231,7 +3231,7 @@
         <v>1.8614842105263198</v>
       </c>
       <c r="L93" s="88" t="n">
-        <f>IF(D93="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
+        <f>IF(D93="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C93-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
         <v>37.72558523704722</v>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         <v>0.91</v>
       </c>
       <c r="D94" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
         <v>89999999.99999997</v>
       </c>
       <c r="E94" s="82" t="n">
@@ -3273,7 +3273,7 @@
         <v>2.0683157894736817</v>
       </c>
       <c r="L94" s="88" t="n">
-        <f>IF(D94="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
+        <f>IF(D94="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C94-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
         <v>39.7939010265209</v>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
         <v>0.915</v>
       </c>
       <c r="D95" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
         <v>84999999.99999997</v>
       </c>
       <c r="E95" s="82" t="n">
@@ -3315,7 +3315,7 @@
         <v>2.311647058823535</v>
       </c>
       <c r="L95" s="88" t="n">
-        <f>IF(D95="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
+        <f>IF(D95="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C95-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
         <v>42.10554808534444</v>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
         <v>0.92</v>
       </c>
       <c r="D96" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
         <v>79999999.99999996</v>
       </c>
       <c r="E96" s="82" t="n">
@@ -3357,7 +3357,7 @@
         <v>2.600602941176477</v>
       </c>
       <c r="L96" s="88" t="n">
-        <f>IF(D96="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
+        <f>IF(D96="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C96-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
         <v>44.706151026520914</v>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
         <v>0.925</v>
       </c>
       <c r="D97" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
         <v>74999999.99999996</v>
       </c>
       <c r="E97" s="82" t="n">
@@ -3399,7 +3399,7 @@
         <v>2.9473500000000046</v>
       </c>
       <c r="L97" s="88" t="n">
-        <f>IF(D97="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
+        <f>IF(D97="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C97-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
         <v>47.65350102652092</v>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>0.93</v>
       </c>
       <c r="D98" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
         <v>69999999.99999996</v>
       </c>
       <c r="E98" s="82" t="n">
@@ -3441,7 +3441,7 @@
         <v>3.3684000000000065</v>
       </c>
       <c r="L98" s="88" t="n">
-        <f>IF(D98="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
+        <f>IF(D98="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C98-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
         <v>51.02190102652092</v>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         <v>0.935</v>
       </c>
       <c r="D99" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
         <v>64999999.99999995</v>
       </c>
       <c r="E99" s="82" t="n">
@@ -3483,7 +3483,7 @@
         <v>3.886615384615392</v>
       </c>
       <c r="L99" s="88" t="n">
-        <f>IF(D99="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
+        <f>IF(D99="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C99-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
         <v>54.90851641113632</v>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="D100" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
         <v>59999999.99999994</v>
       </c>
       <c r="E100" s="82" t="n">
@@ -3525,7 +3525,7 @@
         <v>4.534384615384635</v>
       </c>
       <c r="L100" s="88" t="n">
-        <f>IF(D100="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
+        <f>IF(D100="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C100-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
         <v>59.44290102652096</v>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
         <v>0.9450000000000001</v>
       </c>
       <c r="D101" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
         <v>54999999.99999994</v>
       </c>
       <c r="E101" s="82" t="n">
@@ -3567,7 +3567,7 @@
         <v>5.3588181818181875</v>
       </c>
       <c r="L101" s="88" t="n">
-        <f>IF(D101="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
+        <f>IF(D101="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C101-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
         <v>64.80171920833914</v>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="D102" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
         <v>49999999.99999993</v>
       </c>
       <c r="E102" s="82" t="n">
@@ -3609,7 +3609,7 @@
         <v>6.430581818181839</v>
       </c>
       <c r="L102" s="88" t="n">
-        <f>IF(D102="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
+        <f>IF(D102="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C102-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
         <v>71.23230102652099</v>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
         <v>0.9550000000000001</v>
       </c>
       <c r="D103" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
         <v>44999999.999999925</v>
       </c>
       <c r="E103" s="82" t="n">
@@ -3651,7 +3651,7 @@
         <v>7.859600000000046</v>
       </c>
       <c r="L103" s="88" t="n">
-        <f>IF(D103="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
+        <f>IF(D103="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C103-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
         <v>79.09190102652103</v>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
         <v>0.9600000000000001</v>
       </c>
       <c r="D104" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
         <v>39999999.999999925</v>
       </c>
       <c r="E104" s="82" t="n">
@@ -3693,7 +3693,7 @@
         <v>9.824500000000025</v>
       </c>
       <c r="L104" s="88" t="n">
-        <f>IF(D104="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
+        <f>IF(D104="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C104-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
         <v>88.91640102652106</v>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
         <v>0.9650000000000001</v>
       </c>
       <c r="D105" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
         <v>34999999.99999992</v>
       </c>
       <c r="E105" s="82" t="n">
@@ -3735,7 +3735,7 @@
         <v>12.631500000000079</v>
       </c>
       <c r="L105" s="88" t="n">
-        <f>IF(D105="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
+        <f>IF(D105="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C105-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
         <v>101.54790102652113</v>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
         <v>0.9700000000000001</v>
       </c>
       <c r="D106" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
         <v>29999999.999999914</v>
       </c>
       <c r="E106" s="82" t="n">
@@ -3777,7 +3777,7 @@
         <v>16.842000000000095</v>
       </c>
       <c r="L106" s="88" t="n">
-        <f>IF(D106="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
+        <f>IF(D106="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C106-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
         <v>118.38990102652123</v>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
         <v>0.9750000000000001</v>
       </c>
       <c r="D107" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
         <v>24999999.99999991</v>
       </c>
       <c r="E107" s="82" t="n">
@@ -3819,7 +3819,7 @@
         <v>23.57880000000018</v>
       </c>
       <c r="L107" s="88" t="n">
-        <f>IF(D107="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
+        <f>IF(D107="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C107-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
         <v>141.96870102652142</v>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
         <v>0.9800000000000001</v>
       </c>
       <c r="D108" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
         <v>19999999.999999907</v>
       </c>
       <c r="E108" s="82" t="n">
@@ -3861,7 +3861,7 @@
         <v>35.368200000000314</v>
       </c>
       <c r="L108" s="88" t="n">
-        <f>IF(D108="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
+        <f>IF(D108="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C108-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
         <v>177.33690102652173</v>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
         <v>0.9850000000000001</v>
       </c>
       <c r="D109" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
         <v>14999999.999999903</v>
       </c>
       <c r="E109" s="82" t="n">
@@ -3903,7 +3903,7 @@
         <v>58.94700000000069</v>
       </c>
       <c r="L109" s="88" t="n">
-        <f>IF(D109="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
+        <f>IF(D109="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C109-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
         <v>236.28390102652241</v>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
         <v>0.99</v>
       </c>
       <c r="D110" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
         <v>10000000.00000001</v>
       </c>
       <c r="E110" s="82" t="n">
@@ -3945,7 +3945,7 @@
         <v>117.89399999999813</v>
       </c>
       <c r="L110" s="88" t="n">
-        <f>IF(D110="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
+        <f>IF(D110="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C110-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
         <v>354.17790102652054</v>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
         <v>0.9950000000000001</v>
       </c>
       <c r="D111" s="76" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
         <v>4999999.999999894</v>
       </c>
       <c r="E111" s="82" t="n">
@@ -3987,7 +3987,7 @@
         <v>353.68200000001536</v>
       </c>
       <c r="L111" s="88" t="n">
-        <f>IF(D111="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
+        <f>IF(D111="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C111-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
         <v>707.859901026536</v>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="76" t="str">
-        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
       </c>
       <c r="E112" s="82" t="str">
         <f>IF(D112="","",IF(ABS(C112-$G$43)&lt;0.000001,$G$49,$G$50/D112))</f>
@@ -4021,7 +4021,7 @@
         <f>IF(D112="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L112-L111,J112*(1+$G$42)))</f>
       </c>
       <c r="L112" s="88" t="str">
-        <f>IF(D112="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
+        <f>IF(D112="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C112-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4029,7 +4029,7 @@
         <f>IF($G$40="pons",80%+40*0.5%,IF(80.5%+40*0.5%&lt;=100%,80.5%+40*0.5%,""))</f>
       </c>
       <c r="D113" s="77" t="str">
-        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
       </c>
       <c r="E113" s="83" t="str">
         <f>IF(D113="","",IF(ABS(C113-$G$43)&lt;0.000001,$G$49,$G$50/D113))</f>
@@ -4053,7 +4053,7 @@
         <f>IF(D113="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L113-L112,J113*(1+$G$42)))</f>
       </c>
       <c r="L113" s="89" t="str">
-        <f>IF(D113="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
+        <f>IF(D113="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C113-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="114" ht="6" customHeight="1">

--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R18477e5145584d7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R4910903c19954c88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R9628a35141504f93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R3db615e523e9497d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -824,7 +824,7 @@
         <v>平台 / Quote</v>
       </c>
       <c r="D7" s="67" t="str">
-        <v>Four.meme / BNB</v>
+        <v>Pons V2 / USDG</v>
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="49" t="str">
@@ -838,7 +838,7 @@
         <v>买入税率（Flap）</v>
       </c>
       <c r="J7" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,25,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,25,FALSE)</f>
         <v>0</v>
       </c>
       <c r="K7" s="49"/>
@@ -849,7 +849,7 @@
         <v>目标控筹率</v>
       </c>
       <c r="D8" s="55" t="n">
-        <v>0.94</v>
+        <v>0.9</v>
       </c>
       <c r="E8" s="49"/>
       <c r="F8" s="49" t="str">
@@ -863,7 +863,7 @@
         <v>卖出税率（Flap）</v>
       </c>
       <c r="J8" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,26,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,26,FALSE)</f>
         <v>0</v>
       </c>
       <c r="K8" s="49"/>
@@ -886,7 +886,7 @@
         <v>Creator Tax（Pons）</v>
       </c>
       <c r="J9" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,27,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,27,FALSE)</f>
         <v>0</v>
       </c>
       <c r="K9" s="49"/>
@@ -927,8 +927,8 @@
         <v>单地址 Gas</v>
       </c>
       <c r="G11" s="54" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,33,FALSE)</f>
-        <v>0.01</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,33,FALSE)</f>
+        <v>0.005</v>
       </c>
       <c r="H11" s="49"/>
       <c r="I11" s="49"/>
@@ -949,15 +949,15 @@
       </c>
       <c r="G12" s="64" t="n">
         <f>IF(AND(ISNUMBER($D$55),$D$55&gt;0),ROUNDUP($G$56/$D$55,0),"")</f>
-        <v>14</v>
+        <v>9997</v>
       </c>
       <c r="H12" s="49"/>
       <c r="I12" s="49" t="str">
         <v>洗筹基础费率</v>
       </c>
       <c r="J12" s="55" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
-        <v>0.0025</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,20,FALSE)</f>
+        <v>0.01</v>
       </c>
       <c r="K12" s="49"/>
       <c r="L12" s="49"/>
@@ -1032,29 +1032,29 @@
       </c>
       <c r="D18" s="53" t="n">
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>112.69004142754045</v>
+        <v>52441.86394281925</v>
       </c>
       <c r="E18" s="48" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
+        <v>USDG</v>
       </c>
       <c r="F18" s="3" t="str">
         <v>原生币 Gas 储备</v>
       </c>
       <c r="G18" s="53" t="n">
         <f>D53*MAX(0,G11)</f>
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="H18" s="48" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,4,FALSE)</f>
+        <v>ETH</v>
       </c>
       <c r="I18" s="3" t="str">
         <v>总折算 / USDT</v>
       </c>
       <c r="J18" s="62" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>86489.00582052911</v>
+        <v>55300.72903151572</v>
       </c>
       <c r="K18" s="48" t="str">
         <v>USDT</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D19" s="63" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>84832.84998281738</v>
+        <v>52462.63914792182</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G19" s="63" t="n">
         <f>IF(G18=0,0,IF(AND(ISNUMBER(J44),J44&gt;0),G18*J44,""))</f>
-        <v>1656.155837711734</v>
+        <v>2838.0898835939033</v>
       </c>
       <c r="H19" s="3" t="str">
         <v>USDT</v>
@@ -1118,15 +1118,15 @@
     <row r="22" ht="20" customHeight="1">
       <c r="C22" s="3" t="str">
         <f>"预算 "&amp;TEXT($D$52,"0%")&amp;" 理论资金"</f>
-        <v>预算 95% 理论资金</v>
+        <v>预算 91% 理论资金</v>
       </c>
       <c r="D22" s="65" t="n">
         <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",($G$50/$J$51-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
-        <v>71.23230102652082</v>
+        <v>12456.88593249569</v>
       </c>
       <c r="E22" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
+        <v>USDG</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1144,11 +1144,11 @@
       </c>
       <c r="D23" s="65" t="n">
         <f>IF($D$51="可达",$J$41*MAX(0,$G$7-1),"")</f>
-        <v>18.180001026520895</v>
+        <v>510.7323232323232</v>
       </c>
       <c r="E23" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
+        <v>USDG</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="D24" s="65" t="n">
         <f>IF($D$51="可达",$J$52*$D$29,"")</f>
-        <v>7.055999999999987</v>
+        <v>29477.245687091236</v>
       </c>
       <c r="E24" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
+        <v>USDG</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1194,11 +1194,11 @@
       </c>
       <c r="D25" s="65" t="n">
         <f>IF($D$51="可达",$G$12,"")</f>
-        <v>14</v>
+        <v>9997</v>
       </c>
       <c r="E25" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
+        <v>USDG</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1218,12 +1218,12 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
-        <v>2.221739374498758</v>
+        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
+        <v>USDG</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D27" s="59" t="n">
         <f>D8*J54</f>
-        <v>0.93765</v>
+        <v>0.9</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D28" s="57" t="n">
         <f>D8</f>
-        <v>0.94</v>
+        <v>0.9</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J28" s="57" t="n">
         <f>G42</f>
-        <v>0.0025</v>
+        <v>0.01</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="D29" s="57" t="n">
         <f>MAX(0,$J$12)*2+$J$46+$J$47+$J$48*2</f>
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J29" s="57" t="n">
         <f>G42+J46+J48</f>
-        <v>0.0025</v>
+        <v>0.01</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="J30" s="57" t="n">
         <f>G42+J47+J48</f>
-        <v>0.0025</v>
+        <v>0.01</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" ht="20" customHeight="1" hidden="1">
+    <row r="31" ht="20" hidden="1" customHeight="1">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1325,7 +1325,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" ht="20" customHeight="1" hidden="1">
+    <row r="32" ht="20" hidden="1" customHeight="1">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -1337,7 +1337,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" ht="20" customHeight="1" hidden="1">
+    <row r="33" ht="20" hidden="1" customHeight="1">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1349,7 +1349,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" ht="20" customHeight="1" hidden="1">
+    <row r="34" ht="20" hidden="1" customHeight="1">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1361,7 +1361,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" ht="20" customHeight="1" hidden="1">
+    <row r="35" ht="20" hidden="1" customHeight="1">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -1395,12 +1395,12 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="65" t="n">
-        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,23,FALSE))</f>
-        <v>3.5279999996314997</v>
+        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,23,FALSE))</f>
+        <v>112.36111111111111</v>
       </c>
       <c r="H37" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
-        <v>BNB</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
+        <v>USDG</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -1433,7 +1433,7 @@
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="40" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C40" s="49"/>
       <c r="D40" s="49"/>
       <c r="E40" s="49"/>
@@ -1441,8 +1441,8 @@
         <v>模型类型</v>
       </c>
       <c r="G40" s="49" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,10,FALSE)</f>
-        <v>generic</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,10,FALSE)</f>
+        <v>pons</v>
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="49"/>
@@ -1450,7 +1450,7 @@
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
     </row>
-    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="41" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C41" s="49"/>
       <c r="D41" s="49"/>
       <c r="E41" s="49"/>
@@ -1458,7 +1458,7 @@
         <v>内盘基础费</v>
       </c>
       <c r="G41" s="58" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,19,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,19,FALSE)</f>
         <v>0.01</v>
       </c>
       <c r="H41" s="49"/>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="J41" s="49" t="n">
         <f>IF($G$40="pons",$G$49/(1-$G$41-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$53*(1+$G$41+$J$46),$G$52))</f>
-        <v>18.180001026520895</v>
+        <v>510.7323232323232</v>
       </c>
       <c r="K41" s="49"/>
       <c r="L41" s="49"/>
     </row>
-    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="42" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C42" s="49"/>
       <c r="D42" s="49"/>
       <c r="E42" s="49"/>
@@ -1480,8 +1480,8 @@
         <v>外盘基础费</v>
       </c>
       <c r="G42" s="58" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
-        <v>0.0025</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,20,FALSE)</f>
+        <v>0.01</v>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="49"/>
@@ -1489,7 +1489,7 @@
       <c r="K42" s="49"/>
       <c r="L42" s="49"/>
     </row>
-    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="43" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C43" s="49"/>
       <c r="D43" s="49"/>
       <c r="E43" s="49"/>
@@ -1497,21 +1497,21 @@
         <v>毕业控筹率</v>
       </c>
       <c r="G43" s="58" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,15,FALSE)</f>
-        <v>0.8</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,15,FALSE)</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H43" s="49"/>
       <c r="I43" s="49" t="str">
         <v>模型键</v>
       </c>
       <c r="J43" s="49" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,2,FALSE)</f>
-        <v>fourmeme-bnb</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,2,FALSE)</f>
+        <v>ponsv2-usdg</v>
       </c>
       <c r="K43" s="49"/>
       <c r="L43" s="49"/>
     </row>
-    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="44" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C44" s="49"/>
       <c r="D44" s="49"/>
       <c r="E44" s="49"/>
@@ -1519,26 +1519,26 @@
         <v>内盘初始 TOKEN</v>
       </c>
       <c r="G44" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,12,FALSE)</f>
-        <v>1073972562</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,12,FALSE)</f>
+        <v>1000000000</v>
       </c>
       <c r="H44" s="49"/>
       <c r="I44" s="49" t="str">
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J44" s="49" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,7,FALSE))</f>
-        <v>752.7981080507881</v>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,7,FALSE))</f>
+        <v>2580.0817123580937</v>
       </c>
       <c r="K44" s="49"/>
       <c r="L44" s="49"/>
     </row>
-    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="45" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C45" s="49" t="str">
         <v>总供应量</v>
       </c>
       <c r="D45" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,11,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,11,FALSE)</f>
         <v>1000000000</v>
       </c>
       <c r="E45" s="49"/>
@@ -1546,21 +1546,21 @@
         <v>内盘初始 Quote</v>
       </c>
       <c r="G45" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,13,FALSE)</f>
-        <v>6.164383561643836</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,13,FALSE)</f>
+        <v>202.25</v>
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="49" t="str">
         <v>税率上限</v>
       </c>
       <c r="J45" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,32,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,32,FALSE)</f>
         <v>0.1</v>
       </c>
       <c r="K45" s="49"/>
       <c r="L45" s="49"/>
     </row>
-    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="46" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C46" s="49"/>
       <c r="D46" s="49"/>
       <c r="E46" s="49"/>
@@ -1568,8 +1568,8 @@
         <v>内盘 K</v>
       </c>
       <c r="G46" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,14,FALSE)</f>
-        <v>6620378206</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,14,FALSE)</f>
+        <v>202250000000</v>
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="49" t="str">
@@ -1582,7 +1582,7 @@
       <c r="K46" s="49"/>
       <c r="L46" s="49"/>
     </row>
-    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="47" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C47" s="49"/>
       <c r="D47" s="49"/>
       <c r="E47" s="49"/>
@@ -1599,7 +1599,7 @@
       <c r="K47" s="49"/>
       <c r="L47" s="49"/>
     </row>
-    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="48" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C48" s="49"/>
       <c r="D48" s="49"/>
       <c r="E48" s="49"/>
@@ -1607,8 +1607,8 @@
         <v>外盘初始 TOKEN</v>
       </c>
       <c r="G48" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,16,FALSE)</f>
-        <v>200000000</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,16,FALSE)</f>
+        <v>204081632.65306124</v>
       </c>
       <c r="H48" s="49"/>
       <c r="I48" s="49" t="str">
@@ -1621,7 +1621,7 @@
       <c r="K48" s="49"/>
       <c r="L48" s="49"/>
     </row>
-    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="49" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C49" s="49"/>
       <c r="D49" s="49"/>
       <c r="E49" s="49"/>
@@ -1629,8 +1629,8 @@
         <v>外盘初始 Quote</v>
       </c>
       <c r="G49" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,17,FALSE)</f>
-        <v>17.64</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,17,FALSE)</f>
+        <v>505.625</v>
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="49"/>
@@ -1638,7 +1638,7 @@
       <c r="K49" s="49"/>
       <c r="L49" s="49"/>
     </row>
-    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="50" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C50" s="49"/>
       <c r="D50" s="49"/>
       <c r="E50" s="49"/>
@@ -1646,8 +1646,8 @@
         <v>外盘 K</v>
       </c>
       <c r="G50" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,18,FALSE)</f>
-        <v>3528000000</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,18,FALSE)</f>
+        <v>103188775510.20409</v>
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="49" t="str">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="J50" s="49" t="n">
         <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$52-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$52)-$G$51,IF(ABS($D$52-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$52))))</f>
-        <v>50000000.000000045</v>
+        <v>8367346.93877548</v>
       </c>
       <c r="K50" s="49"/>
       <c r="L50" s="49"/>
     </row>
-    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="51" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C51" s="49" t="str">
         <v>目标是否可达</v>
       </c>
@@ -1673,8 +1673,8 @@
         <v>永久锁仓 TOKEN</v>
       </c>
       <c r="G51" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,22,FALSE)</f>
-        <v>0</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,22,FALSE)</f>
+        <v>81632653.06122449</v>
       </c>
       <c r="H51" s="49"/>
       <c r="I51" s="49" t="str">
@@ -1682,26 +1682,26 @@
       </c>
       <c r="J51" s="49" t="n">
         <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)</f>
-        <v>50000000.00000009</v>
+        <v>8367346.93877551</v>
       </c>
       <c r="K51" s="49"/>
       <c r="L51" s="49"/>
     </row>
-    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="52" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C52" s="49" t="str">
         <v>预算控筹率</v>
       </c>
       <c r="D52" s="58" t="n">
         <f>IF($G$40="four-stock",$D$8+MAX(0,$J$10),$D$8+1%)</f>
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="E52" s="49"/>
       <c r="F52" s="49" t="str">
         <v>一套内盘原值</v>
       </c>
       <c r="G52" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,21,FALSE)</f>
-        <v>18.180001026520895</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,21,FALSE)</f>
+        <v>510.7323232323232</v>
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="49" t="str">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="J52" s="49" t="n">
         <f>IF($D$51="可达",$G$50/$J$50^2*$D$45,"")</f>
-        <v>1411.1999999999973</v>
+        <v>1473862.2843545617</v>
       </c>
       <c r="K52" s="49"/>
       <c r="L52" s="49"/>
     </row>
-    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="53" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C53" s="49" t="str">
         <v>地址总数</v>
       </c>
@@ -1727,8 +1727,8 @@
         <v>内盘募集 Quote</v>
       </c>
       <c r="G53" s="49" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,24,FALSE)</f>
-        <v>18.000000483500074</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,24,FALSE)</f>
+        <v>505.625</v>
       </c>
       <c r="H53" s="49"/>
       <c r="I53" s="49"/>
@@ -1736,13 +1736,13 @@
       <c r="K53" s="49"/>
       <c r="L53" s="49"/>
     </row>
-    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="54" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C54" s="49" t="str">
         <v>当前控筹上限</v>
       </c>
       <c r="D54" s="58" t="n">
         <f>IF($G$40="pons",1-$G$51/$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
-        <v>1</v>
+        <v>0.9183673469387755</v>
       </c>
       <c r="E54" s="49"/>
       <c r="F54" s="49" t="str">
@@ -1757,27 +1757,27 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="58" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
-        <v>0.9975</v>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
+        <v>1</v>
       </c>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
     </row>
-    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="55" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C55" s="49" t="str">
         <v>有效价格 / USDT</v>
       </c>
       <c r="D55" s="60" t="n">
-        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE),""))</f>
-        <v>752.7981080507881</v>
+        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,6,FALSE),""))</f>
+        <v>1.0003961568781237</v>
       </c>
       <c r="E55" s="49"/>
       <c r="F55" s="49" t="str">
         <v>价格来源</v>
       </c>
       <c r="G55" s="49" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,9,FALSE)</f>
-        <v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,9,FALSE)</f>
+        <v>USDG 按 1 USD 估算；https://www.coingecko.com/en/coins/global-dollar</v>
       </c>
       <c r="H55" s="49"/>
       <c r="I55" s="49" t="str">
@@ -1785,17 +1785,17 @@
       </c>
       <c r="J55" s="49" t="n">
         <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
-        <v>60000000.00000005</v>
+        <v>16491445.062873632</v>
       </c>
       <c r="K55" s="49"/>
       <c r="L55" s="49"/>
     </row>
-    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="56" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C56" s="49" t="str">
         <v>价格时间 / UTC</v>
       </c>
       <c r="D56" s="61" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,8,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,8,FALSE)</f>
         <v>46285.27349457176</v>
       </c>
       <c r="E56" s="49"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="J56" s="49" t="n">
         <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
-        <v>62350000.000000015</v>
+        <v>16491445.062873632</v>
       </c>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
@@ -1870,27 +1870,27 @@
       </c>
       <c r="D59" s="75" t="n">
         <f>$G$44-C59*$D$45</f>
-        <v>1073972562</v>
+        <v>1000000000</v>
       </c>
       <c r="E59" s="81" t="n">
         <f>$G$46/D59</f>
-        <v>6.1643830021795285</v>
+        <v>202.25</v>
       </c>
       <c r="F59" s="78" t="n">
         <f>IF(AND(ISNUMBER(D59),D59&gt;0,ISNUMBER(E59)),E59/D59,"")</f>
-        <v>5.739795615169104e-9</v>
+        <v>2.0225e-7</v>
       </c>
       <c r="G59" s="78" t="n">
         <f>IF(AND(ISNUMBER(F59),ISNUMBER($D$55)),F59*$D$55,"")</f>
-        <v>0.000004320907279697511</v>
+        <v>2.0233012272860051e-7</v>
       </c>
       <c r="H59" s="81" t="n">
         <f>IF(ISNUMBER(F59),F59*$D$45,"")</f>
-        <v>5.739795615169104</v>
+        <v>202.25</v>
       </c>
       <c r="I59" s="75" t="n">
         <f>IF(AND(ISNUMBER(H59),ISNUMBER($D$55)),H59*$D$55,"")</f>
-        <v>4320.907279697511</v>
+        <v>202.33012272860051</v>
       </c>
       <c r="J59" s="81" t="n">
         <f>0</f>
@@ -1912,39 +1912,39 @@
       </c>
       <c r="D60" s="76" t="n">
         <f>$G$44-C60*$D$45</f>
-        <v>973972562</v>
+        <v>900000000</v>
       </c>
       <c r="E60" s="82" t="n">
         <f>$G$46/D60</f>
-        <v>6.7972943636167855</v>
+        <v>224.72222222222223</v>
       </c>
       <c r="F60" s="79" t="n">
         <f>IF(AND(ISNUMBER(D60),D60&gt;0,ISNUMBER(E60)),E60/D60,"")</f>
-        <v>6.978938246123596e-9</v>
+        <v>2.496913580246914e-7</v>
       </c>
       <c r="G60" s="79" t="n">
         <f>IF(AND(ISNUMBER(F60),ISNUMBER($D$55)),F60*$D$55,"")</f>
-        <v>0.0000052537315078851285</v>
+        <v>2.497902749735809e-7</v>
       </c>
       <c r="H60" s="82" t="n">
         <f>IF(ISNUMBER(F60),F60*$D$45,"")</f>
-        <v>6.9789382461235965</v>
+        <v>249.6913580246914</v>
       </c>
       <c r="I60" s="76" t="n">
         <f>IF(AND(ISNUMBER(H60),ISNUMBER($D$55)),H60*$D$55,"")</f>
-        <v>5253.731507885129</v>
+        <v>249.79027497358092</v>
       </c>
       <c r="J60" s="82" t="n">
         <f>E60-E59</f>
-        <v>0.632911361437257</v>
+        <v>22.47222222222223</v>
       </c>
       <c r="K60" s="82" t="n">
         <f>IF($G$40="pons",J60/(1-$G$41-$J$48),J60*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>0.6392404750516296</v>
+        <v>22.69921436588104</v>
       </c>
       <c r="L60" s="88" t="n">
         <f>SUM($K$59:K60)</f>
-        <v>0.6392404750516296</v>
+        <v>22.69921436588104</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -1954,39 +1954,39 @@
       </c>
       <c r="D61" s="76" t="n">
         <f>$G$44-C61*$D$45</f>
-        <v>873972562</v>
+        <v>800000000</v>
       </c>
       <c r="E61" s="82" t="n">
         <f>$G$46/D61</f>
-        <v>7.575041247118694</v>
+        <v>252.8125</v>
       </c>
       <c r="F61" s="79" t="n">
         <f>IF(AND(ISNUMBER(D61),D61&gt;0,ISNUMBER(E61)),E61/D61,"")</f>
-        <v>8.667367348219674e-9</v>
+        <v>3.16015625e-7</v>
       </c>
       <c r="G61" s="79" t="n">
         <f>IF(AND(ISNUMBER(F61),ISNUMBER($D$55)),F61*$D$55,"")</f>
-        <v>0.000006524777741520947</v>
+        <v>3.161408167634383e-7</v>
       </c>
       <c r="H61" s="82" t="n">
         <f>IF(ISNUMBER(F61),F61*$D$45,"")</f>
-        <v>8.667367348219674</v>
+        <v>316.015625</v>
       </c>
       <c r="I61" s="76" t="n">
         <f>IF(AND(ISNUMBER(H61),ISNUMBER($D$55)),H61*$D$55,"")</f>
-        <v>6524.777741520947</v>
+        <v>316.1408167634383</v>
       </c>
       <c r="J61" s="82" t="n">
         <f>E61-E60</f>
-        <v>0.7777468835019086</v>
+        <v>28.09027777777777</v>
       </c>
       <c r="K61" s="82" t="n">
         <f>IF($G$40="pons",J61/(1-$G$41-$J$48),J61*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>0.7855243523369276</v>
+        <v>28.374017957351285</v>
       </c>
       <c r="L61" s="88" t="n">
         <f>SUM($K$59:K61)</f>
-        <v>1.4247648273885574</v>
+        <v>51.073232323232325</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -1996,39 +1996,39 @@
       </c>
       <c r="D62" s="76" t="n">
         <f>$G$44-C62*$D$45</f>
-        <v>773972562</v>
+        <v>700000000</v>
       </c>
       <c r="E62" s="82" t="n">
         <f>$G$46/D62</f>
-        <v>8.553763442068893</v>
+        <v>288.92857142857144</v>
       </c>
       <c r="F62" s="79" t="n">
         <f>IF(AND(ISNUMBER(D62),D62&gt;0,ISNUMBER(E62)),E62/D62,"")</f>
-        <v>1.1051765736973107e-8</v>
+        <v>4.1275510204081637e-7</v>
       </c>
       <c r="G62" s="79" t="n">
         <f>IF(AND(ISNUMBER(F62),ISNUMBER($D$55)),F62*$D$55,"")</f>
-        <v>0.00000831974833741388</v>
+        <v>4.1291861781347046e-7</v>
       </c>
       <c r="H62" s="82" t="n">
         <f>IF(ISNUMBER(F62),F62*$D$45,"")</f>
-        <v>11.051765736973108</v>
+        <v>412.7551020408164</v>
       </c>
       <c r="I62" s="76" t="n">
         <f>IF(AND(ISNUMBER(H62),ISNUMBER($D$55)),H62*$D$55,"")</f>
-        <v>8319.74833741388</v>
+        <v>412.91861781347046</v>
       </c>
       <c r="J62" s="82" t="n">
         <f>E62-E61</f>
-        <v>0.9787221949501994</v>
+        <v>36.116071428571445</v>
       </c>
       <c r="K62" s="82" t="n">
         <f>IF($G$40="pons",J62/(1-$G$41-$J$48),J62*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>0.9885094168997014</v>
+        <v>36.480880230880246</v>
       </c>
       <c r="L62" s="88" t="n">
         <f>SUM($K$59:K62)</f>
-        <v>2.413274244288259</v>
+        <v>87.55411255411258</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2038,39 +2038,39 @@
       </c>
       <c r="D63" s="76" t="n">
         <f>$G$44-C63*$D$45</f>
-        <v>673972562</v>
+        <v>600000000</v>
       </c>
       <c r="E63" s="82" t="n">
         <f>$G$46/D63</f>
-        <v>9.82291947665371</v>
+        <v>337.0833333333333</v>
       </c>
       <c r="F63" s="79" t="n">
         <f>IF(AND(ISNUMBER(D63),D63&gt;0,ISNUMBER(E63)),E63/D63,"")</f>
-        <v>1.4574657828064089e-8</v>
+        <v>5.618055555555556e-7</v>
       </c>
       <c r="G63" s="79" t="n">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER($D$55)),F63*$D$55,"")</f>
-        <v>0.000010971774838454255</v>
+        <v>5.62028118690557e-7</v>
       </c>
       <c r="H63" s="82" t="n">
         <f>IF(ISNUMBER(F63),F63*$D$45,"")</f>
-        <v>14.574657828064089</v>
+        <v>561.8055555555555</v>
       </c>
       <c r="I63" s="76" t="n">
         <f>IF(AND(ISNUMBER(H63),ISNUMBER($D$55)),H63*$D$55,"")</f>
-        <v>10971.774838454254</v>
+        <v>562.028118690557</v>
       </c>
       <c r="J63" s="82" t="n">
         <f>E63-E62</f>
-        <v>1.2691560345848156</v>
+        <v>48.15476190476187</v>
       </c>
       <c r="K63" s="82" t="n">
         <f>IF($G$40="pons",J63/(1-$G$41-$J$48),J63*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>1.2818475949306638</v>
+        <v>48.64117364117361</v>
       </c>
       <c r="L63" s="88" t="n">
         <f>SUM($K$59:K63)</f>
-        <v>3.6951218392189227</v>
+        <v>136.1952861952862</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2080,39 +2080,39 @@
       </c>
       <c r="D64" s="76" t="n">
         <f>$G$44-C64*$D$45</f>
-        <v>573972562</v>
+        <v>500000000</v>
       </c>
       <c r="E64" s="82" t="n">
         <f>$G$46/D64</f>
-        <v>11.534311296922239</v>
+        <v>404.5</v>
       </c>
       <c r="F64" s="79" t="n">
         <f>IF(AND(ISNUMBER(D64),D64&gt;0,ISNUMBER(E64)),E64/D64,"")</f>
-        <v>2.0095579580896828e-8</v>
+        <v>8.09e-7</v>
       </c>
       <c r="G64" s="79" t="n">
         <f>IF(AND(ISNUMBER(F64),ISNUMBER($D$55)),F64*$D$55,"")</f>
-        <v>0.00001512791428868318</v>
+        <v>8.093204909144021e-7</v>
       </c>
       <c r="H64" s="82" t="n">
         <f>IF(ISNUMBER(F64),F64*$D$45,"")</f>
-        <v>20.09557958089683</v>
+        <v>809</v>
       </c>
       <c r="I64" s="76" t="n">
         <f>IF(AND(ISNUMBER(H64),ISNUMBER($D$55)),H64*$D$55,"")</f>
-        <v>15127.914288683181</v>
+        <v>809.3204909144021</v>
       </c>
       <c r="J64" s="82" t="n">
         <f>E64-E63</f>
-        <v>1.7113918202685294</v>
+        <v>67.41666666666669</v>
       </c>
       <c r="K64" s="82" t="n">
         <f>IF($G$40="pons",J64/(1-$G$41-$J$48),J64*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>1.7285057384712148</v>
+        <v>68.09764309764311</v>
       </c>
       <c r="L64" s="88" t="n">
         <f>SUM($K$59:K64)</f>
-        <v>5.423627577690137</v>
+        <v>204.29292929292933</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2122,39 +2122,39 @@
       </c>
       <c r="D65" s="76" t="n">
         <f>$G$44-C65*$D$45</f>
-        <v>473972562</v>
+        <v>400000000</v>
       </c>
       <c r="E65" s="82" t="n">
         <f>$G$46/D65</f>
-        <v>13.96785117278582</v>
+        <v>505.625</v>
       </c>
       <c r="F65" s="79" t="n">
         <f>IF(AND(ISNUMBER(D65),D65&gt;0,ISNUMBER(E65)),E65/D65,"")</f>
-        <v>2.9469746336889898e-8</v>
+        <v>0.0000012640625</v>
       </c>
       <c r="G65" s="79" t="n">
         <f>IF(AND(ISNUMBER(F65),ISNUMBER($D$55)),F65*$D$55,"")</f>
-        <v>0.000022184769287147357</v>
+        <v>0.0000012645632670537531</v>
       </c>
       <c r="H65" s="82" t="n">
         <f>IF(ISNUMBER(F65),F65*$D$45,"")</f>
-        <v>29.469746336889898</v>
+        <v>1264.0625</v>
       </c>
       <c r="I65" s="76" t="n">
         <f>IF(AND(ISNUMBER(H65),ISNUMBER($D$55)),H65*$D$55,"")</f>
-        <v>22184.76928714736</v>
+        <v>1264.5632670537532</v>
       </c>
       <c r="J65" s="82" t="n">
         <f>E65-E64</f>
-        <v>2.4335398758635822</v>
+        <v>101.125</v>
       </c>
       <c r="K65" s="82" t="n">
         <f>IF($G$40="pons",J65/(1-$G$41-$J$48),J65*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>2.457875274622218</v>
+        <v>102.14646464646465</v>
       </c>
       <c r="L65" s="88" t="n">
         <f>SUM($K$59:K65)</f>
-        <v>7.881502852312355</v>
+        <v>306.439393939394</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2164,81 +2164,81 @@
       </c>
       <c r="D66" s="76" t="n">
         <f>$G$44-C66*$D$45</f>
-        <v>373972562</v>
+        <v>300000000</v>
       </c>
       <c r="E66" s="82" t="n">
         <f>$G$46/D66</f>
-        <v>17.702844750412464</v>
+        <v>674.1666666666666</v>
       </c>
       <c r="F66" s="79" t="n">
         <f>IF(AND(ISNUMBER(D66),D66&gt;0,ISNUMBER(E66)),E66/D66,"")</f>
-        <v>4.7337282328248626e-8</v>
+        <v>0.0000022472222222222223</v>
       </c>
       <c r="G66" s="79" t="n">
         <f>IF(AND(ISNUMBER(F66),ISNUMBER($D$55)),F66*$D$55,"")</f>
-        <v>0.00003563541657697157</v>
+        <v>0.000002248112474762228</v>
       </c>
       <c r="H66" s="82" t="n">
         <f>IF(ISNUMBER(F66),F66*$D$45,"")</f>
-        <v>47.33728232824863</v>
+        <v>2247.222222222222</v>
       </c>
       <c r="I66" s="76" t="n">
         <f>IF(AND(ISNUMBER(H66),ISNUMBER($D$55)),H66*$D$55,"")</f>
-        <v>35635.41657697157</v>
+        <v>2248.112474762228</v>
       </c>
       <c r="J66" s="82" t="n">
         <f>E66-E65</f>
-        <v>3.7349935776266427</v>
+        <v>168.54166666666663</v>
       </c>
       <c r="K66" s="82" t="n">
         <f>IF($G$40="pons",J66/(1-$G$41-$J$48),J66*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>3.7723435134029093</v>
+        <v>170.2441077441077</v>
       </c>
       <c r="L66" s="88" t="n">
         <f>SUM($K$59:K66)</f>
-        <v>11.653846365715264</v>
+        <v>476.68350168350173</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="C67" s="74" t="n">
         <f>$G$43</f>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D67" s="77" t="n">
         <f>$G$44-C67*$D$45</f>
-        <v>273972562</v>
+        <v>285714285.71428573</v>
       </c>
       <c r="E67" s="83" t="n">
         <f>$G$46/D67</f>
-        <v>24.16438404514391</v>
+        <v>707.875</v>
       </c>
       <c r="F67" s="80" t="n">
         <f>IF(AND(ISNUMBER(D67),D67&gt;0,ISNUMBER(E67)),E67/D67,"")</f>
-        <v>8.820001488011748e-8</v>
+        <v>0.0000024775624999999997</v>
       </c>
       <c r="G67" s="80" t="n">
         <f>IF(AND(ISNUMBER(F67),ISNUMBER($D$55)),F67*$D$55,"")</f>
-        <v>0.00006639680433180379</v>
+        <v>0.000002478544003425356</v>
       </c>
       <c r="H67" s="83" t="n">
         <f>IF(ISNUMBER(F67),F67*$D$45,"")</f>
-        <v>88.20001488011748</v>
+        <v>2477.5624999999995</v>
       </c>
       <c r="I67" s="77" t="n">
         <f>IF(AND(ISNUMBER(H67),ISNUMBER($D$55)),H67*$D$55,"")</f>
-        <v>66396.8043318038</v>
+        <v>2478.5440034253556</v>
       </c>
       <c r="J67" s="83" t="n">
         <f>E67-E66</f>
-        <v>6.461539294731445</v>
+        <v>33.70833333333337</v>
       </c>
       <c r="K67" s="83" t="n">
         <f>IF($G$40="pons",J67/(1-$G$41-$J$48),J67*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>6.526154687678759</v>
+        <v>34.048821548821586</v>
       </c>
       <c r="L67" s="89" t="n">
         <f>$J$41</f>
-        <v>18.180001026520895</v>
+        <v>510.7323232323232</v>
       </c>
     </row>
     <row r="68" ht="6" customHeight="1">
@@ -2314,31 +2314,31 @@
     <row r="72" ht="20" customHeight="1">
       <c r="C72" s="72" t="n">
         <f>IF($G$40="pons",$G$43,80%)</f>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D72" s="75" t="n">
         <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
-        <v>200000000</v>
+        <v>204081632.65306118</v>
       </c>
       <c r="E72" s="81" t="n">
         <f>IF(D72="","",IF(ABS(C72-$G$43)&lt;0.000001,$G$49,$G$50/D72))</f>
-        <v>17.64</v>
+        <v>505.625</v>
       </c>
       <c r="F72" s="78" t="n">
         <f>IF(AND(ISNUMBER(D72),D72&gt;0,ISNUMBER(E72)),E72/D72,"")</f>
-        <v>8.820000000000001e-8</v>
+        <v>0.0000024775625000000006</v>
       </c>
       <c r="G72" s="78" t="n">
         <f>IF(AND(ISNUMBER(F72),ISNUMBER($D$55)),F72*$D$55,"")</f>
-        <v>0.00006639679313007951</v>
+        <v>0.0000024785440034253568</v>
       </c>
       <c r="H72" s="81" t="n">
         <f>IF(ISNUMBER(F72),F72*$D$45,"")</f>
-        <v>88.2</v>
+        <v>2477.5625000000005</v>
       </c>
       <c r="I72" s="75" t="n">
         <f>IF(AND(ISNUMBER(H72),ISNUMBER($D$55)),H72*$D$55,"")</f>
-        <v>66396.79313007952</v>
+        <v>2478.5440034253565</v>
       </c>
       <c r="J72" s="81" t="n">
         <f>IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),0,E72-$G$49)</f>
@@ -2350,1651 +2350,1516 @@
       </c>
       <c r="L72" s="87" t="n">
         <f>IF(D72="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C72-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
-        <v>18.180001026520895</v>
+        <v>510.7323232323232</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="C73" s="73" t="n">
         <f>IF($G$40="pons",80%+0*0.5%,IF(80.5%+0*0.5%&lt;=100%,80.5%+0*0.5%,""))</f>
-        <v>0.805</v>
+        <v>0.8</v>
       </c>
       <c r="D73" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
-        <v>194999999.99999994</v>
+        <v>118367346.93877548</v>
       </c>
       <c r="E73" s="82" t="n">
         <f>IF(D73="","",IF(ABS(C73-$G$43)&lt;0.000001,$G$49,$G$50/D73))</f>
-        <v>18.0923076923077</v>
+        <v>871.7672413793106</v>
       </c>
       <c r="F73" s="79" t="n">
         <f>IF(AND(ISNUMBER(D73),D73&gt;0,ISNUMBER(E73)),E73/D73,"")</f>
-        <v>9.278106508875746e-8</v>
+        <v>0.000007364930142687281</v>
       </c>
       <c r="G73" s="79" t="n">
         <f>IF(AND(ISNUMBER(F73),ISNUMBER($D$55)),F73*$D$55,"")</f>
-        <v>0.00006984541026175364</v>
+        <v>0.000007367847810420207</v>
       </c>
       <c r="H73" s="82" t="n">
         <f>IF(ISNUMBER(F73),F73*$D$45,"")</f>
-        <v>92.78106508875746</v>
+        <v>7364.930142687281</v>
       </c>
       <c r="I73" s="76" t="n">
         <f>IF(AND(ISNUMBER(H73),ISNUMBER($D$55)),H73*$D$55,"")</f>
-        <v>69845.41026175364</v>
+        <v>7367.847810420207</v>
       </c>
       <c r="J73" s="82" t="n">
         <f>IF(D73="","",E73-E72)</f>
-        <v>0.4523076923076985</v>
+        <v>366.1422413793106</v>
       </c>
       <c r="K73" s="82" t="n">
         <f>IF(D73="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L73-L72,J73*(1+$G$42)))</f>
-        <v>0.45343846153846773</v>
+        <v>369.8406478578894</v>
       </c>
       <c r="L73" s="88" t="n">
         <f>IF(D73="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C73-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
-        <v>18.633439488059363</v>
+        <v>880.5729710902126</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="C74" s="73" t="n">
         <f>IF($G$40="pons",80%+1*0.5%,IF(80.5%+1*0.5%&lt;=100%,80.5%+1*0.5%,""))</f>
-        <v>0.81</v>
+        <v>0.805</v>
       </c>
       <c r="D74" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
-        <v>189999999.99999994</v>
+        <v>113367346.93877545</v>
       </c>
       <c r="E74" s="82" t="n">
         <f>IF(D74="","",IF(ABS(C74-$G$43)&lt;0.000001,$G$49,$G$50/D74))</f>
-        <v>18.568421052631585</v>
+        <v>910.2160216021607</v>
       </c>
       <c r="F74" s="79" t="n">
         <f>IF(AND(ISNUMBER(D74),D74&gt;0,ISNUMBER(E74)),E74/D74,"")</f>
-        <v>9.772853185595575e-8</v>
+        <v>0.000008028908201351198</v>
       </c>
       <c r="G74" s="79" t="n">
         <f>IF(AND(ISNUMBER(F74),ISNUMBER($D$55)),F74*$D$55,"")</f>
-        <v>0.00007356985388374466</v>
+        <v>0.000008032088908558986</v>
       </c>
       <c r="H74" s="82" t="n">
         <f>IF(ISNUMBER(F74),F74*$D$45,"")</f>
-        <v>97.72853185595575</v>
+        <v>8028.908201351198</v>
       </c>
       <c r="I74" s="76" t="n">
         <f>IF(AND(ISNUMBER(H74),ISNUMBER($D$55)),H74*$D$55,"")</f>
-        <v>73569.85388374467</v>
+        <v>8032.088908558987</v>
       </c>
       <c r="J74" s="82" t="n">
         <f>IF(D74="","",E74-E73)</f>
-        <v>0.47611336032388607</v>
+        <v>38.44878022285013</v>
       </c>
       <c r="K74" s="82" t="n">
         <f>IF(D74="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L74-L73,J74*(1+$G$42)))</f>
-        <v>0.47730364372469575</v>
+        <v>38.837151740252466</v>
       </c>
       <c r="L74" s="88" t="n">
         <f>IF(D74="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C74-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
-        <v>19.11074313178406</v>
+        <v>919.4101228304651</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="C75" s="73" t="n">
         <f>IF($G$40="pons",80%+2*0.5%,IF(80.5%+2*0.5%&lt;=100%,80.5%+2*0.5%,""))</f>
-        <v>0.8150000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="D75" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
-        <v>184999999.99999994</v>
+        <v>108367346.93877545</v>
       </c>
       <c r="E75" s="82" t="n">
         <f>IF(D75="","",IF(ABS(C75-$G$43)&lt;0.000001,$G$49,$G$50/D75))</f>
-        <v>19.070270270270278</v>
+        <v>952.2128060263659</v>
       </c>
       <c r="F75" s="79" t="n">
         <f>IF(AND(ISNUMBER(D75),D75&gt;0,ISNUMBER(E75)),E75/D75,"")</f>
-        <v>1.0308254200146099e-7</v>
+        <v>0.000008786897833388316</v>
       </c>
       <c r="G75" s="79" t="n">
         <f>IF(AND(ISNUMBER(F75),ISNUMBER($D$55)),F75*$D$55,"")</f>
-        <v>0.00007760034259176574</v>
+        <v>0.000008790378823402383</v>
       </c>
       <c r="H75" s="82" t="n">
         <f>IF(ISNUMBER(F75),F75*$D$45,"")</f>
-        <v>103.082542001461</v>
+        <v>8786.897833388317</v>
       </c>
       <c r="I75" s="76" t="n">
         <f>IF(AND(ISNUMBER(H75),ISNUMBER($D$55)),H75*$D$55,"")</f>
-        <v>77600.34259176573</v>
+        <v>8790.378823402383</v>
       </c>
       <c r="J75" s="82" t="n">
         <f>IF(D75="","",E75-E74)</f>
-        <v>0.5018492176386928</v>
+        <v>41.9967844242052</v>
       </c>
       <c r="K75" s="82" t="n">
         <f>IF(D75="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L75-L74,J75*(1+$G$42)))</f>
-        <v>0.5031038406827896</v>
+        <v>42.420994367883964</v>
       </c>
       <c r="L75" s="88" t="n">
         <f>IF(D75="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C75-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
-        <v>19.61384697246685</v>
+        <v>961.831117198349</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="C76" s="73" t="n">
         <f>IF($G$40="pons",80%+3*0.5%,IF(80.5%+3*0.5%&lt;=100%,80.5%+3*0.5%,""))</f>
-        <v>0.8200000000000001</v>
+        <v>0.8150000000000001</v>
       </c>
       <c r="D76" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
-        <v>179999999.99999994</v>
+        <v>103367346.93877545</v>
       </c>
       <c r="E76" s="82" t="n">
         <f>IF(D76="","",IF(ABS(C76-$G$43)&lt;0.000001,$G$49,$G$50/D76))</f>
-        <v>19.600000000000005</v>
+        <v>998.2724580454103</v>
       </c>
       <c r="F76" s="79" t="n">
         <f>IF(AND(ISNUMBER(D76),D76&gt;0,ISNUMBER(E76)),E76/D76,"")</f>
-        <v>1.0888888888888896e-7</v>
+        <v>0.000009657522298958565</v>
       </c>
       <c r="G76" s="79" t="n">
         <f>IF(AND(ISNUMBER(F76),ISNUMBER($D$55)),F76*$D$55,"")</f>
-        <v>0.00008197134954330808</v>
+        <v>0.00000966134819284293</v>
       </c>
       <c r="H76" s="82" t="n">
         <f>IF(ISNUMBER(F76),F76*$D$45,"")</f>
-        <v>108.88888888888896</v>
+        <v>9657.522298958565</v>
       </c>
       <c r="I76" s="76" t="n">
         <f>IF(AND(ISNUMBER(H76),ISNUMBER($D$55)),H76*$D$55,"")</f>
-        <v>81971.34954330808</v>
+        <v>9661.34819284293</v>
       </c>
       <c r="J76" s="82" t="n">
         <f>IF(D76="","",E76-E75)</f>
-        <v>0.529729729729727</v>
+        <v>46.05965201904439</v>
       </c>
       <c r="K76" s="82" t="n">
         <f>IF(D76="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L76-L75,J76*(1+$G$42)))</f>
-        <v>0.5310540540540513</v>
+        <v>46.5249010293378</v>
       </c>
       <c r="L76" s="88" t="n">
         <f>IF(D76="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C76-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
-        <v>20.1449010265209</v>
+        <v>1008.3560182276868</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="C77" s="73" t="n">
         <f>IF($G$40="pons",80%+4*0.5%,IF(80.5%+4*0.5%&lt;=100%,80.5%+4*0.5%,""))</f>
-        <v>0.8250000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="D77" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
-        <v>174999999.99999994</v>
+        <v>98367346.93877545</v>
       </c>
       <c r="E77" s="82" t="n">
         <f>IF(D77="","",IF(ABS(C77-$G$43)&lt;0.000001,$G$49,$G$50/D77))</f>
-        <v>20.160000000000007</v>
+        <v>1049.0145228215774</v>
       </c>
       <c r="F77" s="79" t="n">
         <f>IF(AND(ISNUMBER(D77),D77&gt;0,ISNUMBER(E77)),E77/D77,"")</f>
-        <v>1.1520000000000008e-7</v>
+        <v>0.000010664255522460026</v>
       </c>
       <c r="G77" s="79" t="n">
         <f>IF(AND(ISNUMBER(F77),ISNUMBER($D$55)),F77*$D$55,"")</f>
-        <v>0.00008672234204745084</v>
+        <v>0.000010668480240635316</v>
       </c>
       <c r="H77" s="82" t="n">
         <f>IF(ISNUMBER(F77),F77*$D$45,"")</f>
-        <v>115.20000000000007</v>
+        <v>10664.255522460026</v>
       </c>
       <c r="I77" s="76" t="n">
         <f>IF(AND(ISNUMBER(H77),ISNUMBER($D$55)),H77*$D$55,"")</f>
-        <v>86722.34204745085</v>
+        <v>10668.480240635316</v>
       </c>
       <c r="J77" s="82" t="n">
         <f>IF(D77="","",E77-E76)</f>
-        <v>0.5600000000000023</v>
+        <v>50.742064776167126</v>
       </c>
       <c r="K77" s="82" t="n">
         <f>IF(D77="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L77-L76,J77*(1+$G$42)))</f>
-        <v>0.5614000000000022</v>
+        <v>51.25461088501754</v>
       </c>
       <c r="L77" s="88" t="n">
         <f>IF(D77="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C77-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
-        <v>20.7063010265209</v>
+        <v>1059.6106291127044</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="C78" s="73" t="n">
         <f>IF($G$40="pons",80%+5*0.5%,IF(80.5%+5*0.5%&lt;=100%,80.5%+5*0.5%,""))</f>
-        <v>0.8300000000000001</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="D78" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
-        <v>169999999.99999994</v>
+        <v>93367346.93877545</v>
       </c>
       <c r="E78" s="82" t="n">
         <f>IF(D78="","",IF(ABS(C78-$G$43)&lt;0.000001,$G$49,$G$50/D78))</f>
-        <v>20.752941176470596</v>
+        <v>1105.1912568306018</v>
       </c>
       <c r="F78" s="79" t="n">
         <f>IF(AND(ISNUMBER(D78),D78&gt;0,ISNUMBER(E78)),E78/D78,"")</f>
-        <v>1.2207612456747413e-7</v>
+        <v>0.000011837021111409731</v>
       </c>
       <c r="G78" s="79" t="n">
         <f>IF(AND(ISNUMBER(F78),ISNUMBER($D$55)),F78*$D$55,"")</f>
-        <v>0.00009189867561256686</v>
+        <v>0.000011841710428739512</v>
       </c>
       <c r="H78" s="82" t="n">
         <f>IF(ISNUMBER(F78),F78*$D$45,"")</f>
-        <v>122.07612456747412</v>
+        <v>11837.021111409731</v>
       </c>
       <c r="I78" s="76" t="n">
         <f>IF(AND(ISNUMBER(H78),ISNUMBER($D$55)),H78*$D$55,"")</f>
-        <v>91898.67561256685</v>
+        <v>11841.71042873951</v>
       </c>
       <c r="J78" s="82" t="n">
         <f>IF(D78="","",E78-E77)</f>
-        <v>0.592941176470589</v>
+        <v>56.17673400902436</v>
       </c>
       <c r="K78" s="82" t="n">
         <f>IF(D78="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L78-L77,J78*(1+$G$42)))</f>
-        <v>0.5944235294117655</v>
+        <v>56.744175766691114</v>
       </c>
       <c r="L78" s="88" t="n">
         <f>IF(D78="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C78-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
-        <v>21.300724555932668</v>
+        <v>1116.3548048793955</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="C79" s="73" t="n">
         <f>IF($G$40="pons",80%+6*0.5%,IF(80.5%+6*0.5%&lt;=100%,80.5%+6*0.5%,""))</f>
-        <v>0.8350000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="D79" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
-        <v>164999999.9999999</v>
+        <v>88367346.93877545</v>
       </c>
       <c r="E79" s="82" t="n">
         <f>IF(D79="","",IF(ABS(C79-$G$43)&lt;0.000001,$G$49,$G$50/D79))</f>
-        <v>21.381818181818193</v>
+        <v>1167.7251732101624</v>
       </c>
       <c r="F79" s="79" t="n">
         <f>IF(AND(ISNUMBER(D79),D79&gt;0,ISNUMBER(E79)),E79/D79,"")</f>
-        <v>1.2958677685950428e-7</v>
+        <v>0.000013214441913925635</v>
       </c>
       <c r="G79" s="79" t="n">
         <f>IF(AND(ISNUMBER(F79),ISNUMBER($D$55)),F79*$D$55,"")</f>
-        <v>0.00009755268044823446</v>
+        <v>0.000013219676905980402</v>
       </c>
       <c r="H79" s="82" t="n">
         <f>IF(ISNUMBER(F79),F79*$D$45,"")</f>
-        <v>129.58677685950428</v>
+        <v>13214.441913925635</v>
       </c>
       <c r="I79" s="76" t="n">
         <f>IF(AND(ISNUMBER(H79),ISNUMBER($D$55)),H79*$D$55,"")</f>
-        <v>97552.68044823447</v>
+        <v>13219.676905980403</v>
       </c>
       <c r="J79" s="82" t="n">
         <f>IF(D79="","",E79-E78)</f>
-        <v>0.6288770053475972</v>
+        <v>62.53391637956065</v>
       </c>
       <c r="K79" s="82" t="n">
         <f>IF(D79="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L79-L78,J79*(1+$G$42)))</f>
-        <v>0.6304491978609661</v>
+        <v>63.16557210056635</v>
       </c>
       <c r="L79" s="88" t="n">
         <f>IF(D79="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C79-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
-        <v>21.931173753793633</v>
+        <v>1179.5203769799618</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="C80" s="73" t="n">
         <f>IF($G$40="pons",80%+7*0.5%,IF(80.5%+7*0.5%&lt;=100%,80.5%+7*0.5%,""))</f>
-        <v>0.8400000000000001</v>
+        <v>0.8350000000000001</v>
       </c>
       <c r="D80" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
-        <v>159999999.9999999</v>
+        <v>83367346.93877542</v>
       </c>
       <c r="E80" s="82" t="n">
         <f>IF(D80="","",IF(ABS(C80-$G$43)&lt;0.000001,$G$49,$G$50/D80))</f>
-        <v>22.05000000000001</v>
+        <v>1237.760097919218</v>
       </c>
       <c r="F80" s="79" t="n">
         <f>IF(AND(ISNUMBER(D80),D80&gt;0,ISNUMBER(E80)),E80/D80,"")</f>
-        <v>1.3781250000000014e-7</v>
+        <v>0.000014847061150071418</v>
       </c>
       <c r="G80" s="79" t="n">
         <f>IF(AND(ISNUMBER(F80),ISNUMBER($D$55)),F80*$D$55,"")</f>
-        <v>0.00010374498926574933</v>
+        <v>0.000014852942915465941</v>
       </c>
       <c r="H80" s="82" t="n">
         <f>IF(ISNUMBER(F80),F80*$D$45,"")</f>
-        <v>137.81250000000014</v>
+        <v>14847.061150071419</v>
       </c>
       <c r="I80" s="76" t="n">
         <f>IF(AND(ISNUMBER(H80),ISNUMBER($D$55)),H80*$D$55,"")</f>
-        <v>103744.98926574933</v>
+        <v>14852.942915465943</v>
       </c>
       <c r="J80" s="82" t="n">
         <f>IF(D80="","",E80-E79)</f>
-        <v>0.668181818181818</v>
+        <v>70.03492470905553</v>
       </c>
       <c r="K80" s="82" t="n">
         <f>IF(D80="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L80-L79,J80*(1+$G$42)))</f>
-        <v>0.6698522727272725</v>
+        <v>70.74234819096455</v>
       </c>
       <c r="L80" s="88" t="n">
         <f>IF(D80="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C80-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
-        <v>22.601026026520906</v>
+        <v>1250.2627251709264</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="C81" s="73" t="n">
         <f>IF($G$40="pons",80%+8*0.5%,IF(80.5%+8*0.5%&lt;=100%,80.5%+8*0.5%,""))</f>
-        <v>0.8450000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="D81" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
-        <v>154999999.9999999</v>
+        <v>78367346.93877542</v>
       </c>
       <c r="E81" s="82" t="n">
         <f>IF(D81="","",IF(ABS(C81-$G$43)&lt;0.000001,$G$49,$G$50/D81))</f>
-        <v>22.76129032258066</v>
+        <v>1316.7317708333348</v>
       </c>
       <c r="F81" s="79" t="n">
         <f>IF(AND(ISNUMBER(D81),D81&gt;0,ISNUMBER(E81)),E81/D81,"")</f>
-        <v>1.4684703433923014e-7</v>
+        <v>0.000016802046034071218</v>
       </c>
       <c r="G81" s="79" t="n">
         <f>IF(AND(ISNUMBER(F81),ISNUMBER($D$55)),F81*$D$55,"")</f>
-        <v>0.00011054616962344156</v>
+        <v>0.000016808702280174165</v>
       </c>
       <c r="H81" s="82" t="n">
         <f>IF(ISNUMBER(F81),F81*$D$45,"")</f>
-        <v>146.84703433923013</v>
+        <v>16802.046034071216</v>
       </c>
       <c r="I81" s="76" t="n">
         <f>IF(AND(ISNUMBER(H81),ISNUMBER($D$55)),H81*$D$55,"")</f>
-        <v>110546.16962344156</v>
+        <v>16808.702280174162</v>
       </c>
       <c r="J81" s="82" t="n">
         <f>IF(D81="","",E81-E80)</f>
-        <v>0.7112903225806484</v>
+        <v>78.97167291411688</v>
       </c>
       <c r="K81" s="82" t="n">
         <f>IF(D81="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L81-L80,J81*(1+$G$42)))</f>
-        <v>0.7130685483871</v>
+        <v>79.7693665799161</v>
       </c>
       <c r="L81" s="88" t="n">
         <f>IF(D81="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C81-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
-        <v>23.314094574908005</v>
+        <v>1330.0320917508425</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="C82" s="73" t="n">
         <f>IF($G$40="pons",80%+9*0.5%,IF(80.5%+9*0.5%&lt;=100%,80.5%+9*0.5%,""))</f>
-        <v>0.8500000000000001</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="D82" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
-        <v>149999999.9999999</v>
+        <v>73367346.93877542</v>
       </c>
       <c r="E82" s="82" t="n">
         <f>IF(D82="","",IF(ABS(C82-$G$43)&lt;0.000001,$G$49,$G$50/D82))</f>
-        <v>23.520000000000014</v>
+        <v>1406.4673157162745</v>
       </c>
       <c r="F82" s="79" t="n">
         <f>IF(AND(ISNUMBER(D82),D82&gt;0,ISNUMBER(E82)),E82/D82,"")</f>
-        <v>1.5680000000000019e-7</v>
+        <v>0.000019170208197523652</v>
       </c>
       <c r="G82" s="79" t="n">
         <f>IF(AND(ISNUMBER(F82),ISNUMBER($D$55)),F82*$D$55,"")</f>
-        <v>0.00011803874334236371</v>
+        <v>0.000019177802607356162</v>
       </c>
       <c r="H82" s="82" t="n">
         <f>IF(ISNUMBER(F82),F82*$D$45,"")</f>
-        <v>156.80000000000018</v>
+        <v>19170.20819752365</v>
       </c>
       <c r="I82" s="76" t="n">
         <f>IF(AND(ISNUMBER(H82),ISNUMBER($D$55)),H82*$D$55,"")</f>
-        <v>118038.74334236371</v>
+        <v>19177.802607356163</v>
       </c>
       <c r="J82" s="82" t="n">
         <f>IF(D82="","",E82-E81)</f>
-        <v>0.758709677419354</v>
+        <v>89.73554488293962</v>
       </c>
       <c r="K82" s="82" t="n">
         <f>IF(D82="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L82-L81,J82*(1+$G$42)))</f>
-        <v>0.7606064516129024</v>
+        <v>90.6419645282217</v>
       </c>
       <c r="L82" s="88" t="n">
         <f>IF(D82="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C82-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
-        <v>24.074701026520906</v>
+        <v>1420.6740562790642</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="C83" s="73" t="n">
         <f>IF($G$40="pons",80%+10*0.5%,IF(80.5%+10*0.5%&lt;=100%,80.5%+10*0.5%,""))</f>
-        <v>0.8550000000000001</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="D83" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
-        <v>144999999.9999999</v>
+        <v>68367346.93877542</v>
       </c>
       <c r="E83" s="82" t="n">
         <f>IF(D83="","",IF(ABS(C83-$G$43)&lt;0.000001,$G$49,$G$50/D83))</f>
-        <v>24.331034482758636</v>
+        <v>1509.3283582089573</v>
       </c>
       <c r="F83" s="79" t="n">
         <f>IF(AND(ISNUMBER(D83),D83&gt;0,ISNUMBER(E83)),E83/D83,"")</f>
-        <v>1.6780023781212862e-7</v>
+        <v>0.00002207674314992209</v>
       </c>
       <c r="G83" s="79" t="n">
         <f>IF(AND(ISNUMBER(F83),ISNUMBER($D$55)),F83*$D$55,"")</f>
-        <v>0.00012631970155544273</v>
+        <v>0.0000220854890035675</v>
       </c>
       <c r="H83" s="82" t="n">
         <f>IF(ISNUMBER(F83),F83*$D$45,"")</f>
-        <v>167.80023781212861</v>
+        <v>22076.74314992209</v>
       </c>
       <c r="I83" s="76" t="n">
         <f>IF(AND(ISNUMBER(H83),ISNUMBER($D$55)),H83*$D$55,"")</f>
-        <v>126319.70155544273</v>
+        <v>22085.4890035675</v>
       </c>
       <c r="J83" s="82" t="n">
         <f>IF(D83="","",E83-E82)</f>
-        <v>0.8110344827586218</v>
+        <v>102.86104249268283</v>
       </c>
       <c r="K83" s="82" t="n">
         <f>IF(D83="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L83-L82,J83*(1+$G$42)))</f>
-        <v>0.8130620689655182</v>
+        <v>103.90004292190224</v>
       </c>
       <c r="L83" s="88" t="n">
         <f>IF(D83="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C83-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
-        <v>24.887763095486427</v>
+        <v>1524.5740992009664</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="C84" s="73" t="n">
         <f>IF($G$40="pons",80%+11*0.5%,IF(80.5%+11*0.5%&lt;=100%,80.5%+11*0.5%,""))</f>
-        <v>0.8600000000000001</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="D84" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
-        <v>139999999.9999999</v>
+        <v>63367346.93877542</v>
       </c>
       <c r="E84" s="82" t="n">
         <f>IF(D84="","",IF(ABS(C84-$G$43)&lt;0.000001,$G$49,$G$50/D84))</f>
-        <v>25.200000000000017</v>
+        <v>1628.421900161033</v>
       </c>
       <c r="F84" s="79" t="n">
         <f>IF(AND(ISNUMBER(D84),D84&gt;0,ISNUMBER(E84)),E84/D84,"")</f>
-        <v>1.8000000000000024e-7</v>
+        <v>0.000025698123384183808</v>
       </c>
       <c r="G84" s="79" t="n">
         <f>IF(AND(ISNUMBER(F84),ISNUMBER($D$55)),F84*$D$55,"")</f>
-        <v>0.00013550365944914203</v>
+        <v>0.000025708303872517323</v>
       </c>
       <c r="H84" s="82" t="n">
         <f>IF(ISNUMBER(F84),F84*$D$45,"")</f>
-        <v>180.00000000000023</v>
+        <v>25698.123384183808</v>
       </c>
       <c r="I84" s="76" t="n">
         <f>IF(AND(ISNUMBER(H84),ISNUMBER($D$55)),H84*$D$55,"")</f>
-        <v>135503.65944914203</v>
+        <v>25708.30387251732</v>
       </c>
       <c r="J84" s="82" t="n">
         <f>IF(D84="","",E84-E83)</f>
-        <v>0.8689655172413815</v>
+        <v>119.09354195207561</v>
       </c>
       <c r="K84" s="82" t="n">
         <f>IF(D84="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L84-L83,J84*(1+$G$42)))</f>
-        <v>0.8711379310344849</v>
+        <v>120.29650702229856</v>
       </c>
       <c r="L84" s="88" t="n">
         <f>IF(D84="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C84-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
-        <v>25.75890102652091</v>
+        <v>1644.870606223265</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="C85" s="73" t="n">
         <f>IF($G$40="pons",80%+12*0.5%,IF(80.5%+12*0.5%&lt;=100%,80.5%+12*0.5%,""))</f>
-        <v>0.865</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="D85" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
-        <v>135000000</v>
+        <v>58367346.93877542</v>
       </c>
       <c r="E85" s="82" t="n">
         <f>IF(D85="","",IF(ABS(C85-$G$43)&lt;0.000001,$G$49,$G$50/D85))</f>
-        <v>26.133333333333333</v>
+        <v>1767.9195804195833</v>
       </c>
       <c r="F85" s="79" t="n">
         <f>IF(AND(ISNUMBER(D85),D85&gt;0,ISNUMBER(E85)),E85/D85,"")</f>
-        <v>1.9358024691358023e-7</v>
+        <v>0.000030289531272922977</v>
       </c>
       <c r="G85" s="79" t="n">
         <f>IF(AND(ISNUMBER(F85),ISNUMBER($D$55)),F85*$D$55,"")</f>
-        <v>0.0001457268436325476</v>
+        <v>0.000030301530679071887</v>
       </c>
       <c r="H85" s="82" t="n">
         <f>IF(ISNUMBER(F85),F85*$D$45,"")</f>
-        <v>193.58024691358023</v>
+        <v>30289.531272922977</v>
       </c>
       <c r="I85" s="76" t="n">
         <f>IF(AND(ISNUMBER(H85),ISNUMBER($D$55)),H85*$D$55,"")</f>
-        <v>145726.8436325476</v>
+        <v>30301.530679071886</v>
       </c>
       <c r="J85" s="82" t="n">
         <f>IF(D85="","",E85-E84)</f>
-        <v>0.9333333333333158</v>
+        <v>139.49768025855042</v>
       </c>
       <c r="K85" s="82" t="n">
         <f>IF(D85="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L85-L84,J85*(1+$G$42)))</f>
-        <v>0.935666666666649</v>
+        <v>140.906747735909</v>
       </c>
       <c r="L85" s="88" t="n">
         <f>IF(D85="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C85-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
-        <v>26.694567693187558</v>
+        <v>1785.777353959174</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="C86" s="73" t="n">
         <f>IF($G$40="pons",80%+13*0.5%,IF(80.5%+13*0.5%&lt;=100%,80.5%+13*0.5%,""))</f>
-        <v>0.8700000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="D86" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
-        <v>129999999.9999999</v>
+        <v>53367346.93877551</v>
       </c>
       <c r="E86" s="82" t="n">
         <f>IF(D86="","",IF(ABS(C86-$G$43)&lt;0.000001,$G$49,$G$50/D86))</f>
-        <v>27.13846153846156</v>
+        <v>1933.5564053537287</v>
       </c>
       <c r="F86" s="79" t="n">
         <f>IF(AND(ISNUMBER(D86),D86&gt;0,ISNUMBER(E86)),E86/D86,"")</f>
-        <v>2.0875739644970446e-7</v>
+        <v>0.00003623107604678115</v>
       </c>
       <c r="G86" s="79" t="n">
         <f>IF(AND(ISNUMBER(F86),ISNUMBER($D$55)),F86*$D$55,"")</f>
-        <v>0.00015715217308894582</v>
+        <v>0.000036245429236758905</v>
       </c>
       <c r="H86" s="82" t="n">
         <f>IF(ISNUMBER(F86),F86*$D$45,"")</f>
-        <v>208.75739644970446</v>
+        <v>36231.07604678115</v>
       </c>
       <c r="I86" s="76" t="n">
         <f>IF(AND(ISNUMBER(H86),ISNUMBER($D$55)),H86*$D$55,"")</f>
-        <v>157152.17308894583</v>
+        <v>36245.4292367589</v>
       </c>
       <c r="J86" s="82" t="n">
         <f>IF(D86="","",E86-E85)</f>
-        <v>1.0051282051282264</v>
+        <v>165.63682493414535</v>
       </c>
       <c r="K86" s="82" t="n">
         <f>IF(D86="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L86-L85,J86*(1+$G$42)))</f>
-        <v>1.0076410256410469</v>
+        <v>167.30992417590414</v>
       </c>
       <c r="L86" s="88" t="n">
         <f>IF(D86="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C86-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
-        <v>27.702208718828608</v>
+        <v>1953.0872781350781</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="C87" s="73" t="n">
         <f>IF($G$40="pons",80%+14*0.5%,IF(80.5%+14*0.5%&lt;=100%,80.5%+14*0.5%,""))</f>
-        <v>0.875</v>
+        <v>0.8700000000000001</v>
       </c>
       <c r="D87" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
-        <v>125000000</v>
+        <v>48367346.938775405</v>
       </c>
       <c r="E87" s="82" t="n">
         <f>IF(D87="","",IF(ABS(C87-$G$43)&lt;0.000001,$G$49,$G$50/D87))</f>
-        <v>28.224</v>
+        <v>2133.4388185654057</v>
       </c>
       <c r="F87" s="79" t="n">
         <f>IF(AND(ISNUMBER(D87),D87&gt;0,ISNUMBER(E87)),E87/D87,"")</f>
-        <v>2.2579200000000001e-7</v>
+        <v>0.000044109072620128736</v>
       </c>
       <c r="G87" s="79" t="n">
         <f>IF(AND(ISNUMBER(F87),ISNUMBER($D$55)),F87*$D$55,"")</f>
-        <v>0.00016997579041300355</v>
+        <v>0.00004412654673263486</v>
       </c>
       <c r="H87" s="82" t="n">
         <f>IF(ISNUMBER(F87),F87*$D$45,"")</f>
-        <v>225.792</v>
+        <v>44109.07262012873</v>
       </c>
       <c r="I87" s="76" t="n">
         <f>IF(AND(ISNUMBER(H87),ISNUMBER($D$55)),H87*$D$55,"")</f>
-        <v>169975.79041300353</v>
+        <v>44126.54673263485</v>
       </c>
       <c r="J87" s="82" t="n">
         <f>IF(D87="","",E87-E86)</f>
-        <v>1.085538461538441</v>
+        <v>199.88241321167698</v>
       </c>
       <c r="K87" s="82" t="n">
         <f>IF(D87="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L87-L86,J87*(1+$G$42)))</f>
-        <v>1.088252307692287</v>
+        <v>201.90142748654125</v>
       </c>
       <c r="L87" s="88" t="n">
         <f>IF(D87="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C87-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
-        <v>28.790461026520894</v>
+        <v>2154.9887056216194</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="C88" s="73" t="n">
         <f>IF($G$40="pons",80%+15*0.5%,IF(80.5%+15*0.5%&lt;=100%,80.5%+15*0.5%,""))</f>
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="D88" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
-        <v>120000000</v>
+        <v>43367346.93877551</v>
       </c>
       <c r="E88" s="82" t="n">
         <f>IF(D88="","",IF(ABS(C88-$G$43)&lt;0.000001,$G$49,$G$50/D88))</f>
-        <v>29.4</v>
+        <v>2379.4117647058824</v>
       </c>
       <c r="F88" s="79" t="n">
         <f>IF(AND(ISNUMBER(D88),D88&gt;0,ISNUMBER(E88)),E88/D88,"")</f>
-        <v>2.45e-7</v>
+        <v>0.000054866435986159176</v>
       </c>
       <c r="G88" s="79" t="n">
         <f>IF(AND(ISNUMBER(F88),ISNUMBER($D$55)),F88*$D$55,"")</f>
-        <v>0.00018443553647244307</v>
+        <v>0.00005488817170215322</v>
       </c>
       <c r="H88" s="82" t="n">
         <f>IF(ISNUMBER(F88),F88*$D$45,"")</f>
-        <v>244.99999999999997</v>
+        <v>54866.43598615917</v>
       </c>
       <c r="I88" s="76" t="n">
         <f>IF(AND(ISNUMBER(H88),ISNUMBER($D$55)),H88*$D$55,"")</f>
-        <v>184435.53647244305</v>
+        <v>54888.171702153224</v>
       </c>
       <c r="J88" s="82" t="n">
         <f>IF(D88="","",E88-E87)</f>
-        <v>1.1759999999999984</v>
+        <v>245.97294614047678</v>
       </c>
       <c r="K88" s="82" t="n">
         <f>IF(D88="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L88-L87,J88*(1+$G$42)))</f>
-        <v>1.1789399999999983</v>
+        <v>248.4575213540179</v>
       </c>
       <c r="L88" s="88" t="n">
         <f>IF(D88="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C88-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
-        <v>29.96940102652089</v>
+        <v>2403.4462269756373</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="C89" s="73" t="n">
         <f>IF($G$40="pons",80%+16*0.5%,IF(80.5%+16*0.5%&lt;=100%,80.5%+16*0.5%,""))</f>
-        <v>0.885</v>
+        <v>0.88</v>
       </c>
       <c r="D89" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
-        <v>114999999.99999999</v>
+        <v>38367346.93877551</v>
       </c>
       <c r="E89" s="82" t="n">
         <f>IF(D89="","",IF(ABS(C89-$G$43)&lt;0.000001,$G$49,$G$50/D89))</f>
-        <v>30.67826086956522</v>
+        <v>2689.494680851064</v>
       </c>
       <c r="F89" s="79" t="n">
         <f>IF(AND(ISNUMBER(D89),D89&gt;0,ISNUMBER(E89)),E89/D89,"")</f>
-        <v>2.667674858223063e-7</v>
+        <v>0.00007009853157537347</v>
       </c>
       <c r="G89" s="79" t="n">
         <f>IF(AND(ISNUMBER(F89),ISNUMBER($D$55)),F89*$D$55,"")</f>
-        <v>0.0002008220586164976</v>
+        <v>0.00007012630159080342</v>
       </c>
       <c r="H89" s="82" t="n">
         <f>IF(ISNUMBER(F89),F89*$D$45,"")</f>
-        <v>266.7674858223063</v>
+        <v>70098.53157537348</v>
       </c>
       <c r="I89" s="76" t="n">
         <f>IF(AND(ISNUMBER(H89),ISNUMBER($D$55)),H89*$D$55,"")</f>
-        <v>200822.0586164976</v>
+        <v>70126.30159080343</v>
       </c>
       <c r="J89" s="82" t="n">
         <f>IF(D89="","",E89-E88)</f>
-        <v>1.278260869565223</v>
+        <v>310.08291614518157</v>
       </c>
       <c r="K89" s="82" t="n">
         <f>IF(D89="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L89-L88,J89*(1+$G$42)))</f>
-        <v>1.2814565217391358</v>
+        <v>313.215066813314</v>
       </c>
       <c r="L89" s="88" t="n">
         <f>IF(D89="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C89-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
-        <v>31.25085754826003</v>
+        <v>2716.6612937889513</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="C90" s="73" t="n">
         <f>IF($G$40="pons",80%+17*0.5%,IF(80.5%+17*0.5%&lt;=100%,80.5%+17*0.5%,""))</f>
-        <v>0.89</v>
+        <v>0.885</v>
       </c>
       <c r="D90" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
-        <v>109999999.99999999</v>
+        <v>33367346.938775495</v>
       </c>
       <c r="E90" s="82" t="n">
         <f>IF(D90="","",IF(ABS(C90-$G$43)&lt;0.000001,$G$49,$G$50/D90))</f>
-        <v>32.07272727272728</v>
+        <v>3092.5076452599405</v>
       </c>
       <c r="F90" s="79" t="n">
         <f>IF(AND(ISNUMBER(D90),D90&gt;0,ISNUMBER(E90)),E90/D90,"")</f>
-        <v>2.915702479338844e-7</v>
+        <v>0.00009268065725855483</v>
       </c>
       <c r="G90" s="79" t="n">
         <f>IF(AND(ISNUMBER(F90),ISNUMBER($D$55)),F90*$D$55,"")</f>
-        <v>0.00021949353100852737</v>
+        <v>0.00009271737333839683</v>
       </c>
       <c r="H90" s="82" t="n">
         <f>IF(ISNUMBER(F90),F90*$D$45,"")</f>
-        <v>291.5702479338844</v>
+        <v>92680.65725855483</v>
       </c>
       <c r="I90" s="76" t="n">
         <f>IF(AND(ISNUMBER(H90),ISNUMBER($D$55)),H90*$D$55,"")</f>
-        <v>219493.53100852738</v>
+        <v>92717.37333839682</v>
       </c>
       <c r="J90" s="82" t="n">
         <f>IF(D90="","",E90-E89)</f>
-        <v>1.3944664031620562</v>
+        <v>403.01296440887654</v>
       </c>
       <c r="K90" s="82" t="n">
         <f>IF(D90="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L90-L89,J90*(1+$G$42)))</f>
-        <v>1.3979525691699612</v>
+        <v>407.083802433207</v>
       </c>
       <c r="L90" s="88" t="n">
         <f>IF(D90="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C90-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
-        <v>32.64881011742999</v>
+        <v>3123.7450962221583</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="C91" s="73" t="n">
         <f>IF($G$40="pons",80%+18*0.5%,IF(80.5%+18*0.5%&lt;=100%,80.5%+18*0.5%,""))</f>
-        <v>0.895</v>
+        <v>0.89</v>
       </c>
       <c r="D91" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
-        <v>104999999.99999999</v>
+        <v>28367346.938775495</v>
       </c>
       <c r="E91" s="82" t="n">
         <f>IF(D91="","",IF(ABS(C91-$G$43)&lt;0.000001,$G$49,$G$50/D91))</f>
-        <v>33.6</v>
+        <v>3637.5899280575563</v>
       </c>
       <c r="F91" s="79" t="n">
         <f>IF(AND(ISNUMBER(D91),D91&gt;0,ISNUMBER(E91)),E91/D91,"")</f>
-        <v>3.2000000000000006e-7</v>
+        <v>0.0001282315873919571</v>
       </c>
       <c r="G91" s="79" t="n">
         <f>IF(AND(ISNUMBER(F91),ISNUMBER($D$55)),F91*$D$55,"")</f>
-        <v>0.00024089539457625224</v>
+        <v>0.00012828238721729514</v>
       </c>
       <c r="H91" s="82" t="n">
         <f>IF(ISNUMBER(F91),F91*$D$45,"")</f>
-        <v>320.00000000000006</v>
+        <v>128231.5873919571</v>
       </c>
       <c r="I91" s="76" t="n">
         <f>IF(AND(ISNUMBER(H91),ISNUMBER($D$55)),H91*$D$55,"")</f>
-        <v>240895.39457625223</v>
+        <v>128282.38721729514</v>
       </c>
       <c r="J91" s="82" t="n">
         <f>IF(D91="","",E91-E90)</f>
-        <v>1.5272727272727238</v>
+        <v>545.0822827976158</v>
       </c>
       <c r="K91" s="82" t="n">
         <f>IF(D91="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L91-L90,J91*(1+$G$42)))</f>
-        <v>1.5310909090909055</v>
+        <v>550.5881644420342</v>
       </c>
       <c r="L91" s="88" t="n">
         <f>IF(D91="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C91-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
-        <v>34.179901026520895</v>
+        <v>3674.3332606641925</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="C92" s="73" t="n">
         <f>IF($G$40="pons",80%+19*0.5%,IF(80.5%+19*0.5%&lt;=100%,80.5%+19*0.5%,""))</f>
-        <v>0.9</v>
+        <v>0.895</v>
       </c>
       <c r="D92" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
-        <v>99999999.99999999</v>
+        <v>23367346.938775495</v>
       </c>
       <c r="E92" s="82" t="n">
         <f>IF(D92="","",IF(ABS(C92-$G$43)&lt;0.000001,$G$49,$G$50/D92))</f>
-        <v>35.28000000000001</v>
+        <v>4415.938864628824</v>
       </c>
       <c r="F92" s="79" t="n">
         <f>IF(AND(ISNUMBER(D92),D92&gt;0,ISNUMBER(E92)),E92/D92,"")</f>
-        <v>3.5280000000000014e-7</v>
+        <v>0.00018897904311512012</v>
       </c>
       <c r="G92" s="79" t="n">
         <f>IF(AND(ISNUMBER(F92),ISNUMBER($D$55)),F92*$D$55,"")</f>
-        <v>0.00026558717252031814</v>
+        <v>0.0001890539084628714</v>
       </c>
       <c r="H92" s="82" t="n">
         <f>IF(ISNUMBER(F92),F92*$D$45,"")</f>
-        <v>352.8000000000001</v>
+        <v>188979.04311512012</v>
       </c>
       <c r="I92" s="76" t="n">
         <f>IF(AND(ISNUMBER(H92),ISNUMBER($D$55)),H92*$D$55,"")</f>
-        <v>265587.1725203181</v>
+        <v>189053.9084628714</v>
       </c>
       <c r="J92" s="82" t="n">
         <f>IF(D92="","",E92-E91)</f>
-        <v>1.6800000000000068</v>
+        <v>778.348936571268</v>
       </c>
       <c r="K92" s="82" t="n">
         <f>IF(D92="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L92-L91,J92*(1+$G$42)))</f>
-        <v>1.6842000000000068</v>
+        <v>786.211047041681</v>
       </c>
       <c r="L92" s="88" t="n">
         <f>IF(D92="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C92-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
-        <v>35.8641010265209</v>
+        <v>4460.5443077058735</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="C93" s="73" t="n">
         <f>IF($G$40="pons",80%+20*0.5%,IF(80.5%+20*0.5%&lt;=100%,80.5%+20*0.5%,""))</f>
-        <v>0.905</v>
+        <v>0.9</v>
       </c>
       <c r="D93" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
-        <v>94999999.99999997</v>
+        <v>18367346.938775495</v>
       </c>
       <c r="E93" s="82" t="n">
         <f>IF(D93="","",IF(ABS(C93-$G$43)&lt;0.000001,$G$49,$G$50/D93))</f>
-        <v>37.13684210526317</v>
+        <v>5618.05555555556</v>
       </c>
       <c r="F93" s="79" t="n">
         <f>IF(AND(ISNUMBER(D93),D93&gt;0,ISNUMBER(E93)),E93/D93,"")</f>
-        <v>3.90914127423823e-7</v>
+        <v>0.0003058719135802474</v>
       </c>
       <c r="G93" s="79" t="n">
         <f>IF(AND(ISNUMBER(F93),ISNUMBER($D$55)),F93*$D$55,"")</f>
-        <v>0.00029427941553497865</v>
+        <v>0.0003059930868426371</v>
       </c>
       <c r="H93" s="82" t="n">
         <f>IF(ISNUMBER(F93),F93*$D$45,"")</f>
-        <v>390.914127423823</v>
+        <v>305871.91358024743</v>
       </c>
       <c r="I93" s="76" t="n">
         <f>IF(AND(ISNUMBER(H93),ISNUMBER($D$55)),H93*$D$55,"")</f>
-        <v>294279.4155349787</v>
+        <v>305993.0868426371</v>
       </c>
       <c r="J93" s="82" t="n">
         <f>IF(D93="","",E93-E92)</f>
-        <v>1.856842105263162</v>
+        <v>1202.1166909267358</v>
       </c>
       <c r="K93" s="82" t="n">
         <f>IF(D93="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L93-L92,J93*(1+$G$42)))</f>
-        <v>1.8614842105263198</v>
+        <v>1214.2592837643851</v>
       </c>
       <c r="L93" s="88" t="n">
         <f>IF(D93="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C93-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
-        <v>37.72558523704722</v>
+        <v>5674.803591470259</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="C94" s="73" t="n">
         <f>IF($G$40="pons",80%+21*0.5%,IF(80.5%+21*0.5%&lt;=100%,80.5%+21*0.5%,""))</f>
-        <v>0.91</v>
+        <v>0.905</v>
       </c>
       <c r="D94" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
-        <v>89999999.99999997</v>
+        <v>13367346.93877548</v>
       </c>
       <c r="E94" s="82" t="n">
         <f>IF(D94="","",IF(ABS(C94-$G$43)&lt;0.000001,$G$49,$G$50/D94))</f>
-        <v>39.20000000000001</v>
+        <v>7719.46564885498</v>
       </c>
       <c r="F94" s="79" t="n">
         <f>IF(AND(ISNUMBER(D94),D94&gt;0,ISNUMBER(E94)),E94/D94,"")</f>
-        <v>4.355555555555558e-7</v>
+        <v>0.0005774867431967861</v>
       </c>
       <c r="G94" s="79" t="n">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER($D$55)),F94*$D$55,"")</f>
-        <v>0.0003278853981732323</v>
+        <v>0.0005777155185421287</v>
       </c>
       <c r="H94" s="82" t="n">
         <f>IF(ISNUMBER(F94),F94*$D$45,"")</f>
-        <v>435.5555555555558</v>
+        <v>577486.7431967861</v>
       </c>
       <c r="I94" s="76" t="n">
         <f>IF(AND(ISNUMBER(H94),ISNUMBER($D$55)),H94*$D$55,"")</f>
-        <v>327885.39817323233</v>
+        <v>577715.5185421288</v>
       </c>
       <c r="J94" s="82" t="n">
         <f>IF(D94="","",E94-E93)</f>
-        <v>2.0631578947368396</v>
+        <v>2101.4100932994197</v>
       </c>
       <c r="K94" s="82" t="n">
         <f>IF(D94="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L94-L93,J94*(1+$G$42)))</f>
-        <v>2.0683157894736817</v>
+        <v>2122.6364578781886</v>
       </c>
       <c r="L94" s="88" t="n">
         <f>IF(D94="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C94-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
-        <v>39.7939010265209</v>
+        <v>7797.440049348447</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="C95" s="73" t="n">
         <f>IF($G$40="pons",80%+22*0.5%,IF(80.5%+22*0.5%&lt;=100%,80.5%+22*0.5%,""))</f>
-        <v>0.915</v>
+        <v>0.91</v>
       </c>
       <c r="D95" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
-        <v>84999999.99999997</v>
+        <v>8367346.93877548</v>
       </c>
       <c r="E95" s="82" t="n">
         <f>IF(D95="","",IF(ABS(C95-$G$43)&lt;0.000001,$G$49,$G$50/D95))</f>
-        <v>41.50588235294119</v>
+        <v>12332.317073170778</v>
       </c>
       <c r="F95" s="79" t="n">
         <f>IF(AND(ISNUMBER(D95),D95&gt;0,ISNUMBER(E95)),E95/D95,"")</f>
-        <v>4.883044982698965e-7</v>
+        <v>0.0014738622843545616</v>
       </c>
       <c r="G95" s="79" t="n">
         <f>IF(AND(ISNUMBER(F95),ISNUMBER($D$55)),F95*$D$55,"")</f>
-        <v>0.00036759470245026745</v>
+        <v>0.0014744461650359158</v>
       </c>
       <c r="H95" s="82" t="n">
         <f>IF(ISNUMBER(F95),F95*$D$45,"")</f>
-        <v>488.3044982698965</v>
+        <v>1473862.2843545617</v>
       </c>
       <c r="I95" s="76" t="n">
         <f>IF(AND(ISNUMBER(H95),ISNUMBER($D$55)),H95*$D$55,"")</f>
-        <v>367594.7024502674</v>
+        <v>1474446.1650359158</v>
       </c>
       <c r="J95" s="82" t="n">
         <f>IF(D95="","",E95-E94)</f>
-        <v>2.3058823529411825</v>
+        <v>4612.851424315798</v>
       </c>
       <c r="K95" s="82" t="n">
         <f>IF(D95="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L95-L94,J95*(1+$G$42)))</f>
-        <v>2.311647058823535</v>
+        <v>4659.445883147243</v>
       </c>
       <c r="L95" s="88" t="n">
         <f>IF(D95="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C95-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
-        <v>42.10554808534444</v>
+        <v>12456.88593249569</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="C96" s="73" t="n">
         <f>IF($G$40="pons",80%+23*0.5%,IF(80.5%+23*0.5%&lt;=100%,80.5%+23*0.5%,""))</f>
-        <v>0.92</v>
+        <v>0.915</v>
       </c>
       <c r="D96" s="76" t="n">
         <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
-        <v>79999999.99999996</v>
+        <v>3367346.93877548</v>
       </c>
       <c r="E96" s="82" t="n">
         <f>IF(D96="","",IF(ABS(C96-$G$43)&lt;0.000001,$G$49,$G$50/D96))</f>
-        <v>44.10000000000002</v>
+        <v>30643.939393939672</v>
       </c>
       <c r="F96" s="79" t="n">
         <f>IF(AND(ISNUMBER(D96),D96&gt;0,ISNUMBER(E96)),E96/D96,"")</f>
-        <v>5.512500000000005e-7</v>
+        <v>0.009100321395776106</v>
       </c>
       <c r="G96" s="79" t="n">
         <f>IF(AND(ISNUMBER(F96),ISNUMBER($D$55)),F96*$D$55,"")</f>
-        <v>0.0004149799570629973</v>
+        <v>0.00910392655069018</v>
       </c>
       <c r="H96" s="82" t="n">
         <f>IF(ISNUMBER(F96),F96*$D$45,"")</f>
-        <v>551.2500000000006</v>
+        <v>9100321.395776106</v>
       </c>
       <c r="I96" s="76" t="n">
         <f>IF(AND(ISNUMBER(H96),ISNUMBER($D$55)),H96*$D$55,"")</f>
-        <v>414979.95706299733</v>
+        <v>9103926.550690178</v>
       </c>
       <c r="J96" s="82" t="n">
         <f>IF(D96="","",E96-E95)</f>
-        <v>2.5941176470588303</v>
+        <v>18311.622320768896</v>
       </c>
       <c r="K96" s="82" t="n">
         <f>IF(D96="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L96-L95,J96*(1+$G$42)))</f>
-        <v>2.600602941176477</v>
+        <v>18496.588202796633</v>
       </c>
       <c r="L96" s="88" t="n">
         <f>IF(D96="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C96-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
-        <v>44.706151026520914</v>
+        <v>30953.474135292323</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="C97" s="73" t="n">
         <f>IF($G$40="pons",80%+24*0.5%,IF(80.5%+24*0.5%&lt;=100%,80.5%+24*0.5%,""))</f>
-        <v>0.925</v>
-      </c>
-      <c r="D97" s="76" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D97" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
-        <v>74999999.99999996</v>
-      </c>
-      <c r="E97" s="82" t="n">
+      </c>
+      <c r="E97" s="82" t="str">
         <f>IF(D97="","",IF(ABS(C97-$G$43)&lt;0.000001,$G$49,$G$50/D97))</f>
-        <v>47.04000000000003</v>
-      </c>
-      <c r="F97" s="79" t="n">
+      </c>
+      <c r="F97" s="79" t="str">
         <f>IF(AND(ISNUMBER(D97),D97&gt;0,ISNUMBER(E97)),E97/D97,"")</f>
-        <v>6.272000000000007e-7</v>
-      </c>
-      <c r="G97" s="79" t="n">
+      </c>
+      <c r="G97" s="79" t="str">
         <f>IF(AND(ISNUMBER(F97),ISNUMBER($D$55)),F97*$D$55,"")</f>
-        <v>0.00047215497336945483</v>
-      </c>
-      <c r="H97" s="82" t="n">
+      </c>
+      <c r="H97" s="82" t="str">
         <f>IF(ISNUMBER(F97),F97*$D$45,"")</f>
-        <v>627.2000000000007</v>
-      </c>
-      <c r="I97" s="76" t="n">
+      </c>
+      <c r="I97" s="76" t="str">
         <f>IF(AND(ISNUMBER(H97),ISNUMBER($D$55)),H97*$D$55,"")</f>
-        <v>472154.97336945485</v>
-      </c>
-      <c r="J97" s="82" t="n">
+      </c>
+      <c r="J97" s="82" t="str">
         <f>IF(D97="","",E97-E96)</f>
-        <v>2.940000000000005</v>
-      </c>
-      <c r="K97" s="82" t="n">
+      </c>
+      <c r="K97" s="82" t="str">
         <f>IF(D97="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L97-L96,J97*(1+$G$42)))</f>
-        <v>2.9473500000000046</v>
-      </c>
-      <c r="L97" s="88" t="n">
+      </c>
+      <c r="L97" s="88" t="str">
         <f>IF(D97="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C97-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
-        <v>47.65350102652092</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="C98" s="73" t="n">
         <f>IF($G$40="pons",80%+25*0.5%,IF(80.5%+25*0.5%&lt;=100%,80.5%+25*0.5%,""))</f>
-        <v>0.93</v>
-      </c>
-      <c r="D98" s="76" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="D98" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
-        <v>69999999.99999996</v>
-      </c>
-      <c r="E98" s="82" t="n">
+      </c>
+      <c r="E98" s="82" t="str">
         <f>IF(D98="","",IF(ABS(C98-$G$43)&lt;0.000001,$G$49,$G$50/D98))</f>
-        <v>50.400000000000034</v>
-      </c>
-      <c r="F98" s="79" t="n">
+      </c>
+      <c r="F98" s="79" t="str">
         <f>IF(AND(ISNUMBER(D98),D98&gt;0,ISNUMBER(E98)),E98/D98,"")</f>
-        <v>7.200000000000009e-7</v>
-      </c>
-      <c r="G98" s="79" t="n">
+      </c>
+      <c r="G98" s="79" t="str">
         <f>IF(AND(ISNUMBER(F98),ISNUMBER($D$55)),F98*$D$55,"")</f>
-        <v>0.0005420146377965681</v>
-      </c>
-      <c r="H98" s="82" t="n">
+      </c>
+      <c r="H98" s="82" t="str">
         <f>IF(ISNUMBER(F98),F98*$D$45,"")</f>
-        <v>720.0000000000009</v>
-      </c>
-      <c r="I98" s="76" t="n">
+      </c>
+      <c r="I98" s="76" t="str">
         <f>IF(AND(ISNUMBER(H98),ISNUMBER($D$55)),H98*$D$55,"")</f>
-        <v>542014.6377965681</v>
-      </c>
-      <c r="J98" s="82" t="n">
+      </c>
+      <c r="J98" s="82" t="str">
         <f>IF(D98="","",E98-E97)</f>
-        <v>3.3600000000000065</v>
-      </c>
-      <c r="K98" s="82" t="n">
+      </c>
+      <c r="K98" s="82" t="str">
         <f>IF(D98="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L98-L97,J98*(1+$G$42)))</f>
-        <v>3.3684000000000065</v>
-      </c>
-      <c r="L98" s="88" t="n">
+      </c>
+      <c r="L98" s="88" t="str">
         <f>IF(D98="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C98-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
-        <v>51.02190102652092</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="C99" s="73" t="n">
         <f>IF($G$40="pons",80%+26*0.5%,IF(80.5%+26*0.5%&lt;=100%,80.5%+26*0.5%,""))</f>
-        <v>0.935</v>
-      </c>
-      <c r="D99" s="76" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D99" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
-        <v>64999999.99999995</v>
-      </c>
-      <c r="E99" s="82" t="n">
+      </c>
+      <c r="E99" s="82" t="str">
         <f>IF(D99="","",IF(ABS(C99-$G$43)&lt;0.000001,$G$49,$G$50/D99))</f>
-        <v>54.27692307692312</v>
-      </c>
-      <c r="F99" s="79" t="n">
+      </c>
+      <c r="F99" s="79" t="str">
         <f>IF(AND(ISNUMBER(D99),D99&gt;0,ISNUMBER(E99)),E99/D99,"")</f>
-        <v>8.350295857988178e-7</v>
-      </c>
-      <c r="G99" s="79" t="n">
+      </c>
+      <c r="G99" s="79" t="str">
         <f>IF(AND(ISNUMBER(F99),ISNUMBER($D$55)),F99*$D$55,"")</f>
-        <v>0.0006286086923557833</v>
-      </c>
-      <c r="H99" s="82" t="n">
+      </c>
+      <c r="H99" s="82" t="str">
         <f>IF(ISNUMBER(F99),F99*$D$45,"")</f>
-        <v>835.0295857988178</v>
-      </c>
-      <c r="I99" s="76" t="n">
+      </c>
+      <c r="I99" s="76" t="str">
         <f>IF(AND(ISNUMBER(H99),ISNUMBER($D$55)),H99*$D$55,"")</f>
-        <v>628608.6923557833</v>
-      </c>
-      <c r="J99" s="82" t="n">
+      </c>
+      <c r="J99" s="82" t="str">
         <f>IF(D99="","",E99-E98)</f>
-        <v>3.8769230769230845</v>
-      </c>
-      <c r="K99" s="82" t="n">
+      </c>
+      <c r="K99" s="82" t="str">
         <f>IF(D99="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L99-L98,J99*(1+$G$42)))</f>
-        <v>3.886615384615392</v>
-      </c>
-      <c r="L99" s="88" t="n">
+      </c>
+      <c r="L99" s="88" t="str">
         <f>IF(D99="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C99-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
-        <v>54.90851641113632</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="C100" s="73" t="n">
         <f>IF($G$40="pons",80%+27*0.5%,IF(80.5%+27*0.5%&lt;=100%,80.5%+27*0.5%,""))</f>
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="D100" s="76" t="n">
+        <v>0.935</v>
+      </c>
+      <c r="D100" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
-        <v>59999999.99999994</v>
-      </c>
-      <c r="E100" s="82" t="n">
+      </c>
+      <c r="E100" s="82" t="str">
         <f>IF(D100="","",IF(ABS(C100-$G$43)&lt;0.000001,$G$49,$G$50/D100))</f>
-        <v>58.80000000000006</v>
-      </c>
-      <c r="F100" s="79" t="n">
+      </c>
+      <c r="F100" s="79" t="str">
         <f>IF(AND(ISNUMBER(D100),D100&gt;0,ISNUMBER(E100)),E100/D100,"")</f>
-        <v>9.80000000000002e-7</v>
-      </c>
-      <c r="G100" s="79" t="n">
+      </c>
+      <c r="G100" s="79" t="str">
         <f>IF(AND(ISNUMBER(F100),ISNUMBER($D$55)),F100*$D$55,"")</f>
-        <v>0.0007377421458897739</v>
-      </c>
-      <c r="H100" s="82" t="n">
+      </c>
+      <c r="H100" s="82" t="str">
         <f>IF(ISNUMBER(F100),F100*$D$45,"")</f>
-        <v>980.000000000002</v>
-      </c>
-      <c r="I100" s="76" t="n">
+      </c>
+      <c r="I100" s="76" t="str">
         <f>IF(AND(ISNUMBER(H100),ISNUMBER($D$55)),H100*$D$55,"")</f>
-        <v>737742.1458897738</v>
-      </c>
-      <c r="J100" s="82" t="n">
+      </c>
+      <c r="J100" s="82" t="str">
         <f>IF(D100="","",E100-E99)</f>
-        <v>4.5230769230769425</v>
-      </c>
-      <c r="K100" s="82" t="n">
+      </c>
+      <c r="K100" s="82" t="str">
         <f>IF(D100="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L100-L99,J100*(1+$G$42)))</f>
-        <v>4.534384615384635</v>
-      </c>
-      <c r="L100" s="88" t="n">
+      </c>
+      <c r="L100" s="88" t="str">
         <f>IF(D100="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C100-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
-        <v>59.44290102652096</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="C101" s="73" t="n">
         <f>IF($G$40="pons",80%+28*0.5%,IF(80.5%+28*0.5%&lt;=100%,80.5%+28*0.5%,""))</f>
-        <v>0.9450000000000001</v>
-      </c>
-      <c r="D101" s="76" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="D101" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
-        <v>54999999.99999994</v>
-      </c>
-      <c r="E101" s="82" t="n">
+      </c>
+      <c r="E101" s="82" t="str">
         <f>IF(D101="","",IF(ABS(C101-$G$43)&lt;0.000001,$G$49,$G$50/D101))</f>
-        <v>64.14545454545461</v>
-      </c>
-      <c r="F101" s="79" t="n">
+      </c>
+      <c r="F101" s="79" t="str">
         <f>IF(AND(ISNUMBER(D101),D101&gt;0,ISNUMBER(E101)),E101/D101,"")</f>
-        <v>0.0000011662809917355396</v>
-      </c>
-      <c r="G101" s="79" t="n">
+      </c>
+      <c r="G101" s="79" t="str">
         <f>IF(AND(ISNUMBER(F101),ISNUMBER($D$55)),F101*$D$55,"")</f>
-        <v>0.000877974124034111</v>
-      </c>
-      <c r="H101" s="82" t="n">
+      </c>
+      <c r="H101" s="82" t="str">
         <f>IF(ISNUMBER(F101),F101*$D$45,"")</f>
-        <v>1166.2809917355396</v>
-      </c>
-      <c r="I101" s="76" t="n">
+      </c>
+      <c r="I101" s="76" t="str">
         <f>IF(AND(ISNUMBER(H101),ISNUMBER($D$55)),H101*$D$55,"")</f>
-        <v>877974.124034111</v>
-      </c>
-      <c r="J101" s="82" t="n">
+      </c>
+      <c r="J101" s="82" t="str">
         <f>IF(D101="","",E101-E100)</f>
-        <v>5.345454545454551</v>
-      </c>
-      <c r="K101" s="82" t="n">
+      </c>
+      <c r="K101" s="82" t="str">
         <f>IF(D101="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L101-L100,J101*(1+$G$42)))</f>
-        <v>5.3588181818181875</v>
-      </c>
-      <c r="L101" s="88" t="n">
+      </c>
+      <c r="L101" s="88" t="str">
         <f>IF(D101="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C101-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
-        <v>64.80171920833914</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="C102" s="73" t="n">
         <f>IF($G$40="pons",80%+29*0.5%,IF(80.5%+29*0.5%&lt;=100%,80.5%+29*0.5%,""))</f>
-        <v>0.9500000000000001</v>
-      </c>
-      <c r="D102" s="76" t="n">
+        <v>0.9450000000000001</v>
+      </c>
+      <c r="D102" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
-        <v>49999999.99999993</v>
-      </c>
-      <c r="E102" s="82" t="n">
+      </c>
+      <c r="E102" s="82" t="str">
         <f>IF(D102="","",IF(ABS(C102-$G$43)&lt;0.000001,$G$49,$G$50/D102))</f>
-        <v>70.56000000000009</v>
-      </c>
-      <c r="F102" s="79" t="n">
+      </c>
+      <c r="F102" s="79" t="str">
         <f>IF(AND(ISNUMBER(D102),D102&gt;0,ISNUMBER(E102)),E102/D102,"")</f>
-        <v>0.0000014112000000000037</v>
-      </c>
-      <c r="G102" s="79" t="n">
+      </c>
+      <c r="G102" s="79" t="str">
         <f>IF(AND(ISNUMBER(F102),ISNUMBER($D$55)),F102*$D$55,"")</f>
-        <v>0.001062348690081275</v>
-      </c>
-      <c r="H102" s="82" t="n">
+      </c>
+      <c r="H102" s="82" t="str">
         <f>IF(ISNUMBER(F102),F102*$D$45,"")</f>
-        <v>1411.2000000000037</v>
-      </c>
-      <c r="I102" s="76" t="n">
+      </c>
+      <c r="I102" s="76" t="str">
         <f>IF(AND(ISNUMBER(H102),ISNUMBER($D$55)),H102*$D$55,"")</f>
-        <v>1062348.6900812748</v>
-      </c>
-      <c r="J102" s="82" t="n">
+      </c>
+      <c r="J102" s="82" t="str">
         <f>IF(D102="","",E102-E101)</f>
-        <v>6.414545454545475</v>
-      </c>
-      <c r="K102" s="82" t="n">
+      </c>
+      <c r="K102" s="82" t="str">
         <f>IF(D102="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L102-L101,J102*(1+$G$42)))</f>
-        <v>6.430581818181839</v>
-      </c>
-      <c r="L102" s="88" t="n">
+      </c>
+      <c r="L102" s="88" t="str">
         <f>IF(D102="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C102-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
-        <v>71.23230102652099</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="C103" s="73" t="n">
         <f>IF($G$40="pons",80%+30*0.5%,IF(80.5%+30*0.5%&lt;=100%,80.5%+30*0.5%,""))</f>
-        <v>0.9550000000000001</v>
-      </c>
-      <c r="D103" s="76" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="D103" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
-        <v>44999999.999999925</v>
-      </c>
-      <c r="E103" s="82" t="n">
+      </c>
+      <c r="E103" s="82" t="str">
         <f>IF(D103="","",IF(ABS(C103-$G$43)&lt;0.000001,$G$49,$G$50/D103))</f>
-        <v>78.40000000000013</v>
-      </c>
-      <c r="F103" s="79" t="n">
+      </c>
+      <c r="F103" s="79" t="str">
         <f>IF(AND(ISNUMBER(D103),D103&gt;0,ISNUMBER(E103)),E103/D103,"")</f>
-        <v>0.0000017422222222222282</v>
-      </c>
-      <c r="G103" s="79" t="n">
+      </c>
+      <c r="G103" s="79" t="str">
         <f>IF(AND(ISNUMBER(F103),ISNUMBER($D$55)),F103*$D$55,"")</f>
-        <v>0.001311541592692933</v>
-      </c>
-      <c r="H103" s="82" t="n">
+      </c>
+      <c r="H103" s="82" t="str">
         <f>IF(ISNUMBER(F103),F103*$D$45,"")</f>
-        <v>1742.222222222228</v>
-      </c>
-      <c r="I103" s="76" t="n">
+      </c>
+      <c r="I103" s="76" t="str">
         <f>IF(AND(ISNUMBER(H103),ISNUMBER($D$55)),H103*$D$55,"")</f>
-        <v>1311541.592692933</v>
-      </c>
-      <c r="J103" s="82" t="n">
+      </c>
+      <c r="J103" s="82" t="str">
         <f>IF(D103="","",E103-E102)</f>
-        <v>7.840000000000046</v>
-      </c>
-      <c r="K103" s="82" t="n">
+      </c>
+      <c r="K103" s="82" t="str">
         <f>IF(D103="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L103-L102,J103*(1+$G$42)))</f>
-        <v>7.859600000000046</v>
-      </c>
-      <c r="L103" s="88" t="n">
+      </c>
+      <c r="L103" s="88" t="str">
         <f>IF(D103="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C103-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
-        <v>79.09190102652103</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="C104" s="73" t="n">
         <f>IF($G$40="pons",80%+31*0.5%,IF(80.5%+31*0.5%&lt;=100%,80.5%+31*0.5%,""))</f>
-        <v>0.9600000000000001</v>
-      </c>
-      <c r="D104" s="76" t="n">
+        <v>0.9550000000000001</v>
+      </c>
+      <c r="D104" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
-        <v>39999999.999999925</v>
-      </c>
-      <c r="E104" s="82" t="n">
+      </c>
+      <c r="E104" s="82" t="str">
         <f>IF(D104="","",IF(ABS(C104-$G$43)&lt;0.000001,$G$49,$G$50/D104))</f>
-        <v>88.20000000000016</v>
-      </c>
-      <c r="F104" s="79" t="n">
+      </c>
+      <c r="F104" s="79" t="str">
         <f>IF(AND(ISNUMBER(D104),D104&gt;0,ISNUMBER(E104)),E104/D104,"")</f>
-        <v>0.000002205000000000008</v>
-      </c>
-      <c r="G104" s="79" t="n">
+      </c>
+      <c r="G104" s="79" t="str">
         <f>IF(AND(ISNUMBER(F104),ISNUMBER($D$55)),F104*$D$55,"")</f>
-        <v>0.0016599198282519938</v>
-      </c>
-      <c r="H104" s="82" t="n">
+      </c>
+      <c r="H104" s="82" t="str">
         <f>IF(ISNUMBER(F104),F104*$D$45,"")</f>
-        <v>2205.000000000008</v>
-      </c>
-      <c r="I104" s="76" t="n">
+      </c>
+      <c r="I104" s="76" t="str">
         <f>IF(AND(ISNUMBER(H104),ISNUMBER($D$55)),H104*$D$55,"")</f>
-        <v>1659919.8282519937</v>
-      </c>
-      <c r="J104" s="82" t="n">
+      </c>
+      <c r="J104" s="82" t="str">
         <f>IF(D104="","",E104-E103)</f>
-        <v>9.800000000000026</v>
-      </c>
-      <c r="K104" s="82" t="n">
+      </c>
+      <c r="K104" s="82" t="str">
         <f>IF(D104="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L104-L103,J104*(1+$G$42)))</f>
-        <v>9.824500000000025</v>
-      </c>
-      <c r="L104" s="88" t="n">
+      </c>
+      <c r="L104" s="88" t="str">
         <f>IF(D104="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C104-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
-        <v>88.91640102652106</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="C105" s="73" t="n">
         <f>IF($G$40="pons",80%+32*0.5%,IF(80.5%+32*0.5%&lt;=100%,80.5%+32*0.5%,""))</f>
-        <v>0.9650000000000001</v>
-      </c>
-      <c r="D105" s="76" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="D105" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
-        <v>34999999.99999992</v>
-      </c>
-      <c r="E105" s="82" t="n">
+      </c>
+      <c r="E105" s="82" t="str">
         <f>IF(D105="","",IF(ABS(C105-$G$43)&lt;0.000001,$G$49,$G$50/D105))</f>
-        <v>100.80000000000024</v>
-      </c>
-      <c r="F105" s="79" t="n">
+      </c>
+      <c r="F105" s="79" t="str">
         <f>IF(AND(ISNUMBER(D105),D105&gt;0,ISNUMBER(E105)),E105/D105,"")</f>
-        <v>0.0000028800000000000135</v>
-      </c>
-      <c r="G105" s="79" t="n">
+      </c>
+      <c r="G105" s="79" t="str">
         <f>IF(AND(ISNUMBER(F105),ISNUMBER($D$55)),F105*$D$55,"")</f>
-        <v>0.00216805855118628</v>
-      </c>
-      <c r="H105" s="82" t="n">
+      </c>
+      <c r="H105" s="82" t="str">
         <f>IF(ISNUMBER(F105),F105*$D$45,"")</f>
-        <v>2880.0000000000136</v>
-      </c>
-      <c r="I105" s="76" t="n">
+      </c>
+      <c r="I105" s="76" t="str">
         <f>IF(AND(ISNUMBER(H105),ISNUMBER($D$55)),H105*$D$55,"")</f>
-        <v>2168058.55118628</v>
-      </c>
-      <c r="J105" s="82" t="n">
+      </c>
+      <c r="J105" s="82" t="str">
         <f>IF(D105="","",E105-E104)</f>
-        <v>12.60000000000008</v>
-      </c>
-      <c r="K105" s="82" t="n">
+      </c>
+      <c r="K105" s="82" t="str">
         <f>IF(D105="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L105-L104,J105*(1+$G$42)))</f>
-        <v>12.631500000000079</v>
-      </c>
-      <c r="L105" s="88" t="n">
+      </c>
+      <c r="L105" s="88" t="str">
         <f>IF(D105="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C105-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
-        <v>101.54790102652113</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="C106" s="73" t="n">
         <f>IF($G$40="pons",80%+33*0.5%,IF(80.5%+33*0.5%&lt;=100%,80.5%+33*0.5%,""))</f>
-        <v>0.9700000000000001</v>
-      </c>
-      <c r="D106" s="76" t="n">
+        <v>0.9650000000000001</v>
+      </c>
+      <c r="D106" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
-        <v>29999999.999999914</v>
-      </c>
-      <c r="E106" s="82" t="n">
+      </c>
+      <c r="E106" s="82" t="str">
         <f>IF(D106="","",IF(ABS(C106-$G$43)&lt;0.000001,$G$49,$G$50/D106))</f>
-        <v>117.60000000000034</v>
-      </c>
-      <c r="F106" s="79" t="n">
+      </c>
+      <c r="F106" s="79" t="str">
         <f>IF(AND(ISNUMBER(D106),D106&gt;0,ISNUMBER(E106)),E106/D106,"")</f>
-        <v>0.000003920000000000023</v>
-      </c>
-      <c r="G106" s="79" t="n">
+      </c>
+      <c r="G106" s="79" t="str">
         <f>IF(AND(ISNUMBER(F106),ISNUMBER($D$55)),F106*$D$55,"")</f>
-        <v>0.0029509685835591064</v>
-      </c>
-      <c r="H106" s="82" t="n">
+      </c>
+      <c r="H106" s="82" t="str">
         <f>IF(ISNUMBER(F106),F106*$D$45,"")</f>
-        <v>3920.0000000000227</v>
-      </c>
-      <c r="I106" s="76" t="n">
+      </c>
+      <c r="I106" s="76" t="str">
         <f>IF(AND(ISNUMBER(H106),ISNUMBER($D$55)),H106*$D$55,"")</f>
-        <v>2950968.5835591066</v>
-      </c>
-      <c r="J106" s="82" t="n">
+      </c>
+      <c r="J106" s="82" t="str">
         <f>IF(D106="","",E106-E105)</f>
-        <v>16.800000000000097</v>
-      </c>
-      <c r="K106" s="82" t="n">
+      </c>
+      <c r="K106" s="82" t="str">
         <f>IF(D106="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L106-L105,J106*(1+$G$42)))</f>
-        <v>16.842000000000095</v>
-      </c>
-      <c r="L106" s="88" t="n">
+      </c>
+      <c r="L106" s="88" t="str">
         <f>IF(D106="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C106-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
-        <v>118.38990102652123</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="C107" s="73" t="n">
         <f>IF($G$40="pons",80%+34*0.5%,IF(80.5%+34*0.5%&lt;=100%,80.5%+34*0.5%,""))</f>
-        <v>0.9750000000000001</v>
-      </c>
-      <c r="D107" s="76" t="n">
+        <v>0.9700000000000001</v>
+      </c>
+      <c r="D107" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
-        <v>24999999.99999991</v>
-      </c>
-      <c r="E107" s="82" t="n">
+      </c>
+      <c r="E107" s="82" t="str">
         <f>IF(D107="","",IF(ABS(C107-$G$43)&lt;0.000001,$G$49,$G$50/D107))</f>
-        <v>141.12000000000052</v>
-      </c>
-      <c r="F107" s="79" t="n">
+      </c>
+      <c r="F107" s="79" t="str">
         <f>IF(AND(ISNUMBER(D107),D107&gt;0,ISNUMBER(E107)),E107/D107,"")</f>
-        <v>0.000005644800000000041</v>
-      </c>
-      <c r="G107" s="79" t="n">
+      </c>
+      <c r="G107" s="79" t="str">
         <f>IF(AND(ISNUMBER(F107),ISNUMBER($D$55)),F107*$D$55,"")</f>
-        <v>0.00424939476032512</v>
-      </c>
-      <c r="H107" s="82" t="n">
+      </c>
+      <c r="H107" s="82" t="str">
         <f>IF(ISNUMBER(F107),F107*$D$45,"")</f>
-        <v>5644.800000000041</v>
-      </c>
-      <c r="I107" s="76" t="n">
+      </c>
+      <c r="I107" s="76" t="str">
         <f>IF(AND(ISNUMBER(H107),ISNUMBER($D$55)),H107*$D$55,"")</f>
-        <v>4249394.76032512</v>
-      </c>
-      <c r="J107" s="82" t="n">
+      </c>
+      <c r="J107" s="82" t="str">
         <f>IF(D107="","",E107-E106)</f>
-        <v>23.52000000000018</v>
-      </c>
-      <c r="K107" s="82" t="n">
+      </c>
+      <c r="K107" s="82" t="str">
         <f>IF(D107="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L107-L106,J107*(1+$G$42)))</f>
-        <v>23.57880000000018</v>
-      </c>
-      <c r="L107" s="88" t="n">
+      </c>
+      <c r="L107" s="88" t="str">
         <f>IF(D107="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C107-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
-        <v>141.96870102652142</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="C108" s="73" t="n">
         <f>IF($G$40="pons",80%+35*0.5%,IF(80.5%+35*0.5%&lt;=100%,80.5%+35*0.5%,""))</f>
-        <v>0.9800000000000001</v>
-      </c>
-      <c r="D108" s="76" t="n">
+        <v>0.9750000000000001</v>
+      </c>
+      <c r="D108" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
-        <v>19999999.999999907</v>
-      </c>
-      <c r="E108" s="82" t="n">
+      </c>
+      <c r="E108" s="82" t="str">
         <f>IF(D108="","",IF(ABS(C108-$G$43)&lt;0.000001,$G$49,$G$50/D108))</f>
-        <v>176.40000000000083</v>
-      </c>
-      <c r="F108" s="79" t="n">
+      </c>
+      <c r="F108" s="79" t="str">
         <f>IF(AND(ISNUMBER(D108),D108&gt;0,ISNUMBER(E108)),E108/D108,"")</f>
-        <v>0.000008820000000000083</v>
-      </c>
-      <c r="G108" s="79" t="n">
+      </c>
+      <c r="G108" s="79" t="str">
         <f>IF(AND(ISNUMBER(F108),ISNUMBER($D$55)),F108*$D$55,"")</f>
-        <v>0.0066396793130080135</v>
-      </c>
-      <c r="H108" s="82" t="n">
+      </c>
+      <c r="H108" s="82" t="str">
         <f>IF(ISNUMBER(F108),F108*$D$45,"")</f>
-        <v>8820.000000000084</v>
-      </c>
-      <c r="I108" s="76" t="n">
+      </c>
+      <c r="I108" s="76" t="str">
         <f>IF(AND(ISNUMBER(H108),ISNUMBER($D$55)),H108*$D$55,"")</f>
-        <v>6639679.313008014</v>
-      </c>
-      <c r="J108" s="82" t="n">
+      </c>
+      <c r="J108" s="82" t="str">
         <f>IF(D108="","",E108-E107)</f>
-        <v>35.280000000000314</v>
-      </c>
-      <c r="K108" s="82" t="n">
+      </c>
+      <c r="K108" s="82" t="str">
         <f>IF(D108="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L108-L107,J108*(1+$G$42)))</f>
-        <v>35.368200000000314</v>
-      </c>
-      <c r="L108" s="88" t="n">
+      </c>
+      <c r="L108" s="88" t="str">
         <f>IF(D108="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C108-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
-        <v>177.33690102652173</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="C109" s="73" t="n">
         <f>IF($G$40="pons",80%+36*0.5%,IF(80.5%+36*0.5%&lt;=100%,80.5%+36*0.5%,""))</f>
-        <v>0.9850000000000001</v>
-      </c>
-      <c r="D109" s="76" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D109" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
-        <v>14999999.999999903</v>
-      </c>
-      <c r="E109" s="82" t="n">
+      </c>
+      <c r="E109" s="82" t="str">
         <f>IF(D109="","",IF(ABS(C109-$G$43)&lt;0.000001,$G$49,$G$50/D109))</f>
-        <v>235.20000000000152</v>
-      </c>
-      <c r="F109" s="79" t="n">
+      </c>
+      <c r="F109" s="79" t="str">
         <f>IF(AND(ISNUMBER(D109),D109&gt;0,ISNUMBER(E109)),E109/D109,"")</f>
-        <v>0.000015680000000000202</v>
-      </c>
-      <c r="G109" s="79" t="n">
+      </c>
+      <c r="G109" s="79" t="str">
         <f>IF(AND(ISNUMBER(F109),ISNUMBER($D$55)),F109*$D$55,"")</f>
-        <v>0.011803874334236509</v>
-      </c>
-      <c r="H109" s="82" t="n">
+      </c>
+      <c r="H109" s="82" t="str">
         <f>IF(ISNUMBER(F109),F109*$D$45,"")</f>
-        <v>15680.000000000202</v>
-      </c>
-      <c r="I109" s="76" t="n">
+      </c>
+      <c r="I109" s="76" t="str">
         <f>IF(AND(ISNUMBER(H109),ISNUMBER($D$55)),H109*$D$55,"")</f>
-        <v>11803874.334236508</v>
-      </c>
-      <c r="J109" s="82" t="n">
+      </c>
+      <c r="J109" s="82" t="str">
         <f>IF(D109="","",E109-E108)</f>
-        <v>58.80000000000069</v>
-      </c>
-      <c r="K109" s="82" t="n">
+      </c>
+      <c r="K109" s="82" t="str">
         <f>IF(D109="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L109-L108,J109*(1+$G$42)))</f>
-        <v>58.94700000000069</v>
-      </c>
-      <c r="L109" s="88" t="n">
+      </c>
+      <c r="L109" s="88" t="str">
         <f>IF(D109="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C109-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
-        <v>236.28390102652241</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="C110" s="73" t="n">
         <f>IF($G$40="pons",80%+37*0.5%,IF(80.5%+37*0.5%&lt;=100%,80.5%+37*0.5%,""))</f>
-        <v>0.99</v>
-      </c>
-      <c r="D110" s="76" t="n">
+        <v>0.9850000000000001</v>
+      </c>
+      <c r="D110" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
-        <v>10000000.00000001</v>
-      </c>
-      <c r="E110" s="82" t="n">
+      </c>
+      <c r="E110" s="82" t="str">
         <f>IF(D110="","",IF(ABS(C110-$G$43)&lt;0.000001,$G$49,$G$50/D110))</f>
-        <v>352.79999999999967</v>
-      </c>
-      <c r="F110" s="79" t="n">
+      </c>
+      <c r="F110" s="79" t="str">
         <f>IF(AND(ISNUMBER(D110),D110&gt;0,ISNUMBER(E110)),E110/D110,"")</f>
-        <v>0.00003527999999999993</v>
-      </c>
-      <c r="G110" s="79" t="n">
+      </c>
+      <c r="G110" s="79" t="str">
         <f>IF(AND(ISNUMBER(F110),ISNUMBER($D$55)),F110*$D$55,"")</f>
-        <v>0.026558717252031752</v>
-      </c>
-      <c r="H110" s="82" t="n">
+      </c>
+      <c r="H110" s="82" t="str">
         <f>IF(ISNUMBER(F110),F110*$D$45,"")</f>
-        <v>35279.999999999935</v>
-      </c>
-      <c r="I110" s="76" t="n">
+      </c>
+      <c r="I110" s="76" t="str">
         <f>IF(AND(ISNUMBER(H110),ISNUMBER($D$55)),H110*$D$55,"")</f>
-        <v>26558717.252031755</v>
-      </c>
-      <c r="J110" s="82" t="n">
+      </c>
+      <c r="J110" s="82" t="str">
         <f>IF(D110="","",E110-E109)</f>
-        <v>117.59999999999815</v>
-      </c>
-      <c r="K110" s="82" t="n">
+      </c>
+      <c r="K110" s="82" t="str">
         <f>IF(D110="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L110-L109,J110*(1+$G$42)))</f>
-        <v>117.89399999999813</v>
-      </c>
-      <c r="L110" s="88" t="n">
+      </c>
+      <c r="L110" s="88" t="str">
         <f>IF(D110="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C110-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
-        <v>354.17790102652054</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="C111" s="73" t="n">
         <f>IF($G$40="pons",80%+38*0.5%,IF(80.5%+38*0.5%&lt;=100%,80.5%+38*0.5%,""))</f>
-        <v>0.9950000000000001</v>
-      </c>
-      <c r="D111" s="76" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D111" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
-        <v>4999999.999999894</v>
-      </c>
-      <c r="E111" s="82" t="n">
+      </c>
+      <c r="E111" s="82" t="str">
         <f>IF(D111="","",IF(ABS(C111-$G$43)&lt;0.000001,$G$49,$G$50/D111))</f>
-        <v>705.600000000015</v>
-      </c>
-      <c r="F111" s="79" t="n">
+      </c>
+      <c r="F111" s="79" t="str">
         <f>IF(AND(ISNUMBER(D111),D111&gt;0,ISNUMBER(E111)),E111/D111,"")</f>
-        <v>0.000141120000000006</v>
-      </c>
-      <c r="G111" s="79" t="n">
+      </c>
+      <c r="G111" s="79" t="str">
         <f>IF(AND(ISNUMBER(F111),ISNUMBER($D$55)),F111*$D$55,"")</f>
-        <v>0.10623486900813173</v>
-      </c>
-      <c r="H111" s="82" t="n">
+      </c>
+      <c r="H111" s="82" t="str">
         <f>IF(ISNUMBER(F111),F111*$D$45,"")</f>
-        <v>141120.000000006</v>
-      </c>
-      <c r="I111" s="76" t="n">
+      </c>
+      <c r="I111" s="76" t="str">
         <f>IF(AND(ISNUMBER(H111),ISNUMBER($D$55)),H111*$D$55,"")</f>
-        <v>106234869.00813173</v>
-      </c>
-      <c r="J111" s="82" t="n">
+      </c>
+      <c r="J111" s="82" t="str">
         <f>IF(D111="","",E111-E110)</f>
-        <v>352.80000000001536</v>
-      </c>
-      <c r="K111" s="82" t="n">
+      </c>
+      <c r="K111" s="82" t="str">
         <f>IF(D111="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L111-L110,J111*(1+$G$42)))</f>
-        <v>353.68200000001536</v>
-      </c>
-      <c r="L111" s="88" t="n">
+      </c>
+      <c r="L111" s="88" t="str">
         <f>IF(D111="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C111-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
-        <v>707.859901026536</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="C112" s="73" t="n">
         <f>IF($G$40="pons",80%+39*0.5%,IF(80.5%+39*0.5%&lt;=100%,80.5%+39*0.5%,""))</f>
-        <v>1</v>
+        <v>0.9950000000000001</v>
       </c>
       <c r="D112" s="76" t="str">
         <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
@@ -4025,8 +3890,9 @@
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="C113" s="74" t="str">
+      <c r="C113" s="74" t="n">
         <f>IF($G$40="pons",80%+40*0.5%,IF(80.5%+40*0.5%&lt;=100%,80.5%+40*0.5%,""))</f>
+        <v>1</v>
       </c>
       <c r="D113" s="77" t="str">
         <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
@@ -4129,31 +3995,31 @@
     <row r="118" ht="20" customHeight="1">
       <c r="C118" s="72" t="n">
         <f>IF($G$40="pons",$G$43,80%)</f>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D118" s="75" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C118)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C118)-$G$51,IF(ABS(C118-$G$43)&lt;0.000001,$G$48,$D$45*(1-C118))))</f>
-        <v>200000000</v>
+        <v>204081632.65306118</v>
       </c>
       <c r="E118" s="81" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C118)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C118)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C118-$G$43)&lt;0.000001,$G$49,$G$50/D118))</f>
-        <v>17.64</v>
+        <v>505.625</v>
       </c>
       <c r="F118" s="78" t="n">
         <f>IF(AND(ISNUMBER(D118),D118&gt;0,ISNUMBER(E118)),E118/D118,"")</f>
-        <v>8.820000000000001e-8</v>
+        <v>0.0000024775625000000006</v>
       </c>
       <c r="G118" s="78" t="n">
         <f>IF(AND(ISNUMBER(F118),ISNUMBER($D$55)),F118*$D$55,"")</f>
-        <v>0.00006639679313007951</v>
+        <v>0.0000024785440034253568</v>
       </c>
       <c r="H118" s="81" t="n">
         <f>IF(ISNUMBER(F118),F118*$D$45,"")</f>
-        <v>88.2</v>
+        <v>2477.5625000000005</v>
       </c>
       <c r="I118" s="75" t="n">
         <f>IF(AND(ISNUMBER(H118),ISNUMBER($D$55)),H118*$D$55,"")</f>
-        <v>66396.79313007952</v>
+        <v>2478.5440034253565</v>
       </c>
       <c r="J118" s="72" t="n">
         <f>IF(H$118&gt;0,1-H118/H$118,"")</f>
@@ -4169,31 +4035,31 @@
       </c>
       <c r="D119" s="76" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C119)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C119)-$G$51,IF(ABS(C119-$G$43)&lt;0.000001,$G$48,$D$45*(1-C119))))</f>
-        <v>300000000.00000006</v>
+        <v>218367346.93877557</v>
       </c>
       <c r="E119" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C119)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C119)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C119-$G$43)&lt;0.000001,$G$49,$G$50/D119))</f>
-        <v>11.759999999999998</v>
+        <v>472.5467289719625</v>
       </c>
       <c r="F119" s="79" t="n">
         <f>IF(AND(ISNUMBER(D119),D119&gt;0,ISNUMBER(E119)),E119/D119,"")</f>
-        <v>3.919999999999999e-8</v>
+        <v>0.0000021639990392173977</v>
       </c>
       <c r="G119" s="79" t="n">
         <f>IF(AND(ISNUMBER(F119),ISNUMBER($D$55)),F119*$D$55,"")</f>
-        <v>0.000029509685835590883</v>
+        <v>0.000002164856322321037</v>
       </c>
       <c r="H119" s="82" t="n">
         <f>IF(ISNUMBER(F119),F119*$D$45,"")</f>
-        <v>39.19999999999999</v>
+        <v>2163.9990392173977</v>
       </c>
       <c r="I119" s="76" t="n">
         <f>IF(AND(ISNUMBER(H119),ISNUMBER($D$55)),H119*$D$55,"")</f>
-        <v>29509.685835590884</v>
+        <v>2164.8563223210367</v>
       </c>
       <c r="J119" s="73" t="n">
         <f>IF(H$118&gt;0,1-H119/H$118,"")</f>
-        <v>0.5555555555555557</v>
+        <v>0.126561271726789</v>
       </c>
       <c r="K119" s="82" t="str"/>
       <c r="L119" s="82" t="str"/>
@@ -4205,31 +4071,31 @@
       </c>
       <c r="D120" s="76" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C120)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C120)-$G$51,IF(ABS(C120-$G$43)&lt;0.000001,$G$48,$D$45*(1-C120))))</f>
-        <v>400000000</v>
+        <v>318367346.93877554</v>
       </c>
       <c r="E120" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C120)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C120)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C120-$G$43)&lt;0.000001,$G$49,$G$50/D120))</f>
-        <v>8.82</v>
+        <v>324.1185897435897</v>
       </c>
       <c r="F120" s="79" t="n">
         <f>IF(AND(ISNUMBER(D120),D120&gt;0,ISNUMBER(E120)),E120/D120,"")</f>
-        <v>2.2050000000000002e-8</v>
+        <v>0.0000010180648011176856</v>
       </c>
       <c r="G120" s="79" t="n">
         <f>IF(AND(ISNUMBER(F120),ISNUMBER($D$55)),F120*$D$55,"")</f>
-        <v>0.000016599198282519877</v>
+        <v>0.000001018468114491024</v>
       </c>
       <c r="H120" s="82" t="n">
         <f>IF(ISNUMBER(F120),F120*$D$45,"")</f>
-        <v>22.05</v>
+        <v>1018.0648011176856</v>
       </c>
       <c r="I120" s="76" t="n">
         <f>IF(AND(ISNUMBER(H120),ISNUMBER($D$55)),H120*$D$55,"")</f>
-        <v>16599.19828251988</v>
+        <v>1018.468114491024</v>
       </c>
       <c r="J120" s="73" t="n">
         <f>IF(H$118&gt;0,1-H120/H$118,"")</f>
-        <v>0.75</v>
+        <v>0.5890861275476661</v>
       </c>
       <c r="K120" s="82" t="str"/>
       <c r="L120" s="82" t="str"/>
@@ -4241,31 +4107,31 @@
       </c>
       <c r="D121" s="76" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C121)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C121)-$G$51,IF(ABS(C121-$G$43)&lt;0.000001,$G$48,$D$45*(1-C121))))</f>
-        <v>500000000</v>
+        <v>418367346.93877554</v>
       </c>
       <c r="E121" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C121)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C121)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C121-$G$43)&lt;0.000001,$G$49,$G$50/D121))</f>
-        <v>7.056</v>
+        <v>246.64634146341461</v>
       </c>
       <c r="F121" s="79" t="n">
         <f>IF(AND(ISNUMBER(D121),D121&gt;0,ISNUMBER(E121)),E121/D121,"")</f>
-        <v>1.4112000000000001e-8</v>
+        <v>5.895449137418202e-7</v>
       </c>
       <c r="G121" s="79" t="n">
         <f>IF(AND(ISNUMBER(F121),ISNUMBER($D$55)),F121*$D$55,"")</f>
-        <v>0.000010623486900812722</v>
+        <v>5.897784660143618e-7</v>
       </c>
       <c r="H121" s="82" t="n">
         <f>IF(ISNUMBER(F121),F121*$D$45,"")</f>
-        <v>14.112</v>
+        <v>589.5449137418202</v>
       </c>
       <c r="I121" s="76" t="n">
         <f>IF(AND(ISNUMBER(H121),ISNUMBER($D$55)),H121*$D$55,"")</f>
-        <v>10623.48690081272</v>
+        <v>589.7784660143618</v>
       </c>
       <c r="J121" s="73" t="n">
         <f>IF(H$118&gt;0,1-H121/H$118,"")</f>
-        <v>0.84</v>
+        <v>0.7620464009518145</v>
       </c>
       <c r="K121" s="82" t="str"/>
       <c r="L121" s="82" t="str"/>
@@ -4277,31 +4143,31 @@
       </c>
       <c r="D122" s="76" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C122)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C122)-$G$51,IF(ABS(C122-$G$43)&lt;0.000001,$G$48,$D$45*(1-C122))))</f>
-        <v>600000000</v>
+        <v>518367346.93877554</v>
       </c>
       <c r="E122" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C122)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C122)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C122-$G$43)&lt;0.000001,$G$49,$G$50/D122))</f>
-        <v>5.88</v>
+        <v>199.06496062992125</v>
       </c>
       <c r="F122" s="79" t="n">
         <f>IF(AND(ISNUMBER(D122),D122&gt;0,ISNUMBER(E122)),E122/D122,"")</f>
-        <v>9.8e-9</v>
+        <v>3.8402295554591103e-7</v>
       </c>
       <c r="G122" s="79" t="n">
         <f>IF(AND(ISNUMBER(F122),ISNUMBER($D$55)),F122*$D$55,"")</f>
-        <v>0.000007377421458897723</v>
+        <v>3.8417508888110793e-7</v>
       </c>
       <c r="H122" s="82" t="n">
         <f>IF(ISNUMBER(F122),F122*$D$45,"")</f>
-        <v>9.8</v>
+        <v>384.02295554591103</v>
       </c>
       <c r="I122" s="76" t="n">
         <f>IF(AND(ISNUMBER(H122),ISNUMBER($D$55)),H122*$D$55,"")</f>
-        <v>7377.421458897724</v>
+        <v>384.1750888811079</v>
       </c>
       <c r="J122" s="73" t="n">
         <f>IF(H$118&gt;0,1-H122/H$118,"")</f>
-        <v>0.8888888888888888</v>
+        <v>0.84499968999938</v>
       </c>
       <c r="K122" s="82" t="str"/>
       <c r="L122" s="82" t="str"/>
@@ -4313,31 +4179,31 @@
       </c>
       <c r="D123" s="76" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C123)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C123)-$G$51,IF(ABS(C123-$G$43)&lt;0.000001,$G$48,$D$45*(1-C123))))</f>
-        <v>700000000</v>
+        <v>618367346.9387755</v>
       </c>
       <c r="E123" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C123)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C123)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C123-$G$43)&lt;0.000001,$G$49,$G$50/D123))</f>
-        <v>5.04</v>
+        <v>166.87293729372936</v>
       </c>
       <c r="F123" s="79" t="n">
         <f>IF(AND(ISNUMBER(D123),D123&gt;0,ISNUMBER(E123)),E123/D123,"")</f>
-        <v>7.2e-9</v>
+        <v>2.6986052565652603e-7</v>
       </c>
       <c r="G123" s="79" t="n">
         <f>IF(AND(ISNUMBER(F123),ISNUMBER($D$55)),F123*$D$55,"")</f>
-        <v>0.000005420146377965674</v>
+        <v>2.699674327598989e-7</v>
       </c>
       <c r="H123" s="82" t="n">
         <f>IF(ISNUMBER(F123),F123*$D$45,"")</f>
-        <v>7.2</v>
+        <v>269.860525656526</v>
       </c>
       <c r="I123" s="76" t="n">
         <f>IF(AND(ISNUMBER(H123),ISNUMBER($D$55)),H123*$D$55,"")</f>
-        <v>5420.146377965674</v>
+        <v>269.96743275989894</v>
       </c>
       <c r="J123" s="73" t="n">
         <f>IF(H$118&gt;0,1-H123/H$118,"")</f>
-        <v>0.9183673469387755</v>
+        <v>0.8910782167325644</v>
       </c>
       <c r="K123" s="82" t="str"/>
       <c r="L123" s="82" t="str"/>
@@ -4349,31 +4215,31 @@
       </c>
       <c r="D124" s="76" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C124)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C124)-$G$51,IF(ABS(C124-$G$43)&lt;0.000001,$G$48,$D$45*(1-C124))))</f>
-        <v>800000000</v>
+        <v>718367346.9387755</v>
       </c>
       <c r="E124" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C124)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C124)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C124-$G$43)&lt;0.000001,$G$49,$G$50/D124))</f>
-        <v>4.41</v>
+        <v>143.6434659090909</v>
       </c>
       <c r="F124" s="79" t="n">
         <f>IF(AND(ISNUMBER(D124),D124&gt;0,ISNUMBER(E124)),E124/D124,"")</f>
-        <v>5.5125000000000006e-9</v>
+        <v>1.9995823379390494e-7</v>
       </c>
       <c r="G124" s="79" t="n">
         <f>IF(AND(ISNUMBER(F124),ISNUMBER($D$55)),F124*$D$55,"")</f>
-        <v>0.000004149799570629969</v>
+        <v>2.0003744862355986e-7</v>
       </c>
       <c r="H124" s="82" t="n">
         <f>IF(ISNUMBER(F124),F124*$D$45,"")</f>
-        <v>5.5125</v>
+        <v>199.95823379390495</v>
       </c>
       <c r="I124" s="76" t="n">
         <f>IF(AND(ISNUMBER(H124),ISNUMBER($D$55)),H124*$D$55,"")</f>
-        <v>4149.79957062997</v>
+        <v>200.03744862355987</v>
       </c>
       <c r="J124" s="73" t="n">
         <f>IF(H$118&gt;0,1-H124/H$118,"")</f>
-        <v>0.9375</v>
+        <v>0.9192923553719008</v>
       </c>
       <c r="K124" s="82" t="str"/>
       <c r="L124" s="82" t="str"/>
@@ -4385,31 +4251,31 @@
       </c>
       <c r="D125" s="76" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C125)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C125)-$G$51,IF(ABS(C125-$G$43)&lt;0.000001,$G$48,$D$45*(1-C125))))</f>
-        <v>900000000</v>
+        <v>818367346.9387755</v>
       </c>
       <c r="E125" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C125)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C125)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C125-$G$43)&lt;0.000001,$G$49,$G$50/D125))</f>
-        <v>3.92</v>
+        <v>126.09102244389028</v>
       </c>
       <c r="F125" s="79" t="n">
         <f>IF(AND(ISNUMBER(D125),D125&gt;0,ISNUMBER(E125)),E125/D125,"")</f>
-        <v>4.355555555555555e-9</v>
+        <v>1.5407631171447938e-7</v>
       </c>
       <c r="G125" s="79" t="n">
         <f>IF(AND(ISNUMBER(F125),ISNUMBER($D$55)),F125*$D$55,"")</f>
-        <v>0.000003278853981732321</v>
+        <v>1.54137350105121e-7</v>
       </c>
       <c r="H125" s="82" t="n">
         <f>IF(ISNUMBER(F125),F125*$D$45,"")</f>
-        <v>4.355555555555555</v>
+        <v>154.07631171447937</v>
       </c>
       <c r="I125" s="76" t="n">
         <f>IF(AND(ISNUMBER(H125),ISNUMBER($D$55)),H125*$D$55,"")</f>
-        <v>3278.8539817323212</v>
+        <v>154.137350105121</v>
       </c>
       <c r="J125" s="73" t="n">
         <f>IF(H$118&gt;0,1-H125/H$118,"")</f>
-        <v>0.9506172839506173</v>
+        <v>0.9378113320190795</v>
       </c>
       <c r="K125" s="82" t="str"/>
       <c r="L125" s="82" t="str"/>
@@ -4421,31 +4287,31 @@
       </c>
       <c r="D126" s="77" t="n">
         <f>IF($G$40="four-stock",$G$48+($G$43-C126)*$D$45*(1-$J$47),IF($G$40="pons",$D$45*(1-C126)-$G$51,IF(ABS(C126-$G$43)&lt;0.000001,$G$48,$D$45*(1-C126))))</f>
-        <v>1000000000</v>
+        <v>918367346.9387755</v>
       </c>
       <c r="E126" s="83" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C126)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C126)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C126-$G$43)&lt;0.000001,$G$49,$G$50/D126))</f>
-        <v>3.528</v>
+        <v>112.36111111111111</v>
       </c>
       <c r="F126" s="80" t="n">
         <f>IF(AND(ISNUMBER(D126),D126&gt;0,ISNUMBER(E126)),E126/D126,"")</f>
-        <v>3.5280000000000002e-9</v>
+        <v>1.2234876543209877e-7</v>
       </c>
       <c r="G126" s="80" t="n">
         <f>IF(AND(ISNUMBER(F126),ISNUMBER($D$55)),F126*$D$55,"")</f>
-        <v>0.0000026558717252031804</v>
+        <v>1.2239723473705465e-7</v>
       </c>
       <c r="H126" s="83" t="n">
         <f>IF(ISNUMBER(F126),F126*$D$45,"")</f>
-        <v>3.528</v>
+        <v>122.34876543209877</v>
       </c>
       <c r="I126" s="77" t="n">
         <f>IF(AND(ISNUMBER(H126),ISNUMBER($D$55)),H126*$D$55,"")</f>
-        <v>2655.87172520318</v>
+        <v>122.39723473705463</v>
       </c>
       <c r="J126" s="74" t="n">
         <f>IF(H$118&gt;0,1-H126/H$118,"")</f>
-        <v>0.96</v>
+        <v>0.9506172839506173</v>
       </c>
       <c r="K126" s="83" t="str"/>
       <c r="L126" s="83" t="str">
@@ -4896,7 +4762,7 @@
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation type="list" sqref="D7">
-      <formula1>'Quote参数'!$C$14:$C$22</formula1>
+      <formula1>'Quote参数'!$C$14:$C$23</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="D8">
       <formula1>0</formula1>
@@ -6559,6 +6425,114 @@
         <x:v>https://docs.ponsfamily.com/v2</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="C23" t="str">
+        <x:v>Pons V2 / USDG</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>ponsv2-usdg</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>USDG</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</x:v>
+      </x:c>
+      <x:c r="H23" t="n">
+        <x:v>1.0003961568781237</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>2580.0817123580937</x:v>
+      </x:c>
+      <x:c r="J23" t="n">
+        <x:v>46285.27349457176</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>USDG 按 1 USD 估算；https://www.coingecko.com/en/coins/global-dollar</x:v>
+      </x:c>
+      <x:c r="L23" t="str">
+        <x:v>pons</x:v>
+      </x:c>
+      <x:c r="M23" t="n">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="N23" t="n">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="O23" t="n">
+        <x:v>202.25</x:v>
+      </x:c>
+      <x:c r="P23" t="n">
+        <x:v>202250000000</x:v>
+      </x:c>
+      <x:c r="Q23" t="n">
+        <x:v>0.7142857142857143</x:v>
+      </x:c>
+      <x:c r="R23" t="n">
+        <x:v>204081632.65306124</x:v>
+      </x:c>
+      <x:c r="S23" t="n">
+        <x:v>505.625</x:v>
+      </x:c>
+      <x:c r="T23" t="n">
+        <x:v>103188775510.20409</x:v>
+      </x:c>
+      <x:c r="U23" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="V23" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="W23" t="n">
+        <x:v>510.7323232323232</x:v>
+      </x:c>
+      <x:c r="X23" t="n">
+        <x:v>81632653.06122449</x:v>
+      </x:c>
+      <x:c r="Y23" t="n">
+        <x:v>112.36111111111111</x:v>
+      </x:c>
+      <x:c r="Z23" t="n">
+        <x:v>505.625</x:v>
+      </x:c>
+      <x:c r="AA23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD23" t="str">
+        <x:v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</x:v>
+      </x:c>
+      <x:c r="AE23" t="str">
+        <x:v>区块 68,708,148；USDG 6 decimals</x:v>
+      </x:c>
+      <x:c r="AF23" t="str">
+        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      </x:c>
+      <x:c r="AG23"/>
+      <x:c r="AH23" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AI23" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+      <x:c r="AJ23" t="str">
+        <x:v>quote</x:v>
+      </x:c>
+      <x:c r="AK23" t="str">
+        <x:v>Pons V2 手续费始终按 Quote leg 计收；Hook 暂存的 Meme 费用会在池内转换回 Quote</x:v>
+      </x:c>
+      <x:c r="AL23" t="str">
+        <x:v>https://docs.ponsfamily.com/v2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="C3:M3"/>

--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R9628a35141504f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R3db615e523e9497d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Refa2ce57623f4d9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R9e1971b00c5f408f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D18" s="53" t="n">
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>52441.86394281925</v>
+        <v>689114.823085108</v>
       </c>
       <c r="E18" s="48" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J18" s="62" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>55300.72903151572</v>
+        <v>692225.910545684</v>
       </c>
       <c r="K18" s="48" t="str">
         <v>USDT</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D19" s="63" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>52462.63914792182</v>
+        <v>689387.8206620901</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D22" s="65" t="n">
         <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",($G$50/$J$51-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
-        <v>12456.88593249569</v>
+        <v>199310.17491993104</v>
       </c>
       <c r="E22" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D23" s="65" t="n">
         <f>IF($D$51="可达",$J$41*MAX(0,$G$7-1),"")</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
       <c r="E23" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D24" s="65" t="n">
         <f>IF($D$51="可达",$J$52*$D$29,"")</f>
-        <v>29477.245687091236</v>
+        <v>471635.93099345977</v>
       </c>
       <c r="E24" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1396,7 +1396,7 @@
       <c r="F37" s="3"/>
       <c r="G37" s="65" t="n">
         <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,23,FALSE))</f>
-        <v>112.36111111111111</v>
+        <v>1797.7777777777778</v>
       </c>
       <c r="H37" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J41" s="49" t="n">
         <f>IF($G$40="pons",$G$49/(1-$G$41-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$53*(1+$G$41+$J$46),$G$52))</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
       <c r="K41" s="49"/>
       <c r="L41" s="49"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G45" s="49" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,13,FALSE)</f>
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="49" t="str">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G46" s="49" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,14,FALSE)</f>
-        <v>202250000000</v>
+        <v>3236000000000</v>
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="49" t="str">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G49" s="49" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,17,FALSE)</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="49"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G50" s="49" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,18,FALSE)</f>
-        <v>103188775510.20409</v>
+        <v>1651020408163.2654</v>
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="49" t="str">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G52" s="49" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,21,FALSE)</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="49" t="str">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="J52" s="49" t="n">
         <f>IF($D$51="可达",$G$50/$J$50^2*$D$45,"")</f>
-        <v>1473862.2843545617</v>
+        <v>23581796.549672987</v>
       </c>
       <c r="K52" s="49"/>
       <c r="L52" s="49"/>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G53" s="49" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,24,FALSE)</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="H53" s="49"/>
       <c r="I53" s="49"/>
@@ -1874,23 +1874,23 @@
       </c>
       <c r="E59" s="81" t="n">
         <f>$G$46/D59</f>
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="F59" s="78" t="n">
         <f>IF(AND(ISNUMBER(D59),D59&gt;0,ISNUMBER(E59)),E59/D59,"")</f>
-        <v>2.0225e-7</v>
+        <v>0.000003236</v>
       </c>
       <c r="G59" s="78" t="n">
         <f>IF(AND(ISNUMBER(F59),ISNUMBER($D$55)),F59*$D$55,"")</f>
-        <v>2.0233012272860051e-7</v>
+        <v>0.0000032372819636576082</v>
       </c>
       <c r="H59" s="81" t="n">
         <f>IF(ISNUMBER(F59),F59*$D$45,"")</f>
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="I59" s="75" t="n">
         <f>IF(AND(ISNUMBER(H59),ISNUMBER($D$55)),H59*$D$55,"")</f>
-        <v>202.33012272860051</v>
+        <v>3237.2819636576082</v>
       </c>
       <c r="J59" s="81" t="n">
         <f>0</f>
@@ -1916,35 +1916,35 @@
       </c>
       <c r="E60" s="82" t="n">
         <f>$G$46/D60</f>
-        <v>224.72222222222223</v>
+        <v>3595.5555555555557</v>
       </c>
       <c r="F60" s="79" t="n">
         <f>IF(AND(ISNUMBER(D60),D60&gt;0,ISNUMBER(E60)),E60/D60,"")</f>
-        <v>2.496913580246914e-7</v>
+        <v>0.000003995061728395062</v>
       </c>
       <c r="G60" s="79" t="n">
         <f>IF(AND(ISNUMBER(F60),ISNUMBER($D$55)),F60*$D$55,"")</f>
-        <v>2.497902749735809e-7</v>
+        <v>0.000003996644399577294</v>
       </c>
       <c r="H60" s="82" t="n">
         <f>IF(ISNUMBER(F60),F60*$D$45,"")</f>
-        <v>249.6913580246914</v>
+        <v>3995.0617283950623</v>
       </c>
       <c r="I60" s="76" t="n">
         <f>IF(AND(ISNUMBER(H60),ISNUMBER($D$55)),H60*$D$55,"")</f>
-        <v>249.79027497358092</v>
+        <v>3996.6443995772947</v>
       </c>
       <c r="J60" s="82" t="n">
         <f>E60-E59</f>
-        <v>22.47222222222223</v>
+        <v>359.55555555555566</v>
       </c>
       <c r="K60" s="82" t="n">
         <f>IF($G$40="pons",J60/(1-$G$41-$J$48),J60*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>22.69921436588104</v>
+        <v>363.18742985409665</v>
       </c>
       <c r="L60" s="88" t="n">
         <f>SUM($K$59:K60)</f>
-        <v>22.69921436588104</v>
+        <v>363.18742985409665</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -1958,35 +1958,35 @@
       </c>
       <c r="E61" s="82" t="n">
         <f>$G$46/D61</f>
-        <v>252.8125</v>
+        <v>4045</v>
       </c>
       <c r="F61" s="79" t="n">
         <f>IF(AND(ISNUMBER(D61),D61&gt;0,ISNUMBER(E61)),E61/D61,"")</f>
-        <v>3.16015625e-7</v>
+        <v>0.00000505625</v>
       </c>
       <c r="G61" s="79" t="n">
         <f>IF(AND(ISNUMBER(F61),ISNUMBER($D$55)),F61*$D$55,"")</f>
-        <v>3.161408167634383e-7</v>
+        <v>0.0000050582530682150125</v>
       </c>
       <c r="H61" s="82" t="n">
         <f>IF(ISNUMBER(F61),F61*$D$45,"")</f>
-        <v>316.015625</v>
+        <v>5056.25</v>
       </c>
       <c r="I61" s="76" t="n">
         <f>IF(AND(ISNUMBER(H61),ISNUMBER($D$55)),H61*$D$55,"")</f>
-        <v>316.1408167634383</v>
+        <v>5058.253068215013</v>
       </c>
       <c r="J61" s="82" t="n">
         <f>E61-E60</f>
-        <v>28.09027777777777</v>
+        <v>449.44444444444434</v>
       </c>
       <c r="K61" s="82" t="n">
         <f>IF($G$40="pons",J61/(1-$G$41-$J$48),J61*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>28.374017957351285</v>
+        <v>453.98428731762056</v>
       </c>
       <c r="L61" s="88" t="n">
         <f>SUM($K$59:K61)</f>
-        <v>51.073232323232325</v>
+        <v>817.1717171717172</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2000,35 +2000,35 @@
       </c>
       <c r="E62" s="82" t="n">
         <f>$G$46/D62</f>
-        <v>288.92857142857144</v>
+        <v>4622.857142857143</v>
       </c>
       <c r="F62" s="79" t="n">
         <f>IF(AND(ISNUMBER(D62),D62&gt;0,ISNUMBER(E62)),E62/D62,"")</f>
-        <v>4.1275510204081637e-7</v>
+        <v>0.000006604081632653062</v>
       </c>
       <c r="G62" s="79" t="n">
         <f>IF(AND(ISNUMBER(F62),ISNUMBER($D$55)),F62*$D$55,"")</f>
-        <v>4.1291861781347046e-7</v>
+        <v>0.0000066066978850155274</v>
       </c>
       <c r="H62" s="82" t="n">
         <f>IF(ISNUMBER(F62),F62*$D$45,"")</f>
-        <v>412.7551020408164</v>
+        <v>6604.081632653062</v>
       </c>
       <c r="I62" s="76" t="n">
         <f>IF(AND(ISNUMBER(H62),ISNUMBER($D$55)),H62*$D$55,"")</f>
-        <v>412.91861781347046</v>
+        <v>6606.697885015527</v>
       </c>
       <c r="J62" s="82" t="n">
         <f>E62-E61</f>
-        <v>36.116071428571445</v>
+        <v>577.8571428571431</v>
       </c>
       <c r="K62" s="82" t="n">
         <f>IF($G$40="pons",J62/(1-$G$41-$J$48),J62*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>36.480880230880246</v>
+        <v>583.6940836940839</v>
       </c>
       <c r="L62" s="88" t="n">
         <f>SUM($K$59:K62)</f>
-        <v>87.55411255411258</v>
+        <v>1400.8658008658012</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2042,35 +2042,35 @@
       </c>
       <c r="E63" s="82" t="n">
         <f>$G$46/D63</f>
-        <v>337.0833333333333</v>
+        <v>5393.333333333333</v>
       </c>
       <c r="F63" s="79" t="n">
         <f>IF(AND(ISNUMBER(D63),D63&gt;0,ISNUMBER(E63)),E63/D63,"")</f>
-        <v>5.618055555555556e-7</v>
+        <v>0.000008988888888888889</v>
       </c>
       <c r="G63" s="79" t="n">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER($D$55)),F63*$D$55,"")</f>
-        <v>5.62028118690557e-7</v>
+        <v>0.000008992449899048911</v>
       </c>
       <c r="H63" s="82" t="n">
         <f>IF(ISNUMBER(F63),F63*$D$45,"")</f>
-        <v>561.8055555555555</v>
+        <v>8988.888888888889</v>
       </c>
       <c r="I63" s="76" t="n">
         <f>IF(AND(ISNUMBER(H63),ISNUMBER($D$55)),H63*$D$55,"")</f>
-        <v>562.028118690557</v>
+        <v>8992.449899048912</v>
       </c>
       <c r="J63" s="82" t="n">
         <f>E63-E62</f>
-        <v>48.15476190476187</v>
+        <v>770.4761904761899</v>
       </c>
       <c r="K63" s="82" t="n">
         <f>IF($G$40="pons",J63/(1-$G$41-$J$48),J63*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>48.64117364117361</v>
+        <v>778.2587782587777</v>
       </c>
       <c r="L63" s="88" t="n">
         <f>SUM($K$59:K63)</f>
-        <v>136.1952861952862</v>
+        <v>2179.124579124579</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2084,35 +2084,35 @@
       </c>
       <c r="E64" s="82" t="n">
         <f>$G$46/D64</f>
-        <v>404.5</v>
+        <v>6472</v>
       </c>
       <c r="F64" s="79" t="n">
         <f>IF(AND(ISNUMBER(D64),D64&gt;0,ISNUMBER(E64)),E64/D64,"")</f>
-        <v>8.09e-7</v>
+        <v>0.000012944</v>
       </c>
       <c r="G64" s="79" t="n">
         <f>IF(AND(ISNUMBER(F64),ISNUMBER($D$55)),F64*$D$55,"")</f>
-        <v>8.093204909144021e-7</v>
+        <v>0.000012949127854630433</v>
       </c>
       <c r="H64" s="82" t="n">
         <f>IF(ISNUMBER(F64),F64*$D$45,"")</f>
-        <v>809</v>
+        <v>12944</v>
       </c>
       <c r="I64" s="76" t="n">
         <f>IF(AND(ISNUMBER(H64),ISNUMBER($D$55)),H64*$D$55,"")</f>
-        <v>809.3204909144021</v>
+        <v>12949.127854630433</v>
       </c>
       <c r="J64" s="82" t="n">
         <f>E64-E63</f>
-        <v>67.41666666666669</v>
+        <v>1078.666666666667</v>
       </c>
       <c r="K64" s="82" t="n">
         <f>IF($G$40="pons",J64/(1-$G$41-$J$48),J64*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>68.09764309764311</v>
+        <v>1089.5622895622898</v>
       </c>
       <c r="L64" s="88" t="n">
         <f>SUM($K$59:K64)</f>
-        <v>204.29292929292933</v>
+        <v>3268.6868686868693</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2126,35 +2126,35 @@
       </c>
       <c r="E65" s="82" t="n">
         <f>$G$46/D65</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="F65" s="79" t="n">
         <f>IF(AND(ISNUMBER(D65),D65&gt;0,ISNUMBER(E65)),E65/D65,"")</f>
-        <v>0.0000012640625</v>
+        <v>0.000020225</v>
       </c>
       <c r="G65" s="79" t="n">
         <f>IF(AND(ISNUMBER(F65),ISNUMBER($D$55)),F65*$D$55,"")</f>
-        <v>0.0000012645632670537531</v>
+        <v>0.00002023301227286005</v>
       </c>
       <c r="H65" s="82" t="n">
         <f>IF(ISNUMBER(F65),F65*$D$45,"")</f>
-        <v>1264.0625</v>
+        <v>20225</v>
       </c>
       <c r="I65" s="76" t="n">
         <f>IF(AND(ISNUMBER(H65),ISNUMBER($D$55)),H65*$D$55,"")</f>
-        <v>1264.5632670537532</v>
+        <v>20233.01227286005</v>
       </c>
       <c r="J65" s="82" t="n">
         <f>E65-E64</f>
-        <v>101.125</v>
+        <v>1618</v>
       </c>
       <c r="K65" s="82" t="n">
         <f>IF($G$40="pons",J65/(1-$G$41-$J$48),J65*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>102.14646464646465</v>
+        <v>1634.3434343434344</v>
       </c>
       <c r="L65" s="88" t="n">
         <f>SUM($K$59:K65)</f>
-        <v>306.439393939394</v>
+        <v>4903.030303030304</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2168,35 +2168,35 @@
       </c>
       <c r="E66" s="82" t="n">
         <f>$G$46/D66</f>
-        <v>674.1666666666666</v>
+        <v>10786.666666666666</v>
       </c>
       <c r="F66" s="79" t="n">
         <f>IF(AND(ISNUMBER(D66),D66&gt;0,ISNUMBER(E66)),E66/D66,"")</f>
-        <v>0.0000022472222222222223</v>
+        <v>0.000035955555555555556</v>
       </c>
       <c r="G66" s="79" t="n">
         <f>IF(AND(ISNUMBER(F66),ISNUMBER($D$55)),F66*$D$55,"")</f>
-        <v>0.000002248112474762228</v>
+        <v>0.000035969799596195646</v>
       </c>
       <c r="H66" s="82" t="n">
         <f>IF(ISNUMBER(F66),F66*$D$45,"")</f>
-        <v>2247.222222222222</v>
+        <v>35955.555555555555</v>
       </c>
       <c r="I66" s="76" t="n">
         <f>IF(AND(ISNUMBER(H66),ISNUMBER($D$55)),H66*$D$55,"")</f>
-        <v>2248.112474762228</v>
+        <v>35969.79959619565</v>
       </c>
       <c r="J66" s="82" t="n">
         <f>E66-E65</f>
-        <v>168.54166666666663</v>
+        <v>2696.666666666666</v>
       </c>
       <c r="K66" s="82" t="n">
         <f>IF($G$40="pons",J66/(1-$G$41-$J$48),J66*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>170.2441077441077</v>
+        <v>2723.9057239057233</v>
       </c>
       <c r="L66" s="88" t="n">
         <f>SUM($K$59:K66)</f>
-        <v>476.68350168350173</v>
+        <v>7626.936026936028</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2210,35 +2210,35 @@
       </c>
       <c r="E67" s="83" t="n">
         <f>$G$46/D67</f>
-        <v>707.875</v>
+        <v>11326</v>
       </c>
       <c r="F67" s="80" t="n">
         <f>IF(AND(ISNUMBER(D67),D67&gt;0,ISNUMBER(E67)),E67/D67,"")</f>
-        <v>0.0000024775624999999997</v>
+        <v>0.000039640999999999995</v>
       </c>
       <c r="G67" s="80" t="n">
         <f>IF(AND(ISNUMBER(F67),ISNUMBER($D$55)),F67*$D$55,"")</f>
-        <v>0.000002478544003425356</v>
+        <v>0.000039656704054805695</v>
       </c>
       <c r="H67" s="83" t="n">
         <f>IF(ISNUMBER(F67),F67*$D$45,"")</f>
-        <v>2477.5624999999995</v>
+        <v>39640.99999999999</v>
       </c>
       <c r="I67" s="77" t="n">
         <f>IF(AND(ISNUMBER(H67),ISNUMBER($D$55)),H67*$D$55,"")</f>
-        <v>2478.5440034253556</v>
+        <v>39656.70405480569</v>
       </c>
       <c r="J67" s="83" t="n">
         <f>E67-E66</f>
-        <v>33.70833333333337</v>
+        <v>539.3333333333339</v>
       </c>
       <c r="K67" s="83" t="n">
         <f>IF($G$40="pons",J67/(1-$G$41-$J$48),J67*(1+$G$41+IF($G$40="four-stock",$J$46,0)))</f>
-        <v>34.048821548821586</v>
+        <v>544.7811447811454</v>
       </c>
       <c r="L67" s="89" t="n">
         <f>$J$41</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
     </row>
     <row r="68" ht="6" customHeight="1">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="E72" s="81" t="n">
         <f>IF(D72="","",IF(ABS(C72-$G$43)&lt;0.000001,$G$49,$G$50/D72))</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="F72" s="78" t="n">
         <f>IF(AND(ISNUMBER(D72),D72&gt;0,ISNUMBER(E72)),E72/D72,"")</f>
-        <v>0.0000024775625000000006</v>
+        <v>0.00003964100000000001</v>
       </c>
       <c r="G72" s="78" t="n">
         <f>IF(AND(ISNUMBER(F72),ISNUMBER($D$55)),F72*$D$55,"")</f>
-        <v>0.0000024785440034253568</v>
+        <v>0.00003965670405480571</v>
       </c>
       <c r="H72" s="81" t="n">
         <f>IF(ISNUMBER(F72),F72*$D$45,"")</f>
-        <v>2477.5625000000005</v>
+        <v>39641.00000000001</v>
       </c>
       <c r="I72" s="75" t="n">
         <f>IF(AND(ISNUMBER(H72),ISNUMBER($D$55)),H72*$D$55,"")</f>
-        <v>2478.5440034253565</v>
+        <v>39656.704054805705</v>
       </c>
       <c r="J72" s="81" t="n">
         <f>IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),0,E72-$G$49)</f>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="L72" s="87" t="n">
         <f>IF(D72="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C72-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2364,35 +2364,35 @@
       </c>
       <c r="E73" s="82" t="n">
         <f>IF(D73="","",IF(ABS(C73-$G$43)&lt;0.000001,$G$49,$G$50/D73))</f>
-        <v>871.7672413793106</v>
+        <v>13948.27586206897</v>
       </c>
       <c r="F73" s="79" t="n">
         <f>IF(AND(ISNUMBER(D73),D73&gt;0,ISNUMBER(E73)),E73/D73,"")</f>
-        <v>0.000007364930142687281</v>
+        <v>0.00011783888228299649</v>
       </c>
       <c r="G73" s="79" t="n">
         <f>IF(AND(ISNUMBER(F73),ISNUMBER($D$55)),F73*$D$55,"")</f>
-        <v>0.000007367847810420207</v>
+        <v>0.00011788556496672331</v>
       </c>
       <c r="H73" s="82" t="n">
         <f>IF(ISNUMBER(F73),F73*$D$45,"")</f>
-        <v>7364.930142687281</v>
+        <v>117838.88228299649</v>
       </c>
       <c r="I73" s="76" t="n">
         <f>IF(AND(ISNUMBER(H73),ISNUMBER($D$55)),H73*$D$55,"")</f>
-        <v>7367.847810420207</v>
+        <v>117885.56496672331</v>
       </c>
       <c r="J73" s="82" t="n">
         <f>IF(D73="","",E73-E72)</f>
-        <v>366.1422413793106</v>
+        <v>5858.275862068969</v>
       </c>
       <c r="K73" s="82" t="n">
         <f>IF(D73="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L73-L72,J73*(1+$G$42)))</f>
-        <v>369.8406478578894</v>
+        <v>5917.45036572623</v>
       </c>
       <c r="L73" s="88" t="n">
         <f>IF(D73="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C73-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
-        <v>880.5729710902126</v>
+        <v>14089.167537443402</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2406,35 +2406,35 @@
       </c>
       <c r="E74" s="82" t="n">
         <f>IF(D74="","",IF(ABS(C74-$G$43)&lt;0.000001,$G$49,$G$50/D74))</f>
-        <v>910.2160216021607</v>
+        <v>14563.456345634571</v>
       </c>
       <c r="F74" s="79" t="n">
         <f>IF(AND(ISNUMBER(D74),D74&gt;0,ISNUMBER(E74)),E74/D74,"")</f>
-        <v>0.000008028908201351198</v>
+        <v>0.00012846253122161916</v>
       </c>
       <c r="G74" s="79" t="n">
         <f>IF(AND(ISNUMBER(F74),ISNUMBER($D$55)),F74*$D$55,"")</f>
-        <v>0.000008032088908558986</v>
+        <v>0.00012851342253694377</v>
       </c>
       <c r="H74" s="82" t="n">
         <f>IF(ISNUMBER(F74),F74*$D$45,"")</f>
-        <v>8028.908201351198</v>
+        <v>128462.53122161917</v>
       </c>
       <c r="I74" s="76" t="n">
         <f>IF(AND(ISNUMBER(H74),ISNUMBER($D$55)),H74*$D$55,"")</f>
-        <v>8032.088908558987</v>
+        <v>128513.42253694379</v>
       </c>
       <c r="J74" s="82" t="n">
         <f>IF(D74="","",E74-E73)</f>
-        <v>38.44878022285013</v>
+        <v>615.1804835656021</v>
       </c>
       <c r="K74" s="82" t="n">
         <f>IF(D74="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L74-L73,J74*(1+$G$42)))</f>
-        <v>38.837151740252466</v>
+        <v>621.3944278440395</v>
       </c>
       <c r="L74" s="88" t="n">
         <f>IF(D74="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C74-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
-        <v>919.4101228304651</v>
+        <v>14710.561965287441</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2448,35 +2448,35 @@
       </c>
       <c r="E75" s="82" t="n">
         <f>IF(D75="","",IF(ABS(C75-$G$43)&lt;0.000001,$G$49,$G$50/D75))</f>
-        <v>952.2128060263659</v>
+        <v>15235.404896421855</v>
       </c>
       <c r="F75" s="79" t="n">
         <f>IF(AND(ISNUMBER(D75),D75&gt;0,ISNUMBER(E75)),E75/D75,"")</f>
-        <v>0.000008786897833388316</v>
+        <v>0.00014059036533421306</v>
       </c>
       <c r="G75" s="79" t="n">
         <f>IF(AND(ISNUMBER(F75),ISNUMBER($D$55)),F75*$D$55,"")</f>
-        <v>0.000008790378823402383</v>
+        <v>0.00014064606117443812</v>
       </c>
       <c r="H75" s="82" t="n">
         <f>IF(ISNUMBER(F75),F75*$D$45,"")</f>
-        <v>8786.897833388317</v>
+        <v>140590.36533421307</v>
       </c>
       <c r="I75" s="76" t="n">
         <f>IF(AND(ISNUMBER(H75),ISNUMBER($D$55)),H75*$D$55,"")</f>
-        <v>8790.378823402383</v>
+        <v>140646.06117443813</v>
       </c>
       <c r="J75" s="82" t="n">
         <f>IF(D75="","",E75-E74)</f>
-        <v>41.9967844242052</v>
+        <v>671.9485507872832</v>
       </c>
       <c r="K75" s="82" t="n">
         <f>IF(D75="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L75-L74,J75*(1+$G$42)))</f>
-        <v>42.420994367883964</v>
+        <v>678.7359098861434</v>
       </c>
       <c r="L75" s="88" t="n">
         <f>IF(D75="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C75-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
-        <v>961.831117198349</v>
+        <v>15389.297875173585</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2490,35 +2490,35 @@
       </c>
       <c r="E76" s="82" t="n">
         <f>IF(D76="","",IF(ABS(C76-$G$43)&lt;0.000001,$G$49,$G$50/D76))</f>
-        <v>998.2724580454103</v>
+        <v>15972.359328726565</v>
       </c>
       <c r="F76" s="79" t="n">
         <f>IF(AND(ISNUMBER(D76),D76&gt;0,ISNUMBER(E76)),E76/D76,"")</f>
-        <v>0.000009657522298958565</v>
+        <v>0.00015452035678333704</v>
       </c>
       <c r="G76" s="79" t="n">
         <f>IF(AND(ISNUMBER(F76),ISNUMBER($D$55)),F76*$D$55,"")</f>
-        <v>0.00000966134819284293</v>
+        <v>0.00015458157108548689</v>
       </c>
       <c r="H76" s="82" t="n">
         <f>IF(ISNUMBER(F76),F76*$D$45,"")</f>
-        <v>9657.522298958565</v>
+        <v>154520.35678333705</v>
       </c>
       <c r="I76" s="76" t="n">
         <f>IF(AND(ISNUMBER(H76),ISNUMBER($D$55)),H76*$D$55,"")</f>
-        <v>9661.34819284293</v>
+        <v>154581.57108548688</v>
       </c>
       <c r="J76" s="82" t="n">
         <f>IF(D76="","",E76-E75)</f>
-        <v>46.05965201904439</v>
+        <v>736.9544323047103</v>
       </c>
       <c r="K76" s="82" t="n">
         <f>IF(D76="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L76-L75,J76*(1+$G$42)))</f>
-        <v>46.5249010293378</v>
+        <v>744.3984164694048</v>
       </c>
       <c r="L76" s="88" t="n">
         <f>IF(D76="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C76-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
-        <v>1008.3560182276868</v>
+        <v>16133.69629164299</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2532,35 +2532,35 @@
       </c>
       <c r="E77" s="82" t="n">
         <f>IF(D77="","",IF(ABS(C77-$G$43)&lt;0.000001,$G$49,$G$50/D77))</f>
-        <v>1049.0145228215774</v>
+        <v>16784.23236514524</v>
       </c>
       <c r="F77" s="79" t="n">
         <f>IF(AND(ISNUMBER(D77),D77&gt;0,ISNUMBER(E77)),E77/D77,"")</f>
-        <v>0.000010664255522460026</v>
+        <v>0.00017062808835936042</v>
       </c>
       <c r="G77" s="79" t="n">
         <f>IF(AND(ISNUMBER(F77),ISNUMBER($D$55)),F77*$D$55,"")</f>
-        <v>0.000010668480240635316</v>
+        <v>0.00017069568385016506</v>
       </c>
       <c r="H77" s="82" t="n">
         <f>IF(ISNUMBER(F77),F77*$D$45,"")</f>
-        <v>10664.255522460026</v>
+        <v>170628.0883593604</v>
       </c>
       <c r="I77" s="76" t="n">
         <f>IF(AND(ISNUMBER(H77),ISNUMBER($D$55)),H77*$D$55,"")</f>
-        <v>10668.480240635316</v>
+        <v>170695.68385016505</v>
       </c>
       <c r="J77" s="82" t="n">
         <f>IF(D77="","",E77-E76)</f>
-        <v>50.742064776167126</v>
+        <v>811.873036418674</v>
       </c>
       <c r="K77" s="82" t="n">
         <f>IF(D77="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L77-L76,J77*(1+$G$42)))</f>
-        <v>51.25461088501754</v>
+        <v>820.0737741602807</v>
       </c>
       <c r="L77" s="88" t="n">
         <f>IF(D77="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C77-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
-        <v>1059.6106291127044</v>
+        <v>16953.77006580327</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2574,35 +2574,35 @@
       </c>
       <c r="E78" s="82" t="n">
         <f>IF(D78="","",IF(ABS(C78-$G$43)&lt;0.000001,$G$49,$G$50/D78))</f>
-        <v>1105.1912568306018</v>
+        <v>17683.06010928963</v>
       </c>
       <c r="F78" s="79" t="n">
         <f>IF(AND(ISNUMBER(D78),D78&gt;0,ISNUMBER(E78)),E78/D78,"")</f>
-        <v>0.000011837021111409731</v>
+        <v>0.0001893923377825557</v>
       </c>
       <c r="G78" s="79" t="n">
         <f>IF(AND(ISNUMBER(F78),ISNUMBER($D$55)),F78*$D$55,"")</f>
-        <v>0.000011841710428739512</v>
+        <v>0.0001894673668598322</v>
       </c>
       <c r="H78" s="82" t="n">
         <f>IF(ISNUMBER(F78),F78*$D$45,"")</f>
-        <v>11837.021111409731</v>
+        <v>189392.3377825557</v>
       </c>
       <c r="I78" s="76" t="n">
         <f>IF(AND(ISNUMBER(H78),ISNUMBER($D$55)),H78*$D$55,"")</f>
-        <v>11841.71042873951</v>
+        <v>189467.36685983217</v>
       </c>
       <c r="J78" s="82" t="n">
         <f>IF(D78="","",E78-E77)</f>
-        <v>56.17673400902436</v>
+        <v>898.8277441443897</v>
       </c>
       <c r="K78" s="82" t="n">
         <f>IF(D78="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L78-L77,J78*(1+$G$42)))</f>
-        <v>56.744175766691114</v>
+        <v>907.9068122670578</v>
       </c>
       <c r="L78" s="88" t="n">
         <f>IF(D78="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C78-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
-        <v>1116.3548048793955</v>
+        <v>17861.676878070328</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -2616,35 +2616,35 @@
       </c>
       <c r="E79" s="82" t="n">
         <f>IF(D79="","",IF(ABS(C79-$G$43)&lt;0.000001,$G$49,$G$50/D79))</f>
-        <v>1167.7251732101624</v>
+        <v>18683.6027713626</v>
       </c>
       <c r="F79" s="79" t="n">
         <f>IF(AND(ISNUMBER(D79),D79&gt;0,ISNUMBER(E79)),E79/D79,"")</f>
-        <v>0.000013214441913925635</v>
+        <v>0.00021143107062281016</v>
       </c>
       <c r="G79" s="79" t="n">
         <f>IF(AND(ISNUMBER(F79),ISNUMBER($D$55)),F79*$D$55,"")</f>
-        <v>0.000013219676905980402</v>
+        <v>0.00021151483049568643</v>
       </c>
       <c r="H79" s="82" t="n">
         <f>IF(ISNUMBER(F79),F79*$D$45,"")</f>
-        <v>13214.441913925635</v>
+        <v>211431.07062281016</v>
       </c>
       <c r="I79" s="76" t="n">
         <f>IF(AND(ISNUMBER(H79),ISNUMBER($D$55)),H79*$D$55,"")</f>
-        <v>13219.676905980403</v>
+        <v>211514.83049568644</v>
       </c>
       <c r="J79" s="82" t="n">
         <f>IF(D79="","",E79-E78)</f>
-        <v>62.53391637956065</v>
+        <v>1000.5426620729704</v>
       </c>
       <c r="K79" s="82" t="n">
         <f>IF(D79="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L79-L78,J79*(1+$G$42)))</f>
-        <v>63.16557210056635</v>
+        <v>1010.6491536090616</v>
       </c>
       <c r="L79" s="88" t="n">
         <f>IF(D79="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C79-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
-        <v>1179.5203769799618</v>
+        <v>18872.32603167939</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -2658,35 +2658,35 @@
       </c>
       <c r="E80" s="82" t="n">
         <f>IF(D80="","",IF(ABS(C80-$G$43)&lt;0.000001,$G$49,$G$50/D80))</f>
-        <v>1237.760097919218</v>
+        <v>19804.161566707488</v>
       </c>
       <c r="F80" s="79" t="n">
         <f>IF(AND(ISNUMBER(D80),D80&gt;0,ISNUMBER(E80)),E80/D80,"")</f>
-        <v>0.000014847061150071418</v>
+        <v>0.0002375529784011427</v>
       </c>
       <c r="G80" s="79" t="n">
         <f>IF(AND(ISNUMBER(F80),ISNUMBER($D$55)),F80*$D$55,"")</f>
-        <v>0.000014852942915465941</v>
+        <v>0.00023764708664745506</v>
       </c>
       <c r="H80" s="82" t="n">
         <f>IF(ISNUMBER(F80),F80*$D$45,"")</f>
-        <v>14847.061150071419</v>
+        <v>237552.9784011427</v>
       </c>
       <c r="I80" s="76" t="n">
         <f>IF(AND(ISNUMBER(H80),ISNUMBER($D$55)),H80*$D$55,"")</f>
-        <v>14852.942915465943</v>
+        <v>237647.0866474551</v>
       </c>
       <c r="J80" s="82" t="n">
         <f>IF(D80="","",E80-E79)</f>
-        <v>70.03492470905553</v>
+        <v>1120.5587953448885</v>
       </c>
       <c r="K80" s="82" t="n">
         <f>IF(D80="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L80-L79,J80*(1+$G$42)))</f>
-        <v>70.74234819096455</v>
+        <v>1131.8775710554328</v>
       </c>
       <c r="L80" s="88" t="n">
         <f>IF(D80="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C80-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
-        <v>1250.2627251709264</v>
+        <v>20004.203602734822</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -2700,35 +2700,35 @@
       </c>
       <c r="E81" s="82" t="n">
         <f>IF(D81="","",IF(ABS(C81-$G$43)&lt;0.000001,$G$49,$G$50/D81))</f>
-        <v>1316.7317708333348</v>
+        <v>21067.708333333358</v>
       </c>
       <c r="F81" s="79" t="n">
         <f>IF(AND(ISNUMBER(D81),D81&gt;0,ISNUMBER(E81)),E81/D81,"")</f>
-        <v>0.000016802046034071218</v>
+        <v>0.0002688327365451395</v>
       </c>
       <c r="G81" s="79" t="n">
         <f>IF(AND(ISNUMBER(F81),ISNUMBER($D$55)),F81*$D$55,"")</f>
-        <v>0.000016808702280174165</v>
+        <v>0.00026893923648278664</v>
       </c>
       <c r="H81" s="82" t="n">
         <f>IF(ISNUMBER(F81),F81*$D$45,"")</f>
-        <v>16802.046034071216</v>
+        <v>268832.73654513946</v>
       </c>
       <c r="I81" s="76" t="n">
         <f>IF(AND(ISNUMBER(H81),ISNUMBER($D$55)),H81*$D$55,"")</f>
-        <v>16808.702280174162</v>
+        <v>268939.2364827866</v>
       </c>
       <c r="J81" s="82" t="n">
         <f>IF(D81="","",E81-E80)</f>
-        <v>78.97167291411688</v>
+        <v>1263.54676662587</v>
       </c>
       <c r="K81" s="82" t="n">
         <f>IF(D81="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L81-L80,J81*(1+$G$42)))</f>
-        <v>79.7693665799161</v>
+        <v>1276.3098652786575</v>
       </c>
       <c r="L81" s="88" t="n">
         <f>IF(D81="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C81-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
-        <v>1330.0320917508425</v>
+        <v>21280.51346801348</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -2742,35 +2742,35 @@
       </c>
       <c r="E82" s="82" t="n">
         <f>IF(D82="","",IF(ABS(C82-$G$43)&lt;0.000001,$G$49,$G$50/D82))</f>
-        <v>1406.4673157162745</v>
+        <v>22503.47705146039</v>
       </c>
       <c r="F82" s="79" t="n">
         <f>IF(AND(ISNUMBER(D82),D82&gt;0,ISNUMBER(E82)),E82/D82,"")</f>
-        <v>0.000019170208197523652</v>
+        <v>0.00030672333116037843</v>
       </c>
       <c r="G82" s="79" t="n">
         <f>IF(AND(ISNUMBER(F82),ISNUMBER($D$55)),F82*$D$55,"")</f>
-        <v>0.000019177802607356162</v>
+        <v>0.0003068448417176986</v>
       </c>
       <c r="H82" s="82" t="n">
         <f>IF(ISNUMBER(F82),F82*$D$45,"")</f>
-        <v>19170.20819752365</v>
+        <v>306723.3311603784</v>
       </c>
       <c r="I82" s="76" t="n">
         <f>IF(AND(ISNUMBER(H82),ISNUMBER($D$55)),H82*$D$55,"")</f>
-        <v>19177.802607356163</v>
+        <v>306844.8417176986</v>
       </c>
       <c r="J82" s="82" t="n">
         <f>IF(D82="","",E82-E81)</f>
-        <v>89.73554488293962</v>
+        <v>1435.768718127034</v>
       </c>
       <c r="K82" s="82" t="n">
         <f>IF(D82="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L82-L81,J82*(1+$G$42)))</f>
-        <v>90.6419645282217</v>
+        <v>1450.2714324515473</v>
       </c>
       <c r="L82" s="88" t="n">
         <f>IF(D82="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C82-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
-        <v>1420.6740562790642</v>
+        <v>22730.784900465027</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -2784,35 +2784,35 @@
       </c>
       <c r="E83" s="82" t="n">
         <f>IF(D83="","",IF(ABS(C83-$G$43)&lt;0.000001,$G$49,$G$50/D83))</f>
-        <v>1509.3283582089573</v>
+        <v>24149.253731343317</v>
       </c>
       <c r="F83" s="79" t="n">
         <f>IF(AND(ISNUMBER(D83),D83&gt;0,ISNUMBER(E83)),E83/D83,"")</f>
-        <v>0.00002207674314992209</v>
+        <v>0.00035322789039875344</v>
       </c>
       <c r="G83" s="79" t="n">
         <f>IF(AND(ISNUMBER(F83),ISNUMBER($D$55)),F83*$D$55,"")</f>
-        <v>0.0000220854890035675</v>
+        <v>0.00035336782405708</v>
       </c>
       <c r="H83" s="82" t="n">
         <f>IF(ISNUMBER(F83),F83*$D$45,"")</f>
-        <v>22076.74314992209</v>
+        <v>353227.89039875346</v>
       </c>
       <c r="I83" s="76" t="n">
         <f>IF(AND(ISNUMBER(H83),ISNUMBER($D$55)),H83*$D$55,"")</f>
-        <v>22085.4890035675</v>
+        <v>353367.82405708</v>
       </c>
       <c r="J83" s="82" t="n">
         <f>IF(D83="","",E83-E82)</f>
-        <v>102.86104249268283</v>
+        <v>1645.7766798829252</v>
       </c>
       <c r="K83" s="82" t="n">
         <f>IF(D83="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L83-L82,J83*(1+$G$42)))</f>
-        <v>103.90004292190224</v>
+        <v>1662.4006867504359</v>
       </c>
       <c r="L83" s="88" t="n">
         <f>IF(D83="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C83-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
-        <v>1524.5740992009664</v>
+        <v>24393.185587215463</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -2826,35 +2826,35 @@
       </c>
       <c r="E84" s="82" t="n">
         <f>IF(D84="","",IF(ABS(C84-$G$43)&lt;0.000001,$G$49,$G$50/D84))</f>
-        <v>1628.421900161033</v>
+        <v>26054.750402576527</v>
       </c>
       <c r="F84" s="79" t="n">
         <f>IF(AND(ISNUMBER(D84),D84&gt;0,ISNUMBER(E84)),E84/D84,"")</f>
-        <v>0.000025698123384183808</v>
+        <v>0.0004111699741469409</v>
       </c>
       <c r="G84" s="79" t="n">
         <f>IF(AND(ISNUMBER(F84),ISNUMBER($D$55)),F84*$D$55,"")</f>
-        <v>0.000025708303872517323</v>
+        <v>0.0004113328619602772</v>
       </c>
       <c r="H84" s="82" t="n">
         <f>IF(ISNUMBER(F84),F84*$D$45,"")</f>
-        <v>25698.123384183808</v>
+        <v>411169.9741469409</v>
       </c>
       <c r="I84" s="76" t="n">
         <f>IF(AND(ISNUMBER(H84),ISNUMBER($D$55)),H84*$D$55,"")</f>
-        <v>25708.30387251732</v>
+        <v>411332.86196027714</v>
       </c>
       <c r="J84" s="82" t="n">
         <f>IF(D84="","",E84-E83)</f>
-        <v>119.09354195207561</v>
+        <v>1905.4966712332098</v>
       </c>
       <c r="K84" s="82" t="n">
         <f>IF(D84="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L84-L83,J84*(1+$G$42)))</f>
-        <v>120.29650702229856</v>
+        <v>1924.744112356777</v>
       </c>
       <c r="L84" s="88" t="n">
         <f>IF(D84="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C84-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
-        <v>1644.870606223265</v>
+        <v>26317.92969957224</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -2868,35 +2868,35 @@
       </c>
       <c r="E85" s="82" t="n">
         <f>IF(D85="","",IF(ABS(C85-$G$43)&lt;0.000001,$G$49,$G$50/D85))</f>
-        <v>1767.9195804195833</v>
+        <v>28286.713286713333</v>
       </c>
       <c r="F85" s="79" t="n">
         <f>IF(AND(ISNUMBER(D85),D85&gt;0,ISNUMBER(E85)),E85/D85,"")</f>
-        <v>0.000030289531272922977</v>
+        <v>0.00048463250036676764</v>
       </c>
       <c r="G85" s="79" t="n">
         <f>IF(AND(ISNUMBER(F85),ISNUMBER($D$55)),F85*$D$55,"")</f>
-        <v>0.000030301530679071887</v>
+        <v>0.0004848244908651502</v>
       </c>
       <c r="H85" s="82" t="n">
         <f>IF(ISNUMBER(F85),F85*$D$45,"")</f>
-        <v>30289.531272922977</v>
+        <v>484632.50036676764</v>
       </c>
       <c r="I85" s="76" t="n">
         <f>IF(AND(ISNUMBER(H85),ISNUMBER($D$55)),H85*$D$55,"")</f>
-        <v>30301.530679071886</v>
+        <v>484824.4908651502</v>
       </c>
       <c r="J85" s="82" t="n">
         <f>IF(D85="","",E85-E84)</f>
-        <v>139.49768025855042</v>
+        <v>2231.9628841368067</v>
       </c>
       <c r="K85" s="82" t="n">
         <f>IF(D85="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L85-L84,J85*(1+$G$42)))</f>
-        <v>140.906747735909</v>
+        <v>2254.507963774544</v>
       </c>
       <c r="L85" s="88" t="n">
         <f>IF(D85="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C85-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
-        <v>1785.777353959174</v>
+        <v>28572.437663346784</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -2910,35 +2910,35 @@
       </c>
       <c r="E86" s="82" t="n">
         <f>IF(D86="","",IF(ABS(C86-$G$43)&lt;0.000001,$G$49,$G$50/D86))</f>
-        <v>1933.5564053537287</v>
+        <v>30936.90248565966</v>
       </c>
       <c r="F86" s="79" t="n">
         <f>IF(AND(ISNUMBER(D86),D86&gt;0,ISNUMBER(E86)),E86/D86,"")</f>
-        <v>0.00003623107604678115</v>
+        <v>0.0005796972167484984</v>
       </c>
       <c r="G86" s="79" t="n">
         <f>IF(AND(ISNUMBER(F86),ISNUMBER($D$55)),F86*$D$55,"")</f>
-        <v>0.000036245429236758905</v>
+        <v>0.0005799268677881425</v>
       </c>
       <c r="H86" s="82" t="n">
         <f>IF(ISNUMBER(F86),F86*$D$45,"")</f>
-        <v>36231.07604678115</v>
+        <v>579697.2167484984</v>
       </c>
       <c r="I86" s="76" t="n">
         <f>IF(AND(ISNUMBER(H86),ISNUMBER($D$55)),H86*$D$55,"")</f>
-        <v>36245.4292367589</v>
+        <v>579926.8677881424</v>
       </c>
       <c r="J86" s="82" t="n">
         <f>IF(D86="","",E86-E85)</f>
-        <v>165.63682493414535</v>
+        <v>2650.1891989463256</v>
       </c>
       <c r="K86" s="82" t="n">
         <f>IF(D86="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L86-L85,J86*(1+$G$42)))</f>
-        <v>167.30992417590414</v>
+        <v>2676.9587868144663</v>
       </c>
       <c r="L86" s="88" t="n">
         <f>IF(D86="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C86-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
-        <v>1953.0872781350781</v>
+        <v>31249.39645016125</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -2952,35 +2952,35 @@
       </c>
       <c r="E87" s="82" t="n">
         <f>IF(D87="","",IF(ABS(C87-$G$43)&lt;0.000001,$G$49,$G$50/D87))</f>
-        <v>2133.4388185654057</v>
+        <v>34135.02109704649</v>
       </c>
       <c r="F87" s="79" t="n">
         <f>IF(AND(ISNUMBER(D87),D87&gt;0,ISNUMBER(E87)),E87/D87,"")</f>
-        <v>0.000044109072620128736</v>
+        <v>0.0007057451619220598</v>
       </c>
       <c r="G87" s="79" t="n">
         <f>IF(AND(ISNUMBER(F87),ISNUMBER($D$55)),F87*$D$55,"")</f>
-        <v>0.00004412654673263486</v>
+        <v>0.0007060247477221577</v>
       </c>
       <c r="H87" s="82" t="n">
         <f>IF(ISNUMBER(F87),F87*$D$45,"")</f>
-        <v>44109.07262012873</v>
+        <v>705745.1619220597</v>
       </c>
       <c r="I87" s="76" t="n">
         <f>IF(AND(ISNUMBER(H87),ISNUMBER($D$55)),H87*$D$55,"")</f>
-        <v>44126.54673263485</v>
+        <v>706024.7477221576</v>
       </c>
       <c r="J87" s="82" t="n">
         <f>IF(D87="","",E87-E86)</f>
-        <v>199.88241321167698</v>
+        <v>3198.1186113868316</v>
       </c>
       <c r="K87" s="82" t="n">
         <f>IF(D87="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L87-L86,J87*(1+$G$42)))</f>
-        <v>201.90142748654125</v>
+        <v>3230.42283978466</v>
       </c>
       <c r="L87" s="88" t="n">
         <f>IF(D87="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C87-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
-        <v>2154.9887056216194</v>
+        <v>34479.81928994591</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -2994,35 +2994,35 @@
       </c>
       <c r="E88" s="82" t="n">
         <f>IF(D88="","",IF(ABS(C88-$G$43)&lt;0.000001,$G$49,$G$50/D88))</f>
-        <v>2379.4117647058824</v>
+        <v>38070.58823529412</v>
       </c>
       <c r="F88" s="79" t="n">
         <f>IF(AND(ISNUMBER(D88),D88&gt;0,ISNUMBER(E88)),E88/D88,"")</f>
-        <v>0.000054866435986159176</v>
+        <v>0.0008778629757785468</v>
       </c>
       <c r="G88" s="79" t="n">
         <f>IF(AND(ISNUMBER(F88),ISNUMBER($D$55)),F88*$D$55,"")</f>
-        <v>0.00005488817170215322</v>
+        <v>0.0008782107472344515</v>
       </c>
       <c r="H88" s="82" t="n">
         <f>IF(ISNUMBER(F88),F88*$D$45,"")</f>
-        <v>54866.43598615917</v>
+        <v>877862.9757785468</v>
       </c>
       <c r="I88" s="76" t="n">
         <f>IF(AND(ISNUMBER(H88),ISNUMBER($D$55)),H88*$D$55,"")</f>
-        <v>54888.171702153224</v>
+        <v>878210.7472344516</v>
       </c>
       <c r="J88" s="82" t="n">
         <f>IF(D88="","",E88-E87)</f>
-        <v>245.97294614047678</v>
+        <v>3935.5671382476285</v>
       </c>
       <c r="K88" s="82" t="n">
         <f>IF(D88="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L88-L87,J88*(1+$G$42)))</f>
-        <v>248.4575213540179</v>
+        <v>3975.3203416642864</v>
       </c>
       <c r="L88" s="88" t="n">
         <f>IF(D88="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C88-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
-        <v>2403.4462269756373</v>
+        <v>38455.1396316102</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3036,35 +3036,35 @@
       </c>
       <c r="E89" s="82" t="n">
         <f>IF(D89="","",IF(ABS(C89-$G$43)&lt;0.000001,$G$49,$G$50/D89))</f>
-        <v>2689.494680851064</v>
+        <v>43031.914893617024</v>
       </c>
       <c r="F89" s="79" t="n">
         <f>IF(AND(ISNUMBER(D89),D89&gt;0,ISNUMBER(E89)),E89/D89,"")</f>
-        <v>0.00007009853157537347</v>
+        <v>0.0011215765052059756</v>
       </c>
       <c r="G89" s="79" t="n">
         <f>IF(AND(ISNUMBER(F89),ISNUMBER($D$55)),F89*$D$55,"")</f>
-        <v>0.00007012630159080342</v>
+        <v>0.0011220208254528548</v>
       </c>
       <c r="H89" s="82" t="n">
         <f>IF(ISNUMBER(F89),F89*$D$45,"")</f>
-        <v>70098.53157537348</v>
+        <v>1121576.5052059756</v>
       </c>
       <c r="I89" s="76" t="n">
         <f>IF(AND(ISNUMBER(H89),ISNUMBER($D$55)),H89*$D$55,"")</f>
-        <v>70126.30159080343</v>
+        <v>1122020.8254528549</v>
       </c>
       <c r="J89" s="82" t="n">
         <f>IF(D89="","",E89-E88)</f>
-        <v>310.08291614518157</v>
+        <v>4961.326658322905</v>
       </c>
       <c r="K89" s="82" t="n">
         <f>IF(D89="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L89-L88,J89*(1+$G$42)))</f>
-        <v>313.215066813314</v>
+        <v>5011.441069013024</v>
       </c>
       <c r="L89" s="88" t="n">
         <f>IF(D89="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C89-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
-        <v>2716.6612937889513</v>
+        <v>43466.58070062322</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3078,35 +3078,35 @@
       </c>
       <c r="E90" s="82" t="n">
         <f>IF(D90="","",IF(ABS(C90-$G$43)&lt;0.000001,$G$49,$G$50/D90))</f>
-        <v>3092.5076452599405</v>
+        <v>49480.12232415905</v>
       </c>
       <c r="F90" s="79" t="n">
         <f>IF(AND(ISNUMBER(D90),D90&gt;0,ISNUMBER(E90)),E90/D90,"")</f>
-        <v>0.00009268065725855483</v>
+        <v>0.0014828905161368773</v>
       </c>
       <c r="G90" s="79" t="n">
         <f>IF(AND(ISNUMBER(F90),ISNUMBER($D$55)),F90*$D$55,"")</f>
-        <v>0.00009271737333839683</v>
+        <v>0.0014834779734143493</v>
       </c>
       <c r="H90" s="82" t="n">
         <f>IF(ISNUMBER(F90),F90*$D$45,"")</f>
-        <v>92680.65725855483</v>
+        <v>1482890.5161368772</v>
       </c>
       <c r="I90" s="76" t="n">
         <f>IF(AND(ISNUMBER(H90),ISNUMBER($D$55)),H90*$D$55,"")</f>
-        <v>92717.37333839682</v>
+        <v>1483477.9734143491</v>
       </c>
       <c r="J90" s="82" t="n">
         <f>IF(D90="","",E90-E89)</f>
-        <v>403.01296440887654</v>
+        <v>6448.207430542025</v>
       </c>
       <c r="K90" s="82" t="n">
         <f>IF(D90="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L90-L89,J90*(1+$G$42)))</f>
-        <v>407.083802433207</v>
+        <v>6513.340838931312</v>
       </c>
       <c r="L90" s="88" t="n">
         <f>IF(D90="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C90-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
-        <v>3123.7450962221583</v>
+        <v>49979.92153955453</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3120,35 +3120,35 @@
       </c>
       <c r="E91" s="82" t="n">
         <f>IF(D91="","",IF(ABS(C91-$G$43)&lt;0.000001,$G$49,$G$50/D91))</f>
-        <v>3637.5899280575563</v>
+        <v>58201.4388489209</v>
       </c>
       <c r="F91" s="79" t="n">
         <f>IF(AND(ISNUMBER(D91),D91&gt;0,ISNUMBER(E91)),E91/D91,"")</f>
-        <v>0.0001282315873919571</v>
+        <v>0.0020517053982713135</v>
       </c>
       <c r="G91" s="79" t="n">
         <f>IF(AND(ISNUMBER(F91),ISNUMBER($D$55)),F91*$D$55,"")</f>
-        <v>0.00012828238721729514</v>
+        <v>0.002052518195476722</v>
       </c>
       <c r="H91" s="82" t="n">
         <f>IF(ISNUMBER(F91),F91*$D$45,"")</f>
-        <v>128231.5873919571</v>
+        <v>2051705.3982713136</v>
       </c>
       <c r="I91" s="76" t="n">
         <f>IF(AND(ISNUMBER(H91),ISNUMBER($D$55)),H91*$D$55,"")</f>
-        <v>128282.38721729514</v>
+        <v>2052518.1954767222</v>
       </c>
       <c r="J91" s="82" t="n">
         <f>IF(D91="","",E91-E90)</f>
-        <v>545.0822827976158</v>
+        <v>8721.316524761853</v>
       </c>
       <c r="K91" s="82" t="n">
         <f>IF(D91="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L91-L90,J91*(1+$G$42)))</f>
-        <v>550.5881644420342</v>
+        <v>8809.410631072547</v>
       </c>
       <c r="L91" s="88" t="n">
         <f>IF(D91="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C91-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
-        <v>3674.3332606641925</v>
+        <v>58789.33217062708</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3162,35 +3162,35 @@
       </c>
       <c r="E92" s="82" t="n">
         <f>IF(D92="","",IF(ABS(C92-$G$43)&lt;0.000001,$G$49,$G$50/D92))</f>
-        <v>4415.938864628824</v>
+        <v>70655.02183406119</v>
       </c>
       <c r="F92" s="79" t="n">
         <f>IF(AND(ISNUMBER(D92),D92&gt;0,ISNUMBER(E92)),E92/D92,"")</f>
-        <v>0.00018897904311512012</v>
+        <v>0.003023664689841922</v>
       </c>
       <c r="G92" s="79" t="n">
         <f>IF(AND(ISNUMBER(F92),ISNUMBER($D$55)),F92*$D$55,"")</f>
-        <v>0.0001890539084628714</v>
+        <v>0.0030248625354059424</v>
       </c>
       <c r="H92" s="82" t="n">
         <f>IF(ISNUMBER(F92),F92*$D$45,"")</f>
-        <v>188979.04311512012</v>
+        <v>3023664.689841922</v>
       </c>
       <c r="I92" s="76" t="n">
         <f>IF(AND(ISNUMBER(H92),ISNUMBER($D$55)),H92*$D$55,"")</f>
-        <v>189053.9084628714</v>
+        <v>3024862.5354059422</v>
       </c>
       <c r="J92" s="82" t="n">
         <f>IF(D92="","",E92-E91)</f>
-        <v>778.348936571268</v>
+        <v>12453.582985140289</v>
       </c>
       <c r="K92" s="82" t="n">
         <f>IF(D92="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L92-L91,J92*(1+$G$42)))</f>
-        <v>786.211047041681</v>
+        <v>12579.376752666896</v>
       </c>
       <c r="L92" s="88" t="n">
         <f>IF(D92="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C92-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
-        <v>4460.5443077058735</v>
+        <v>71368.70892329398</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3204,35 +3204,35 @@
       </c>
       <c r="E93" s="82" t="n">
         <f>IF(D93="","",IF(ABS(C93-$G$43)&lt;0.000001,$G$49,$G$50/D93))</f>
-        <v>5618.05555555556</v>
+        <v>89888.88888888896</v>
       </c>
       <c r="F93" s="79" t="n">
         <f>IF(AND(ISNUMBER(D93),D93&gt;0,ISNUMBER(E93)),E93/D93,"")</f>
-        <v>0.0003058719135802474</v>
+        <v>0.0048939506172839585</v>
       </c>
       <c r="G93" s="79" t="n">
         <f>IF(AND(ISNUMBER(F93),ISNUMBER($D$55)),F93*$D$55,"")</f>
-        <v>0.0003059930868426371</v>
+        <v>0.0048958893894821935</v>
       </c>
       <c r="H93" s="82" t="n">
         <f>IF(ISNUMBER(F93),F93*$D$45,"")</f>
-        <v>305871.91358024743</v>
+        <v>4893950.617283959</v>
       </c>
       <c r="I93" s="76" t="n">
         <f>IF(AND(ISNUMBER(H93),ISNUMBER($D$55)),H93*$D$55,"")</f>
-        <v>305993.0868426371</v>
+        <v>4895889.389482194</v>
       </c>
       <c r="J93" s="82" t="n">
         <f>IF(D93="","",E93-E92)</f>
-        <v>1202.1166909267358</v>
+        <v>19233.867054827773</v>
       </c>
       <c r="K93" s="82" t="n">
         <f>IF(D93="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L93-L92,J93*(1+$G$42)))</f>
-        <v>1214.2592837643851</v>
+        <v>19428.148540230162</v>
       </c>
       <c r="L93" s="88" t="n">
         <f>IF(D93="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C93-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
-        <v>5674.803591470259</v>
+        <v>90796.85746352414</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3246,35 +3246,35 @@
       </c>
       <c r="E94" s="82" t="n">
         <f>IF(D94="","",IF(ABS(C94-$G$43)&lt;0.000001,$G$49,$G$50/D94))</f>
-        <v>7719.46564885498</v>
+        <v>123511.45038167968</v>
       </c>
       <c r="F94" s="79" t="n">
         <f>IF(AND(ISNUMBER(D94),D94&gt;0,ISNUMBER(E94)),E94/D94,"")</f>
-        <v>0.0005774867431967861</v>
+        <v>0.009239787891148578</v>
       </c>
       <c r="G94" s="79" t="n">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER($D$55)),F94*$D$55,"")</f>
-        <v>0.0005777155185421287</v>
+        <v>0.00924344829667406</v>
       </c>
       <c r="H94" s="82" t="n">
         <f>IF(ISNUMBER(F94),F94*$D$45,"")</f>
-        <v>577486.7431967861</v>
+        <v>9239787.891148578</v>
       </c>
       <c r="I94" s="76" t="n">
         <f>IF(AND(ISNUMBER(H94),ISNUMBER($D$55)),H94*$D$55,"")</f>
-        <v>577715.5185421288</v>
+        <v>9243448.296674062</v>
       </c>
       <c r="J94" s="82" t="n">
         <f>IF(D94="","",E94-E93)</f>
-        <v>2101.4100932994197</v>
+        <v>33622.561492790715</v>
       </c>
       <c r="K94" s="82" t="n">
         <f>IF(D94="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L94-L93,J94*(1+$G$42)))</f>
-        <v>2122.6364578781886</v>
+        <v>33962.18332605102</v>
       </c>
       <c r="L94" s="88" t="n">
         <f>IF(D94="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C94-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
-        <v>7797.440049348447</v>
+        <v>124759.04078957516</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3288,35 +3288,35 @@
       </c>
       <c r="E95" s="82" t="n">
         <f>IF(D95="","",IF(ABS(C95-$G$43)&lt;0.000001,$G$49,$G$50/D95))</f>
-        <v>12332.317073170778</v>
+        <v>197317.07317073244</v>
       </c>
       <c r="F95" s="79" t="n">
         <f>IF(AND(ISNUMBER(D95),D95&gt;0,ISNUMBER(E95)),E95/D95,"")</f>
-        <v>0.0014738622843545616</v>
+        <v>0.023581796549672986</v>
       </c>
       <c r="G95" s="79" t="n">
         <f>IF(AND(ISNUMBER(F95),ISNUMBER($D$55)),F95*$D$55,"")</f>
-        <v>0.0014744461650359158</v>
+        <v>0.023591138640574653</v>
       </c>
       <c r="H95" s="82" t="n">
         <f>IF(ISNUMBER(F95),F95*$D$45,"")</f>
-        <v>1473862.2843545617</v>
+        <v>23581796.549672987</v>
       </c>
       <c r="I95" s="76" t="n">
         <f>IF(AND(ISNUMBER(H95),ISNUMBER($D$55)),H95*$D$55,"")</f>
-        <v>1474446.1650359158</v>
+        <v>23591138.640574653</v>
       </c>
       <c r="J95" s="82" t="n">
         <f>IF(D95="","",E95-E94)</f>
-        <v>4612.851424315798</v>
+        <v>73805.62278905277</v>
       </c>
       <c r="K95" s="82" t="n">
         <f>IF(D95="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L95-L94,J95*(1+$G$42)))</f>
-        <v>4659.445883147243</v>
+        <v>74551.13413035589</v>
       </c>
       <c r="L95" s="88" t="n">
         <f>IF(D95="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C95-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
-        <v>12456.88593249569</v>
+        <v>199310.17491993104</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3330,35 +3330,35 @@
       </c>
       <c r="E96" s="82" t="n">
         <f>IF(D96="","",IF(ABS(C96-$G$43)&lt;0.000001,$G$49,$G$50/D96))</f>
-        <v>30643.939393939672</v>
+        <v>490303.03030303476</v>
       </c>
       <c r="F96" s="79" t="n">
         <f>IF(AND(ISNUMBER(D96),D96&gt;0,ISNUMBER(E96)),E96/D96,"")</f>
-        <v>0.009100321395776106</v>
+        <v>0.1456051423324177</v>
       </c>
       <c r="G96" s="79" t="n">
         <f>IF(AND(ISNUMBER(F96),ISNUMBER($D$55)),F96*$D$55,"")</f>
-        <v>0.00910392655069018</v>
+        <v>0.14566282481104287</v>
       </c>
       <c r="H96" s="82" t="n">
         <f>IF(ISNUMBER(F96),F96*$D$45,"")</f>
-        <v>9100321.395776106</v>
+        <v>145605142.3324177</v>
       </c>
       <c r="I96" s="76" t="n">
         <f>IF(AND(ISNUMBER(H96),ISNUMBER($D$55)),H96*$D$55,"")</f>
-        <v>9103926.550690178</v>
+        <v>145662824.81104285</v>
       </c>
       <c r="J96" s="82" t="n">
         <f>IF(D96="","",E96-E95)</f>
-        <v>18311.622320768896</v>
+        <v>292985.95713230234</v>
       </c>
       <c r="K96" s="82" t="n">
         <f>IF(D96="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L96-L95,J96*(1+$G$42)))</f>
-        <v>18496.588202796633</v>
+        <v>295945.4112447461</v>
       </c>
       <c r="L96" s="88" t="n">
         <f>IF(D96="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C96-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
-        <v>30953.474135292323</v>
+        <v>495255.58616467717</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -4003,23 +4003,23 @@
       </c>
       <c r="E118" s="81" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C118)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C118)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C118-$G$43)&lt;0.000001,$G$49,$G$50/D118))</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="F118" s="78" t="n">
         <f>IF(AND(ISNUMBER(D118),D118&gt;0,ISNUMBER(E118)),E118/D118,"")</f>
-        <v>0.0000024775625000000006</v>
+        <v>0.00003964100000000001</v>
       </c>
       <c r="G118" s="78" t="n">
         <f>IF(AND(ISNUMBER(F118),ISNUMBER($D$55)),F118*$D$55,"")</f>
-        <v>0.0000024785440034253568</v>
+        <v>0.00003965670405480571</v>
       </c>
       <c r="H118" s="81" t="n">
         <f>IF(ISNUMBER(F118),F118*$D$45,"")</f>
-        <v>2477.5625000000005</v>
+        <v>39641.00000000001</v>
       </c>
       <c r="I118" s="75" t="n">
         <f>IF(AND(ISNUMBER(H118),ISNUMBER($D$55)),H118*$D$55,"")</f>
-        <v>2478.5440034253565</v>
+        <v>39656.704054805705</v>
       </c>
       <c r="J118" s="72" t="n">
         <f>IF(H$118&gt;0,1-H118/H$118,"")</f>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E119" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C119)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C119)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C119-$G$43)&lt;0.000001,$G$49,$G$50/D119))</f>
-        <v>472.5467289719625</v>
+        <v>7560.7476635514</v>
       </c>
       <c r="F119" s="79" t="n">
         <f>IF(AND(ISNUMBER(D119),D119&gt;0,ISNUMBER(E119)),E119/D119,"")</f>
-        <v>0.0000021639990392173977</v>
+        <v>0.000034623984627478364</v>
       </c>
       <c r="G119" s="79" t="n">
         <f>IF(AND(ISNUMBER(F119),ISNUMBER($D$55)),F119*$D$55,"")</f>
-        <v>0.000002164856322321037</v>
+        <v>0.00003463770115713659</v>
       </c>
       <c r="H119" s="82" t="n">
         <f>IF(ISNUMBER(F119),F119*$D$45,"")</f>
-        <v>2163.9990392173977</v>
+        <v>34623.98462747836</v>
       </c>
       <c r="I119" s="76" t="n">
         <f>IF(AND(ISNUMBER(H119),ISNUMBER($D$55)),H119*$D$55,"")</f>
-        <v>2164.8563223210367</v>
+        <v>34637.70115713659</v>
       </c>
       <c r="J119" s="73" t="n">
         <f>IF(H$118&gt;0,1-H119/H$118,"")</f>
@@ -4075,23 +4075,23 @@
       </c>
       <c r="E120" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C120)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C120)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C120-$G$43)&lt;0.000001,$G$49,$G$50/D120))</f>
-        <v>324.1185897435897</v>
+        <v>5185.897435897436</v>
       </c>
       <c r="F120" s="79" t="n">
         <f>IF(AND(ISNUMBER(D120),D120&gt;0,ISNUMBER(E120)),E120/D120,"")</f>
-        <v>0.0000010180648011176856</v>
+        <v>0.00001628903681788297</v>
       </c>
       <c r="G120" s="79" t="n">
         <f>IF(AND(ISNUMBER(F120),ISNUMBER($D$55)),F120*$D$55,"")</f>
-        <v>0.000001018468114491024</v>
+        <v>0.000016295489831856383</v>
       </c>
       <c r="H120" s="82" t="n">
         <f>IF(ISNUMBER(F120),F120*$D$45,"")</f>
-        <v>1018.0648011176856</v>
+        <v>16289.03681788297</v>
       </c>
       <c r="I120" s="76" t="n">
         <f>IF(AND(ISNUMBER(H120),ISNUMBER($D$55)),H120*$D$55,"")</f>
-        <v>1018.468114491024</v>
+        <v>16295.489831856385</v>
       </c>
       <c r="J120" s="73" t="n">
         <f>IF(H$118&gt;0,1-H120/H$118,"")</f>
@@ -4111,23 +4111,23 @@
       </c>
       <c r="E121" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C121)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C121)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C121-$G$43)&lt;0.000001,$G$49,$G$50/D121))</f>
-        <v>246.64634146341461</v>
+        <v>3946.341463414634</v>
       </c>
       <c r="F121" s="79" t="n">
         <f>IF(AND(ISNUMBER(D121),D121&gt;0,ISNUMBER(E121)),E121/D121,"")</f>
-        <v>5.895449137418202e-7</v>
+        <v>0.000009432718619869124</v>
       </c>
       <c r="G121" s="79" t="n">
         <f>IF(AND(ISNUMBER(F121),ISNUMBER($D$55)),F121*$D$55,"")</f>
-        <v>5.897784660143618e-7</v>
+        <v>0.00000943645545622979</v>
       </c>
       <c r="H121" s="82" t="n">
         <f>IF(ISNUMBER(F121),F121*$D$45,"")</f>
-        <v>589.5449137418202</v>
+        <v>9432.718619869123</v>
       </c>
       <c r="I121" s="76" t="n">
         <f>IF(AND(ISNUMBER(H121),ISNUMBER($D$55)),H121*$D$55,"")</f>
-        <v>589.7784660143618</v>
+        <v>9436.455456229789</v>
       </c>
       <c r="J121" s="73" t="n">
         <f>IF(H$118&gt;0,1-H121/H$118,"")</f>
@@ -4147,23 +4147,23 @@
       </c>
       <c r="E122" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C122)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C122)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C122-$G$43)&lt;0.000001,$G$49,$G$50/D122))</f>
-        <v>199.06496062992125</v>
+        <v>3185.03937007874</v>
       </c>
       <c r="F122" s="79" t="n">
         <f>IF(AND(ISNUMBER(D122),D122&gt;0,ISNUMBER(E122)),E122/D122,"")</f>
-        <v>3.8402295554591103e-7</v>
+        <v>0.0000061443672887345765</v>
       </c>
       <c r="G122" s="79" t="n">
         <f>IF(AND(ISNUMBER(F122),ISNUMBER($D$55)),F122*$D$55,"")</f>
-        <v>3.8417508888110793e-7</v>
+        <v>0.000006146801422097727</v>
       </c>
       <c r="H122" s="82" t="n">
         <f>IF(ISNUMBER(F122),F122*$D$45,"")</f>
-        <v>384.02295554591103</v>
+        <v>6144.3672887345765</v>
       </c>
       <c r="I122" s="76" t="n">
         <f>IF(AND(ISNUMBER(H122),ISNUMBER($D$55)),H122*$D$55,"")</f>
-        <v>384.1750888811079</v>
+        <v>6146.801422097727</v>
       </c>
       <c r="J122" s="73" t="n">
         <f>IF(H$118&gt;0,1-H122/H$118,"")</f>
@@ -4183,23 +4183,23 @@
       </c>
       <c r="E123" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C123)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C123)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C123-$G$43)&lt;0.000001,$G$49,$G$50/D123))</f>
-        <v>166.87293729372936</v>
+        <v>2669.96699669967</v>
       </c>
       <c r="F123" s="79" t="n">
         <f>IF(AND(ISNUMBER(D123),D123&gt;0,ISNUMBER(E123)),E123/D123,"")</f>
-        <v>2.6986052565652603e-7</v>
+        <v>0.0000043177684105044165</v>
       </c>
       <c r="G123" s="79" t="n">
         <f>IF(AND(ISNUMBER(F123),ISNUMBER($D$55)),F123*$D$55,"")</f>
-        <v>2.699674327598989e-7</v>
+        <v>0.0000043194789241583826</v>
       </c>
       <c r="H123" s="82" t="n">
         <f>IF(ISNUMBER(F123),F123*$D$45,"")</f>
-        <v>269.860525656526</v>
+        <v>4317.768410504416</v>
       </c>
       <c r="I123" s="76" t="n">
         <f>IF(AND(ISNUMBER(H123),ISNUMBER($D$55)),H123*$D$55,"")</f>
-        <v>269.96743275989894</v>
+        <v>4319.478924158383</v>
       </c>
       <c r="J123" s="73" t="n">
         <f>IF(H$118&gt;0,1-H123/H$118,"")</f>
@@ -4219,23 +4219,23 @@
       </c>
       <c r="E124" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C124)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C124)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C124-$G$43)&lt;0.000001,$G$49,$G$50/D124))</f>
-        <v>143.6434659090909</v>
+        <v>2298.2954545454545</v>
       </c>
       <c r="F124" s="79" t="n">
         <f>IF(AND(ISNUMBER(D124),D124&gt;0,ISNUMBER(E124)),E124/D124,"")</f>
-        <v>1.9995823379390494e-7</v>
+        <v>0.000003199331740702479</v>
       </c>
       <c r="G124" s="79" t="n">
         <f>IF(AND(ISNUMBER(F124),ISNUMBER($D$55)),F124*$D$55,"")</f>
-        <v>2.0003744862355986e-7</v>
+        <v>0.000003200599177976958</v>
       </c>
       <c r="H124" s="82" t="n">
         <f>IF(ISNUMBER(F124),F124*$D$45,"")</f>
-        <v>199.95823379390495</v>
+        <v>3199.3317407024792</v>
       </c>
       <c r="I124" s="76" t="n">
         <f>IF(AND(ISNUMBER(H124),ISNUMBER($D$55)),H124*$D$55,"")</f>
-        <v>200.03744862355987</v>
+        <v>3200.599177976958</v>
       </c>
       <c r="J124" s="73" t="n">
         <f>IF(H$118&gt;0,1-H124/H$118,"")</f>
@@ -4255,23 +4255,23 @@
       </c>
       <c r="E125" s="82" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C125)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C125)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C125-$G$43)&lt;0.000001,$G$49,$G$50/D125))</f>
-        <v>126.09102244389028</v>
+        <v>2017.4563591022445</v>
       </c>
       <c r="F125" s="79" t="n">
         <f>IF(AND(ISNUMBER(D125),D125&gt;0,ISNUMBER(E125)),E125/D125,"")</f>
-        <v>1.5407631171447938e-7</v>
+        <v>0.00000246522098743167</v>
       </c>
       <c r="G125" s="79" t="n">
         <f>IF(AND(ISNUMBER(F125),ISNUMBER($D$55)),F125*$D$55,"")</f>
-        <v>1.54137350105121e-7</v>
+        <v>0.000002466197601681936</v>
       </c>
       <c r="H125" s="82" t="n">
         <f>IF(ISNUMBER(F125),F125*$D$45,"")</f>
-        <v>154.07631171447937</v>
+        <v>2465.22098743167</v>
       </c>
       <c r="I125" s="76" t="n">
         <f>IF(AND(ISNUMBER(H125),ISNUMBER($D$55)),H125*$D$55,"")</f>
-        <v>154.137350105121</v>
+        <v>2466.197601681936</v>
       </c>
       <c r="J125" s="73" t="n">
         <f>IF(H$118&gt;0,1-H125/H$118,"")</f>
@@ -4291,23 +4291,23 @@
       </c>
       <c r="E126" s="83" t="n">
         <f>IF($G$40="four-stock",$G$49-$G$49*(($G$43-C126)*$D$45*(1-$J$47)*(1-$G$42))/($G$48+(($G$43-C126)*$D$45*(1-$J$47)*(1-$G$42))),IF(ABS(C126-$G$43)&lt;0.000001,$G$49,$G$50/D126))</f>
-        <v>112.36111111111111</v>
+        <v>1797.7777777777778</v>
       </c>
       <c r="F126" s="80" t="n">
         <f>IF(AND(ISNUMBER(D126),D126&gt;0,ISNUMBER(E126)),E126/D126,"")</f>
-        <v>1.2234876543209877e-7</v>
+        <v>0.0000019575802469135803</v>
       </c>
       <c r="G126" s="80" t="n">
         <f>IF(AND(ISNUMBER(F126),ISNUMBER($D$55)),F126*$D$55,"")</f>
-        <v>1.2239723473705465e-7</v>
+        <v>0.0000019583557557928744</v>
       </c>
       <c r="H126" s="83" t="n">
         <f>IF(ISNUMBER(F126),F126*$D$45,"")</f>
-        <v>122.34876543209877</v>
+        <v>1957.5802469135804</v>
       </c>
       <c r="I126" s="77" t="n">
         <f>IF(AND(ISNUMBER(H126),ISNUMBER($D$55)),H126*$D$55,"")</f>
-        <v>122.39723473705463</v>
+        <v>1958.355755792874</v>
       </c>
       <c r="J126" s="74" t="n">
         <f>IF(H$118&gt;0,1-H126/H$118,"")</f>
@@ -6463,10 +6463,10 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="O23" t="n">
-        <x:v>202.25</x:v>
+        <x:v>3236</x:v>
       </x:c>
       <x:c r="P23" t="n">
-        <x:v>202250000000</x:v>
+        <x:v>3236000000000</x:v>
       </x:c>
       <x:c r="Q23" t="n">
         <x:v>0.7142857142857143</x:v>
@@ -6475,10 +6475,10 @@
         <x:v>204081632.65306124</x:v>
       </x:c>
       <x:c r="S23" t="n">
-        <x:v>505.625</x:v>
+        <x:v>8090</x:v>
       </x:c>
       <x:c r="T23" t="n">
-        <x:v>103188775510.20409</x:v>
+        <x:v>1651020408163.2654</x:v>
       </x:c>
       <x:c r="U23" t="n">
         <x:v>0.01</x:v>
@@ -6487,16 +6487,16 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="W23" t="n">
-        <x:v>510.7323232323232</x:v>
+        <x:v>8171.717171717171</x:v>
       </x:c>
       <x:c r="X23" t="n">
         <x:v>81632653.06122449</x:v>
       </x:c>
       <x:c r="Y23" t="n">
-        <x:v>112.36111111111111</x:v>
+        <x:v>1797.7777777777778</x:v>
       </x:c>
       <x:c r="Z23" t="n">
-        <x:v>505.625</x:v>
+        <x:v>8090</x:v>
       </x:c>
       <x:c r="AA23" t="n">
         <x:v>0</x:v>
@@ -6508,10 +6508,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD23" t="str">
-        <x:v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</x:v>
+        <x:v>https://robin.etherscan.io/tx/0x387e3237904e4822075066331564561c373b691fd47ad2d52b4f64fb4f398c84#eventlog</x:v>
       </x:c>
       <x:c r="AE23" t="str">
-        <x:v>区块 68,708,148；USDG 6 decimals</x:v>
+        <x:v>TRAIN 发行区块 69,045,064；USDG 6 decimals；PERC 迁池同为 8,090</x:v>
       </x:c>
       <x:c r="AF23" t="str">
         <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>

--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Refa2ce57623f4d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R9e1971b00c5f408f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R14fcad28f4cb47d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rb0457d51e2684136"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1218,7 +1218,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
+        <f>IF($D$51&lt;&gt;"可达","",0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="3" t="str">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D27" s="59" t="n">
         <f>D8*J54</f>
-        <v>0.9</v>
+        <v>0.88209</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="C28" s="3" t="str">
-        <v>补回目标控筹率</v>
+        <v>原目标控筹率</v>
       </c>
       <c r="D28" s="57" t="n">
         <f>D8</f>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
+        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -1757,8 +1757,8 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="58" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
-        <v>1</v>
+        <f>MAX(0,1-$J$29)*MAX(0,1-$J$30)</f>
+        <v>0.9801</v>
       </c>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G55" s="49" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,9,FALSE)</f>
-        <v>USDG 按 1 USD 估算；https://www.coingecko.com/en/coins/global-dollar</v>
+        <v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</v>
       </c>
       <c r="H55" s="49"/>
       <c r="I55" s="49" t="str">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="J56" s="49" t="n">
         <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
-        <v>16491445.062873632</v>
+        <v>34582354.153782725</v>
       </c>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
@@ -5047,7 +5047,7 @@
       <x:c r="C6" s="5" t="str">
         <x:v>USDT / USD</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="D6" s="5">
         <x:v>0.999604</x:v>
       </x:c>
       <x:c r="E6" s="5"/>
@@ -5091,7 +5091,7 @@
       <x:c r="C7" s="5" t="str">
         <x:v>快照时间 / UTC</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="n">
+      <x:c r="D7" s="6">
         <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
@@ -5135,8 +5135,10 @@
       <x:c r="C8" s="5" t="str">
         <x:v>汇率来源</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:v>
+      <x:c r="D8" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="E8" s="5"/>
       <x:c r="F8" s="5"/>
@@ -5264,7 +5266,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</x:v>
+        <x:v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
@@ -5469,17 +5471,19 @@
         <x:v>SOL</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str"/>
-      <x:c r="H14" s="20" t="n">
+      <x:c r="H14" s="20">
         <x:v>108.53297905970763</x:v>
       </x:c>
-      <x:c r="I14" s="20" t="n">
+      <x:c r="I14" s="20">
         <x:v>108.53297905970763</x:v>
       </x:c>
-      <x:c r="J14" s="23" t="n">
+      <x:c r="J14" s="23">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K14" s="35" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K14" s="35" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L14" s="26" t="str">
         <x:v>generic</x:v>
@@ -5541,10 +5545,16 @@
       <x:c r="AE14" s="17" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF14" s="35" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG14" s="35" t="str"/>
+      <x:c r="AF14" s="35" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG14" s="35" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH14" s="29" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -5577,17 +5587,19 @@
         <x:v>SOL</x:v>
       </x:c>
       <x:c r="G15" s="36" t="str"/>
-      <x:c r="H15" s="21" t="n">
+      <x:c r="H15" s="21">
         <x:v>1.0003961568781237</x:v>
       </x:c>
-      <x:c r="I15" s="21" t="n">
+      <x:c r="I15" s="21">
         <x:v>108.53297905970763</x:v>
       </x:c>
-      <x:c r="J15" s="24" t="n">
+      <x:c r="J15" s="24">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K15" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K15" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L15" s="27" t="str">
         <x:v>generic</x:v>
@@ -5649,10 +5661,16 @@
       <x:c r="AE15" s="18" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF15" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG15" s="36" t="str"/>
+      <x:c r="AF15" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG15" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH15" s="30" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -5685,17 +5703,19 @@
         <x:v>BNB</x:v>
       </x:c>
       <x:c r="G16" s="36" t="str"/>
-      <x:c r="H16" s="21" t="n">
+      <x:c r="H16" s="21">
         <x:v>1.0003961568781237</x:v>
       </x:c>
-      <x:c r="I16" s="21" t="n">
+      <x:c r="I16" s="21">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="J16" s="24" t="n">
+      <x:c r="J16" s="24">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K16" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K16" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L16" s="27" t="str">
         <x:v>generic</x:v>
@@ -5757,10 +5777,16 @@
       <x:c r="AE16" s="18" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF16" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG16" s="36" t="str"/>
+      <x:c r="AF16" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG16" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH16" s="30" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -5793,17 +5819,19 @@
         <x:v>BNB</x:v>
       </x:c>
       <x:c r="G17" s="36" t="str"/>
-      <x:c r="H17" s="21" t="n">
+      <x:c r="H17" s="21">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="I17" s="21" t="n">
+      <x:c r="I17" s="21">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="J17" s="24" t="n">
+      <x:c r="J17" s="24">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K17" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K17" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L17" s="27" t="str">
         <x:v>generic</x:v>
@@ -5865,10 +5893,16 @@
       <x:c r="AE17" s="18" t="str">
         <x:v>2026-09-05</x:v>
       </x:c>
-      <x:c r="AF17" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG17" s="36" t="str"/>
+      <x:c r="AF17" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG17" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH17" s="30" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -5901,17 +5935,19 @@
         <x:v>BNB</x:v>
       </x:c>
       <x:c r="G18" s="36" t="str"/>
-      <x:c r="H18" s="21" t="n">
+      <x:c r="H18" s="21">
         <x:v>0.7357363515952317</x:v>
       </x:c>
-      <x:c r="I18" s="21" t="n">
+      <x:c r="I18" s="21">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="J18" s="24" t="n">
+      <x:c r="J18" s="24">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K18" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K18" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L18" s="27" t="str">
         <x:v>generic</x:v>
@@ -5973,10 +6009,16 @@
       <x:c r="AE18" s="18" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF18" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG18" s="36" t="str"/>
+      <x:c r="AF18" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG18" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH18" s="30" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -6009,17 +6051,19 @@
         <x:v>HYPE</x:v>
       </x:c>
       <x:c r="G19" s="36" t="str"/>
-      <x:c r="H19" s="21" t="n">
+      <x:c r="H19" s="21">
         <x:v>91.08607008375316</x:v>
       </x:c>
-      <x:c r="I19" s="21" t="n">
+      <x:c r="I19" s="21">
         <x:v>91.08607008375316</x:v>
       </x:c>
-      <x:c r="J19" s="24" t="n">
+      <x:c r="J19" s="24">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K19" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K19" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L19" s="27" t="str">
         <x:v>generic</x:v>
@@ -6081,10 +6125,16 @@
       <x:c r="AE19" s="18" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF19" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG19" s="36" t="str"/>
+      <x:c r="AF19" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG19" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH19" s="30" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -6117,17 +6167,19 @@
         <x:v>BNB</x:v>
       </x:c>
       <x:c r="G20" s="36" t="str"/>
-      <x:c r="H20" s="21" t="n">
+      <x:c r="H20" s="21">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="I20" s="21" t="n">
+      <x:c r="I20" s="21">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="J20" s="24" t="n">
+      <x:c r="J20" s="24">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K20" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K20" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L20" s="27" t="str">
         <x:v>flap</x:v>
@@ -6189,10 +6241,16 @@
       <x:c r="AE20" s="18" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF20" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG20" s="36" t="str"/>
+      <x:c r="AF20" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG20" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH20" s="30" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -6225,17 +6283,19 @@
         <x:v>BNB</x:v>
       </x:c>
       <x:c r="G21" s="36" t="str"/>
-      <x:c r="H21" s="21" t="n">
+      <x:c r="H21" s="21">
         <x:v>1.0003961568781237</x:v>
       </x:c>
-      <x:c r="I21" s="21" t="n">
+      <x:c r="I21" s="21">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="J21" s="24" t="n">
+      <x:c r="J21" s="24">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K21" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K21" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L21" s="27" t="str">
         <x:v>flap</x:v>
@@ -6297,10 +6357,16 @@
       <x:c r="AE21" s="18" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF21" s="36" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG21" s="36" t="str"/>
+      <x:c r="AF21" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG21" s="36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH21" s="30" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -6333,17 +6399,19 @@
         <x:v>ETH</x:v>
       </x:c>
       <x:c r="G22" s="37" t="str"/>
-      <x:c r="H22" s="22" t="n">
+      <x:c r="H22" s="22">
         <x:v>2580.0817123580937</x:v>
       </x:c>
-      <x:c r="I22" s="22" t="n">
+      <x:c r="I22" s="22">
         <x:v>2580.0817123580937</x:v>
       </x:c>
-      <x:c r="J22" s="25" t="n">
+      <x:c r="J22" s="25">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K22" s="37" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="K22" s="37" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L22" s="28" t="str">
         <x:v>pons</x:v>
@@ -6405,10 +6473,16 @@
       <x:c r="AE22" s="19" t="str">
         <x:v>原网页模型参数</x:v>
       </x:c>
-      <x:c r="AF22" s="37" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG22" s="37" t="str"/>
+      <x:c r="AF22" s="37" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG22" s="37" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH22" s="31" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -6441,17 +6515,19 @@
       <x:c r="G23" t="str">
         <x:v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</x:v>
       </x:c>
-      <x:c r="H23" t="n">
+      <x:c r="H23">
         <x:v>1.0003961568781237</x:v>
       </x:c>
-      <x:c r="I23" t="n">
+      <x:c r="I23">
         <x:v>2580.0817123580937</x:v>
       </x:c>
-      <x:c r="J23" t="n">
+      <x:c r="J23">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K23" t="str">
-        <x:v>USDG 按 1 USD 估算；https://www.coingecko.com/en/coins/global-dollar</x:v>
+      <x:c r="K23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="L23" t="str">
         <x:v>pons</x:v>
@@ -6513,10 +6589,16 @@
       <x:c r="AE23" t="str">
         <x:v>TRAIN 发行区块 69,045,064；USDG 6 decimals；PERC 迁池同为 8,090</x:v>
       </x:c>
-      <x:c r="AF23" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG23"/>
+      <x:c r="AF23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="AH23" t="n">
         <x:v>0.1</x:v>
       </x:c>

--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R14fcad28f4cb47d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rb0457d51e2684136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R56ed3c3ed042463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rb7541ef9e6094d02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D18" s="53" t="n">
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>689114.823085108</v>
+        <v>733940.915795696</v>
       </c>
       <c r="E18" s="48" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J18" s="62" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>692225.910545684</v>
+        <v>737069.7614212187</v>
       </c>
       <c r="K18" s="48" t="str">
         <v>USDT</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D19" s="63" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>689387.8206620901</v>
+        <v>734231.6715376248</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1218,8 +1218,8 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",0)</f>
-        <v>0</v>
+        <f>IF($D$51&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(IF($G$40="pons",1/(1-$G$42-$J$48),IF($G$40="four-stock",1/(1-$G$42),1+$G$42)))),""))</f>
+        <v>44826.09271058801</v>
       </c>
       <c r="E26" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -1784,8 +1784,8 @@
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="49" t="n">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
-        <v>16491445.062873632</v>
+        <f>IF($G$40="pons",$G$48-($D$8-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
+        <v>18367346.93877551</v>
       </c>
       <c r="K55" s="49"/>
       <c r="L55" s="49"/>
@@ -1811,8 +1811,8 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="49" t="n">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
-        <v>34582354.153782725</v>
+        <f>IF($G$40="pons",$G$48-($D$27-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
+        <v>36277346.93877551</v>
       </c>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
@@ -5266,7 +5266,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</x:v>
+        <x:v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>

--- a/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/templates/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R56ed3c3ed042463c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rb7541ef9e6094d02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R73381a3b10ae4f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rc860e189e8394303"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="7">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <x:numFmt numFmtId="201" formatCode="0.0000000000"/>
     <x:numFmt numFmtId="202" formatCode="@"/>
@@ -22,6 +22,7 @@
     <x:numFmt numFmtId="204" formatCode="#,##0"/>
     <x:numFmt numFmtId="205" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="206" formatCode="0.0000%"/>
+    <x:numFmt numFmtId="207" formatCode=";;;"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -155,7 +156,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="90">
+  <x:cellXfs count="91">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -416,6 +417,9 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1031,8 +1035,8 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="53" t="n">
-        <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>733940.915795696</v>
+        <f>IF(AND(LEFT($D$51,2)="可达",ISNUMBER($D$22),ISNUMBER($D$23),ISNUMBER($D$25),ISNUMBER($D$26)),SUM($D$22:$D$23,$D$25:$D$26),"")</f>
+        <v>262304.9848022362</v>
       </c>
       <c r="E18" s="48" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1054,7 +1058,7 @@
       </c>
       <c r="J18" s="62" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>737069.7614212187</v>
+        <v>265246.9886097256</v>
       </c>
       <c r="K18" s="48" t="str">
         <v>USDT</v>
@@ -1067,7 +1071,7 @@
       </c>
       <c r="D19" s="63" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>734231.6715376248</v>
+        <v>262408.8987261317</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1163,14 +1167,9 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="C24" s="3" t="str">
-        <v>洗筹损耗</v>
-      </c>
-      <c r="D24" s="65" t="n">
-        <f>IF($D$51="可达",$J$52*$D$29,"")</f>
-        <v>471635.93099345977</v>
-      </c>
+    <row r="24" customHeight="1" hidden="1">
+      <c r="C24" s="3"/>
+      <c r="D24" s="90"/>
       <c r="E24" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
         <v>USDG</v>
@@ -1375,7 +1374,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；手续费仅降低洗后持币，不另列资金。洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -5266,7 +5265,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</x:v>
+        <x:v>外盘一卖一买用卖出所得 Quote 回买；双边费用仅降低洗后持币，不另列资金；只按外盘曲线和买入费预留恢复目标所需 Quote。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
